--- a/NN/reports/feature_importance_white_ash.xlsx
+++ b/NN/reports/feature_importance_white_ash.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7062474833747497</v>
+        <v>0.6845825246565658</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6362195522648638</v>
+        <v>0.5382493457024158</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.896995760783203</v>
+        <v>1.716374809820653</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.364295226489566</v>
+        <v>1.46080402211227</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -538,31 +538,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.08246880628740741</v>
+        <v>0.07229710297930352</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09988749815210433</v>
+        <v>0.08544705036925032</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09498283663706635</v>
+        <v>0.09580546699064142</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8289843043962586</v>
+        <v>0.950238284056983</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07128262755739898</v>
+        <v>0.06542633112881102</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07705544123577049</v>
+        <v>0.0733571523048489</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06846314211187576</v>
+        <v>0.05403795099861045</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8493562573969222</v>
+        <v>0.9544387207107241</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04903500602640339</v>
+        <v>0.04943422175665614</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08430304018553582</v>
+        <v>0.07674211600304734</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01730137250248034</v>
+        <v>0.02481883644397202</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7606943922861409</v>
+        <v>0.7752739268555842</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
@@ -645,32 +645,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.004626324919916361</v>
+        <v>0.03095962366193929</v>
       </c>
       <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0206178134549151</v>
+      </c>
+      <c r="F6" t="n">
         <v>7</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.05824420674616871</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
+        <v>0.02327847696583166</v>
+      </c>
+      <c r="H6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.001262949775852151</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7</v>
-      </c>
       <c r="I6" t="n">
-        <v>1.096015046168342</v>
+        <v>1.108252928577687</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>5.25</v>
@@ -682,35 +682,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04459958238824484</v>
+        <v>0.01372099602664899</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005993456693266628</v>
+        <v>0.09700977603986639</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.00781935454004935</v>
+      </c>
+      <c r="H7" t="n">
         <v>7</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.01518133428992629</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
       <c r="I7" t="n">
-        <v>0.6364046570365809</v>
+        <v>0.4582047093013486</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01900451052351277</v>
+        <v>0.001710597127719114</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01378208735510999</v>
+        <v>0.03299938050792029</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009939008654648441</v>
+        <v>0.000480967553369394</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2327342654583391</v>
+        <v>1.241415499160037</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.001871315493037013</v>
+        <v>0.04900116966437267</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002703338354009314</v>
+        <v>0.006282901775732765</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004925752331383371</v>
+        <v>0.0222445090788812</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2096521009145822</v>
+        <v>0.691115068428279</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001559013620837175</v>
+        <v>0.001510450875415741</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00430646129333622</v>
+        <v>0.008577984193002682</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003129693806159795</v>
+        <v>0.0005094488461650393</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1930540242407095</v>
+        <v>0.8557199798313491</v>
       </c>
       <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
         <v>9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>11.25</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001553307575391961</v>
+        <v>0.002774283169211131</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001729292291145796</v>
+        <v>0.006850580205395447</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003834401666479636</v>
+        <v>0.0005062922773447998</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1001185059481942</v>
+        <v>0.6723410535432368</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>12.5</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003691020199628685</v>
+        <v>0.001127500295513923</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003808319631496802</v>
+        <v>0.004204229016941893</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0005837023647143225</v>
+        <v>0.0002686653235798641</v>
       </c>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09389834165287603</v>
+        <v>0.3376288728348107</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>12.75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001458861271158632</v>
+        <v>0.001989528458822621</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001627135550989605</v>
+        <v>0.01061077153102466</v>
       </c>
       <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0004304776373687647</v>
+      </c>
+      <c r="H13" t="n">
         <v>13</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.0007451898772962596</v>
-      </c>
-      <c r="H13" t="n">
-        <v>11</v>
-      </c>
       <c r="I13" t="n">
-        <v>0.09686951623215956</v>
+        <v>0.1434364390812606</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="K13" t="n">
-        <v>12.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00155754237862303</v>
+        <v>0.0007892185650921092</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001241403155364813</v>
+        <v>0.001317236861904575</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008623729204845998</v>
+        <v>0.0002300031859155394</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07623042591435913</v>
+        <v>0.2876059388042056</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001940536037222691</v>
+        <v>0.001671802649962494</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001076021648895751</v>
+        <v>0.001301859257282997</v>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0002548472917035527</v>
+        <v>0.0004260038654013032</v>
       </c>
       <c r="H15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07762246528209449</v>
+        <v>0.1476834725725422</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>13.75</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001404225682017941</v>
+        <v>0.0007484733299693599</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001101670676905276</v>
+        <v>0.00225963088193102</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0009103498877840787</v>
+        <v>0.0001314299664285756</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.06250486034620684</v>
+        <v>0.2904242566689663</v>
       </c>
       <c r="J16" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001790339871881961</v>
+        <v>0.0009911985965783464</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001054235308444598</v>
+        <v>0.001252252663216556</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0008934843093977074</v>
+        <v>0.0001395679118505244</v>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04799445060064622</v>
+        <v>0.1813992530194883</v>
       </c>
       <c r="J17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>14.75</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001804553066443183</v>
+        <v>0.0009669290773591936</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001934451077542527</v>
+        <v>0.0009551664113118747</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.001037664772678126</v>
+        <v>0.0002866632852076778</v>
       </c>
       <c r="H18" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0625206972171175</v>
+        <v>0.1830152428100216</v>
       </c>
       <c r="J18" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>15.25</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001151076564402788</v>
+        <v>0.0007132990845621818</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000616267317932914</v>
+        <v>0.0009767724073988632</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.919866859200873e-05</v>
+        <v>0.00030907281911563</v>
       </c>
       <c r="H19" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06992645175208789</v>
+        <v>0.1898896484834935</v>
       </c>
       <c r="J19" t="n">
         <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001018483715986682</v>
+        <v>0.0009472842970054597</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001012632241617861</v>
+        <v>0.0008788756963891966</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003831946832179245</v>
+        <v>0.0003334092436082625</v>
       </c>
       <c r="H20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.1852204622860074</v>
       </c>
       <c r="J20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>18.5</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.532889393750695e-05</v>
+        <v>0.0007956209360197645</v>
       </c>
       <c r="D21" t="n">
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001131826872553171</v>
+        <v>0.0009749774851976207</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.115942098724899e-05</v>
+        <v>0.0001024960144341058</v>
       </c>
       <c r="H21" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01051214548129864</v>
+        <v>0.1897455725824511</v>
       </c>
       <c r="J21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K21" t="n">
-        <v>19.25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.000996670607305688</v>
+        <v>0.001093656776562284</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0005552439466838009</v>
+        <v>0.001364844683579517</v>
       </c>
       <c r="F22" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>6.366449805519369e-05</v>
+        <v>-0.0001018963849096166</v>
       </c>
       <c r="H22" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06222176896551357</v>
+        <v>0.1870093359082308</v>
       </c>
       <c r="J22" t="n">
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>19.25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0007957878926734792</v>
+        <v>0.0007833738412022525</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0004977819595329388</v>
+        <v>0.0009664663431288174</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001953221747326817</v>
+        <v>0.0002139003216387048</v>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05329504018320641</v>
+        <v>0.1617144420372227</v>
       </c>
       <c r="J23" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="K23" t="n">
-        <v>19.75</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,1145 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0007680844327823844</v>
+      </c>
+      <c r="D24" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0008439315814980868</v>
+      </c>
+      <c r="F24" t="n">
+        <v>37</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0005290502901014738</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1579236991637396</v>
+      </c>
+      <c r="J24" t="n">
+        <v>29</v>
+      </c>
+      <c r="K24" t="n">
+        <v>24.75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0007582790424622805</v>
+      </c>
+      <c r="D25" t="n">
+        <v>26</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.001185168703042303</v>
+      </c>
+      <c r="F25" t="n">
+        <v>22</v>
+      </c>
+      <c r="G25" t="n">
+        <v>6.652102956079542e-05</v>
+      </c>
+      <c r="H25" t="n">
+        <v>31</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1560730357989031</v>
+      </c>
+      <c r="J25" t="n">
+        <v>30</v>
+      </c>
+      <c r="K25" t="n">
+        <v>27.25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0006972640002841054</v>
+      </c>
+      <c r="D26" t="n">
+        <v>32</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0008304877241044079</v>
+      </c>
+      <c r="F26" t="n">
+        <v>38</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0004414328785109611</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1490607909920729</v>
+      </c>
+      <c r="J26" t="n">
+        <v>33</v>
+      </c>
+      <c r="K26" t="n">
+        <v>28.75</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.00122477645199416</v>
+      </c>
+      <c r="D27" t="n">
+        <v>13</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.002270076568888336</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.0006954477944202564</v>
+      </c>
+      <c r="H27" t="n">
+        <v>53</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.141477787344328</v>
+      </c>
+      <c r="J27" t="n">
+        <v>36</v>
+      </c>
+      <c r="K27" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.001224198408668698</v>
+      </c>
+      <c r="D28" t="n">
+        <v>14</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.001121648991920873</v>
+      </c>
+      <c r="F28" t="n">
+        <v>24</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.081325731242312e-05</v>
+      </c>
+      <c r="H28" t="n">
+        <v>35</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.05251498539844945</v>
+      </c>
+      <c r="J28" t="n">
+        <v>46</v>
+      </c>
+      <c r="K28" t="n">
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6.698978141619845e-05</v>
+      </c>
+      <c r="D29" t="n">
+        <v>50</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.00127938416420528</v>
+      </c>
+      <c r="F29" t="n">
+        <v>19</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3.689122070235085e-05</v>
+      </c>
+      <c r="H29" t="n">
+        <v>33</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1870865751752169</v>
+      </c>
+      <c r="J29" t="n">
+        <v>17</v>
+      </c>
+      <c r="K29" t="n">
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>9.30899383212723e-05</v>
+      </c>
+      <c r="D30" t="n">
+        <v>48</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.00127044775560163</v>
+      </c>
+      <c r="F30" t="n">
+        <v>20</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.107875387381442e-05</v>
+      </c>
+      <c r="H30" t="n">
+        <v>34</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1863432137872707</v>
+      </c>
+      <c r="J30" t="n">
+        <v>19</v>
+      </c>
+      <c r="K30" t="n">
+        <v>30.25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0007240075033226553</v>
+      </c>
+      <c r="D31" t="n">
+        <v>29</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0009655402662797008</v>
+      </c>
+      <c r="F31" t="n">
+        <v>29</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0001806327722099321</v>
+      </c>
+      <c r="H31" t="n">
+        <v>22</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.08944651907265522</v>
+      </c>
+      <c r="J31" t="n">
+        <v>44</v>
+      </c>
+      <c r="K31" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0006390868063306954</v>
+      </c>
+      <c r="D32" t="n">
+        <v>35</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0009912261557726723</v>
+      </c>
+      <c r="F32" t="n">
+        <v>25</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0002101848453808008</v>
+      </c>
+      <c r="H32" t="n">
+        <v>21</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09443301208759403</v>
+      </c>
+      <c r="J32" t="n">
+        <v>43</v>
+      </c>
+      <c r="K32" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0007280861185023606</v>
+      </c>
+      <c r="D33" t="n">
+        <v>28</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0009416747201330058</v>
+      </c>
+      <c r="F33" t="n">
+        <v>31</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.811809673091247e-05</v>
+      </c>
+      <c r="H33" t="n">
+        <v>38</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.1591691352498623</v>
+      </c>
+      <c r="J33" t="n">
+        <v>28</v>
+      </c>
+      <c r="K33" t="n">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9.076134271550499e-05</v>
+      </c>
+      <c r="D34" t="n">
+        <v>49</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.002862490007269064</v>
+      </c>
+      <c r="F34" t="n">
+        <v>13</v>
+      </c>
+      <c r="G34" t="n">
+        <v>5.389562769104738e-05</v>
+      </c>
+      <c r="H34" t="n">
+        <v>32</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1558927385142801</v>
+      </c>
+      <c r="J34" t="n">
+        <v>31</v>
+      </c>
+      <c r="K34" t="n">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0008132295048725146</v>
+      </c>
+      <c r="D35" t="n">
+        <v>21</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.000933487076112565</v>
+      </c>
+      <c r="F35" t="n">
+        <v>32</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0.0002243916088854991</v>
+      </c>
+      <c r="H35" t="n">
+        <v>52</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1702745362477729</v>
+      </c>
+      <c r="J35" t="n">
+        <v>24</v>
+      </c>
+      <c r="K35" t="n">
+        <v>32.25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0005035863633431989</v>
+      </c>
+      <c r="D36" t="n">
+        <v>39</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.001172804625687977</v>
+      </c>
+      <c r="F36" t="n">
+        <v>23</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.0001476851197737328</v>
+      </c>
+      <c r="H36" t="n">
+        <v>50</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1721664355155985</v>
+      </c>
+      <c r="J36" t="n">
+        <v>23</v>
+      </c>
+      <c r="K36" t="n">
+        <v>33.75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0006584575605353089</v>
+      </c>
+      <c r="D37" t="n">
+        <v>33</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.000888392709842498</v>
+      </c>
+      <c r="F37" t="n">
+        <v>34</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.0001031818641623161</v>
+      </c>
+      <c r="H37" t="n">
+        <v>47</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.165977979793769</v>
+      </c>
+      <c r="J37" t="n">
+        <v>25</v>
+      </c>
+      <c r="K37" t="n">
+        <v>34.75</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0006455006670693641</v>
+      </c>
+      <c r="D38" t="n">
+        <v>34</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0007525057352409966</v>
+      </c>
+      <c r="F38" t="n">
+        <v>40</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-2.52807225967766e-06</v>
+      </c>
+      <c r="H38" t="n">
+        <v>39</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.160548726236875</v>
+      </c>
+      <c r="J38" t="n">
+        <v>27</v>
+      </c>
+      <c r="K38" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.000616693724746763</v>
+      </c>
+      <c r="D39" t="n">
+        <v>37</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0007678261886064273</v>
+      </c>
+      <c r="F39" t="n">
+        <v>39</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.0001614084051627662</v>
+      </c>
+      <c r="H39" t="n">
+        <v>51</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1943039087441263</v>
+      </c>
+      <c r="J39" t="n">
+        <v>14</v>
+      </c>
+      <c r="K39" t="n">
+        <v>35.25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0008855942243954736</v>
+      </c>
+      <c r="D40" t="n">
+        <v>20</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0008648024995998908</v>
+      </c>
+      <c r="F40" t="n">
+        <v>36</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.0001079637018489787</v>
+      </c>
+      <c r="H40" t="n">
+        <v>48</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.128782645996957</v>
+      </c>
+      <c r="J40" t="n">
+        <v>38</v>
+      </c>
+      <c r="K40" t="n">
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.000472529583246803</v>
+      </c>
+      <c r="D41" t="n">
+        <v>43</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0006595950789886791</v>
+      </c>
+      <c r="F41" t="n">
+        <v>42</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.425820673009893e-05</v>
+      </c>
+      <c r="H41" t="n">
+        <v>36</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1492943793711148</v>
+      </c>
+      <c r="J41" t="n">
+        <v>32</v>
+      </c>
+      <c r="K41" t="n">
+        <v>38.25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0005468799884780956</v>
+      </c>
+      <c r="D42" t="n">
+        <v>38</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0005708097496547163</v>
+      </c>
+      <c r="F42" t="n">
+        <v>43</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8.38183885920496e-05</v>
+      </c>
+      <c r="H42" t="n">
+        <v>28</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.07311181718503645</v>
+      </c>
+      <c r="J42" t="n">
+        <v>45</v>
+      </c>
+      <c r="K42" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0007162777074455035</v>
+      </c>
+      <c r="D43" t="n">
+        <v>30</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0007506174608899811</v>
+      </c>
+      <c r="F43" t="n">
+        <v>41</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-1.842118415588123e-05</v>
+      </c>
+      <c r="H43" t="n">
+        <v>43</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1183116735148451</v>
+      </c>
+      <c r="J43" t="n">
+        <v>40</v>
+      </c>
+      <c r="K43" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0004809459134601496</v>
+      </c>
+      <c r="D44" t="n">
+        <v>42</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0004779629780192875</v>
+      </c>
+      <c r="F44" t="n">
+        <v>46</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.0001096498824923131</v>
+      </c>
+      <c r="H44" t="n">
+        <v>26</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.09670591672826001</v>
+      </c>
+      <c r="J44" t="n">
+        <v>42</v>
+      </c>
+      <c r="K44" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0004924684336355406</v>
+      </c>
+      <c r="D45" t="n">
+        <v>40</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0009265011957629304</v>
+      </c>
+      <c r="F45" t="n">
+        <v>33</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-6.170482251288689e-05</v>
+      </c>
+      <c r="H45" t="n">
+        <v>45</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.1230074443286315</v>
+      </c>
+      <c r="J45" t="n">
+        <v>39</v>
+      </c>
+      <c r="K45" t="n">
+        <v>39.25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0003904569279833252</v>
+      </c>
+      <c r="D46" t="n">
+        <v>44</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.000420697237944519</v>
+      </c>
+      <c r="F46" t="n">
+        <v>50</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0001204278557299321</v>
+      </c>
+      <c r="H46" t="n">
+        <v>25</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.09725371808717842</v>
+      </c>
+      <c r="J46" t="n">
+        <v>41</v>
+      </c>
+      <c r="K46" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0002457714656790424</v>
+      </c>
+      <c r="D47" t="n">
+        <v>45</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0004852459499602878</v>
+      </c>
+      <c r="F47" t="n">
+        <v>45</v>
+      </c>
+      <c r="G47" t="n">
+        <v>6.790068628048651e-05</v>
+      </c>
+      <c r="H47" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.008242740809141669</v>
+      </c>
+      <c r="J47" t="n">
+        <v>49</v>
+      </c>
+      <c r="K47" t="n">
+        <v>42.25</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0006351413567515426</v>
+      </c>
+      <c r="D48" t="n">
+        <v>36</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.000438946854662599</v>
+      </c>
+      <c r="F48" t="n">
+        <v>48</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.000122722619602722</v>
+      </c>
+      <c r="H48" t="n">
+        <v>49</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.1326389331697615</v>
+      </c>
+      <c r="J48" t="n">
+        <v>37</v>
+      </c>
+      <c r="K48" t="n">
+        <v>42.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0004855531946411347</v>
+      </c>
+      <c r="D49" t="n">
+        <v>41</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0003700164525165009</v>
+      </c>
+      <c r="F49" t="n">
+        <v>51</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7.847920351825577e-05</v>
+      </c>
+      <c r="H49" t="n">
+        <v>29</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>52</v>
+      </c>
+      <c r="K49" t="n">
+        <v>43.25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0001535210752696423</v>
+      </c>
+      <c r="D50" t="n">
+        <v>46</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.000476872713969579</v>
+      </c>
+      <c r="F50" t="n">
+        <v>47</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.84976308591045e-05</v>
+      </c>
+      <c r="H50" t="n">
+        <v>37</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.0400575501465541</v>
+      </c>
+      <c r="J50" t="n">
+        <v>47</v>
+      </c>
+      <c r="K50" t="n">
+        <v>44.25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0001188637430725328</v>
+      </c>
+      <c r="D51" t="n">
+        <v>47</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.0004301595968848989</v>
+      </c>
+      <c r="F51" t="n">
+        <v>49</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-7.455357771535276e-06</v>
+      </c>
+      <c r="H51" t="n">
+        <v>41</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.004971275335964087</v>
+      </c>
+      <c r="J51" t="n">
+        <v>50</v>
+      </c>
+      <c r="K51" t="n">
+        <v>46.75</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5.268053962815199e-05</v>
+      </c>
+      <c r="D52" t="n">
+        <v>51</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.0005316944652482683</v>
+      </c>
+      <c r="F52" t="n">
+        <v>44</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-4.629870047615503e-05</v>
+      </c>
+      <c r="H52" t="n">
+        <v>44</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.02685289281413383</v>
+      </c>
+      <c r="J52" t="n">
+        <v>48</v>
+      </c>
+      <c r="K52" t="n">
+        <v>46.75</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>8.533205717533462e-06</v>
+      </c>
+      <c r="D53" t="n">
+        <v>53</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0001278686581038072</v>
+      </c>
+      <c r="F53" t="n">
+        <v>53</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-4.185863186412231e-06</v>
+      </c>
+      <c r="H53" t="n">
+        <v>40</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.0007573068389503668</v>
+      </c>
+      <c r="J53" t="n">
+        <v>51</v>
+      </c>
+      <c r="K53" t="n">
+        <v>49.25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>5.759605181805941e-05</v>
-      </c>
-      <c r="D24" t="n">
-        <v>23</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.0001186360407289184</v>
-      </c>
-      <c r="F24" t="n">
-        <v>23</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-2.920791253500088e-05</v>
-      </c>
-      <c r="H24" t="n">
-        <v>20</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="C54" t="n">
+        <v>2.750403793454735e-05</v>
+      </c>
+      <c r="D54" t="n">
+        <v>52</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0001939323378855499</v>
+      </c>
+      <c r="F54" t="n">
+        <v>52</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-8.474531482294268e-06</v>
+      </c>
+      <c r="H54" t="n">
+        <v>42</v>
+      </c>
+      <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>22</v>
-      </c>
-      <c r="K24" t="n">
-        <v>22</v>
+      <c r="J54" t="n">
+        <v>52</v>
+      </c>
+      <c r="K54" t="n">
+        <v>49.5</v>
       </c>
     </row>
   </sheetData>
@@ -1423,25 +2533,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7062474833747497</v>
+        <v>0.6845825246565658</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6362195522648638</v>
+        <v>0.5382493457024158</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.896995760783203</v>
+        <v>1.716374809820653</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.364295226489566</v>
+        <v>1.46080402211227</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -1460,31 +2570,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.08246880628740741</v>
+        <v>0.07229710297930352</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09988749815210433</v>
+        <v>0.08544705036925032</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09498283663706635</v>
+        <v>0.09580546699064142</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8289843043962586</v>
+        <v>0.950238284056983</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1497,31 +2607,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07128262755739898</v>
+        <v>0.06542633112881102</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07705544123577049</v>
+        <v>0.0733571523048489</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06846314211187576</v>
+        <v>0.05403795099861045</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8493562573969222</v>
+        <v>0.9544387207107241</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
@@ -1534,31 +2644,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04903500602640339</v>
+        <v>0.04943422175665614</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08430304018553582</v>
+        <v>0.07674211600304734</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01730137250248034</v>
+        <v>0.02481883644397202</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7606943922861409</v>
+        <v>0.7752739268555842</v>
       </c>
       <c r="J5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="6">
@@ -1567,32 +2677,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.004626324919916361</v>
+        <v>0.03095962366193929</v>
       </c>
       <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0206178134549151</v>
+      </c>
+      <c r="F6" t="n">
         <v>7</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.05824420674616871</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
+        <v>0.02327847696583166</v>
+      </c>
+      <c r="H6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.001262949775852151</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7</v>
-      </c>
       <c r="I6" t="n">
-        <v>1.096015046168342</v>
+        <v>1.108252928577687</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>5.25</v>
@@ -1604,35 +2714,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04459958238824484</v>
+        <v>0.01372099602664899</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005993456693266628</v>
+        <v>0.09700977603986639</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.00781935454004935</v>
+      </c>
+      <c r="H7" t="n">
         <v>7</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.01518133428992629</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
       <c r="I7" t="n">
-        <v>0.6364046570365809</v>
+        <v>0.4582047093013486</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
@@ -1641,35 +2751,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01900451052351277</v>
+        <v>0.001710597127719114</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01378208735510999</v>
+        <v>0.03299938050792029</v>
       </c>
       <c r="F8" t="n">
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009939008654648441</v>
+        <v>0.000480967553369394</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2327342654583391</v>
+        <v>1.241415499160037</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>6.25</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="9">
@@ -1678,35 +2788,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.001871315493037013</v>
+        <v>0.04900116966437267</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002703338354009314</v>
+        <v>0.006282901775732765</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0004925752331383371</v>
+        <v>0.0222445090788812</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2096521009145822</v>
+        <v>0.691115068428279</v>
       </c>
       <c r="J9" t="n">
         <v>8</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
@@ -1715,35 +2825,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001559013620837175</v>
+        <v>0.001510450875415741</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00430646129333622</v>
+        <v>0.008577984193002682</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003129693806159795</v>
+        <v>0.0005094488461650393</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1930540242407095</v>
+        <v>0.8557199798313491</v>
       </c>
       <c r="J10" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" t="n">
         <v>9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>11.25</v>
       </c>
     </row>
     <row r="11">
@@ -1752,35 +2862,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001553307575391961</v>
+        <v>0.002774283169211131</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001729292291145796</v>
+        <v>0.006850580205395447</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003834401666479636</v>
+        <v>0.0005062922773447998</v>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1001185059481942</v>
+        <v>0.6723410535432368</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
-        <v>12.5</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="12">
@@ -1789,35 +2899,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003691020199628685</v>
+        <v>0.001127500295513923</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003808319631496802</v>
+        <v>0.004204229016941893</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0005837023647143225</v>
+        <v>0.0002686653235798641</v>
       </c>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I12" t="n">
-        <v>0.09389834165287603</v>
+        <v>0.3376288728348107</v>
       </c>
       <c r="J12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>12.75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -1826,35 +2936,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001458861271158632</v>
+        <v>0.001989528458822621</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.001627135550989605</v>
+        <v>0.01061077153102466</v>
       </c>
       <c r="F13" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0004304776373687647</v>
+      </c>
+      <c r="H13" t="n">
         <v>13</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.0007451898772962596</v>
-      </c>
-      <c r="H13" t="n">
-        <v>11</v>
-      </c>
       <c r="I13" t="n">
-        <v>0.09686951623215956</v>
+        <v>0.1434364390812606</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="K13" t="n">
-        <v>12.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="14">
@@ -1863,35 +2973,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00155754237862303</v>
+        <v>0.0007892185650921092</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001241403155364813</v>
+        <v>0.001317236861904575</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0008623729204845998</v>
+        <v>0.0002300031859155394</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07623042591435913</v>
+        <v>0.2876059388042056</v>
       </c>
       <c r="J14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -1900,35 +3010,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001940536037222691</v>
+        <v>0.001671802649962494</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001076021648895751</v>
+        <v>0.001301859257282997</v>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0002548472917035527</v>
+        <v>0.0004260038654013032</v>
       </c>
       <c r="H15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>0.07762246528209449</v>
+        <v>0.1476834725725422</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K15" t="n">
-        <v>13.75</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="16">
@@ -1937,35 +3047,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001404225682017941</v>
+        <v>0.0007484733299693599</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001101670676905276</v>
+        <v>0.00225963088193102</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0009103498877840787</v>
+        <v>0.0001314299664285756</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.06250486034620684</v>
+        <v>0.2904242566689663</v>
       </c>
       <c r="J16" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="17">
@@ -1974,35 +3084,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001790339871881961</v>
+        <v>0.0009911985965783464</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001054235308444598</v>
+        <v>0.001252252663216556</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0008934843093977074</v>
+        <v>0.0001395679118505244</v>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I17" t="n">
-        <v>0.04799445060064622</v>
+        <v>0.1813992530194883</v>
       </c>
       <c r="J17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>14.75</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="18">
@@ -2011,35 +3121,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001804553066443183</v>
+        <v>0.0009669290773591936</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>0.001934451077542527</v>
+        <v>0.0009551664113118747</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.001037664772678126</v>
+        <v>0.0002866632852076778</v>
       </c>
       <c r="H18" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0625206972171175</v>
+        <v>0.1830152428100216</v>
       </c>
       <c r="J18" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>15.25</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="19">
@@ -2048,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001151076564402788</v>
+        <v>0.0007132990845621818</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000616267317932914</v>
+        <v>0.0009767724073988632</v>
       </c>
       <c r="F19" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>-5.919866859200873e-05</v>
+        <v>0.00030907281911563</v>
       </c>
       <c r="H19" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>0.06992645175208789</v>
+        <v>0.1898896484834935</v>
       </c>
       <c r="J19" t="n">
         <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -2085,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001018483715986682</v>
+        <v>0.0009472842970054597</v>
       </c>
       <c r="D20" t="n">
         <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.001012632241617861</v>
+        <v>0.0008788756963891966</v>
       </c>
       <c r="F20" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003831946832179245</v>
+        <v>0.0003334092436082625</v>
       </c>
       <c r="H20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.1852204622860074</v>
       </c>
       <c r="J20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>18.5</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="21">
@@ -2122,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.532889393750695e-05</v>
+        <v>0.0007956209360197645</v>
       </c>
       <c r="D21" t="n">
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001131826872553171</v>
+        <v>0.0009749774851976207</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.115942098724899e-05</v>
+        <v>0.0001024960144341058</v>
       </c>
       <c r="H21" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01051214548129864</v>
+        <v>0.1897455725824511</v>
       </c>
       <c r="J21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K21" t="n">
-        <v>19.25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2164,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2194,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.7062474833747497</v>
+        <v>0.6845825246565658</v>
       </c>
     </row>
     <row r="3">
@@ -2207,7 +3317,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.08246880628740741</v>
+        <v>0.07229710297930352</v>
       </c>
     </row>
     <row r="4">
@@ -2220,7 +3330,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07128262755739898</v>
+        <v>0.06542633112881102</v>
       </c>
     </row>
     <row r="5">
@@ -2233,7 +3343,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04903500602640339</v>
+        <v>0.04943422175665614</v>
       </c>
     </row>
     <row r="6">
@@ -2246,7 +3356,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04459958238824484</v>
+        <v>0.04900116966437267</v>
       </c>
     </row>
     <row r="7">
@@ -2255,11 +3365,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01900451052351277</v>
+        <v>0.03095962366193929</v>
       </c>
     </row>
     <row r="8">
@@ -2268,11 +3378,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.004626324919916361</v>
+        <v>0.01372099602664899</v>
       </c>
     </row>
     <row r="9">
@@ -2281,11 +3391,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003691020199628685</v>
+        <v>0.002774283169211131</v>
       </c>
     </row>
     <row r="10">
@@ -2294,11 +3404,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001940536037222691</v>
+        <v>0.001989528458822621</v>
       </c>
     </row>
     <row r="11">
@@ -2307,11 +3417,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001871315493037013</v>
+        <v>0.001710597127719114</v>
       </c>
     </row>
     <row r="12">
@@ -2320,11 +3430,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001804553066443183</v>
+        <v>0.001671802649962494</v>
       </c>
     </row>
     <row r="13">
@@ -2333,11 +3443,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001790339871881961</v>
+        <v>0.001510450875415741</v>
       </c>
     </row>
     <row r="14">
@@ -2346,11 +3456,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001559013620837175</v>
+        <v>0.00122477645199416</v>
       </c>
     </row>
     <row r="15">
@@ -2359,11 +3469,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.00155754237862303</v>
+        <v>0.001224198408668698</v>
       </c>
     </row>
     <row r="16">
@@ -2372,11 +3482,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001553307575391961</v>
+        <v>0.001127500295513923</v>
       </c>
     </row>
     <row r="17">
@@ -2385,11 +3495,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001458861271158632</v>
+        <v>0.001093656776562284</v>
       </c>
     </row>
     <row r="18">
@@ -2398,11 +3508,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001404225682017941</v>
+        <v>0.0009911985965783464</v>
       </c>
     </row>
     <row r="19">
@@ -2411,11 +3521,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001151076564402788</v>
+        <v>0.0009669290773591936</v>
       </c>
     </row>
     <row r="20">
@@ -2424,11 +3534,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001018483715986682</v>
+        <v>0.0009472842970054597</v>
       </c>
     </row>
     <row r="21">
@@ -2437,11 +3547,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.000996670607305688</v>
+        <v>0.0008855942243954736</v>
       </c>
     </row>
     <row r="22">
@@ -2450,11 +3560,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0007957878926734792</v>
+        <v>0.0008132295048725146</v>
       </c>
     </row>
     <row r="23">
@@ -2463,11 +3573,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.532889393750695e-05</v>
+        <v>0.0007956209360197645</v>
       </c>
     </row>
     <row r="24">
@@ -2476,11 +3586,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0007892185650921092</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0007833738412022525</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0007680844327823844</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0007582790424622805</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0007484733299693599</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0007280861185023606</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0007240075033226553</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0007162777074455035</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0007132990845621818</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0006972640002841054</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0006584575605353089</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0006455006670693641</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0006390868063306954</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0006351413567515426</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.000616693724746763</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0005468799884780956</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0005035863633431989</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0004924684336355406</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0004855531946411347</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0004809459134601496</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.000472529583246803</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0003904569279833252</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0002457714656790424</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0001535210752696423</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0001188637430725328</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>9.30899383212723e-05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>9.076134271550499e-05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>6.698978141619845e-05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>5.268053962815199e-05</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>5.759605181805941e-05</v>
+      <c r="C53" t="n">
+        <v>2.750403793454735e-05</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>8.533205717533462e-06</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6362195522648638</v>
+        <v>0.5382493457024158</v>
       </c>
     </row>
     <row r="3">
@@ -2533,11 +4033,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09988749815210433</v>
+        <v>0.09700977603986639</v>
       </c>
     </row>
     <row r="4">
@@ -2546,11 +4046,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08430304018553582</v>
+        <v>0.08544705036925032</v>
       </c>
     </row>
     <row r="5">
@@ -2559,11 +4059,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07705544123577049</v>
+        <v>0.07674211600304734</v>
       </c>
     </row>
     <row r="6">
@@ -2572,11 +4072,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05824420674616871</v>
+        <v>0.0733571523048489</v>
       </c>
     </row>
     <row r="7">
@@ -2585,11 +4085,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01378208735510999</v>
+        <v>0.03299938050792029</v>
       </c>
     </row>
     <row r="8">
@@ -2598,11 +4098,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005993456693266628</v>
+        <v>0.0206178134549151</v>
       </c>
     </row>
     <row r="9">
@@ -2611,11 +4111,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.00430646129333622</v>
+        <v>0.01061077153102466</v>
       </c>
     </row>
     <row r="10">
@@ -2624,11 +4124,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003808319631496802</v>
+        <v>0.008577984193002682</v>
       </c>
     </row>
     <row r="11">
@@ -2637,11 +4137,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002703338354009314</v>
+        <v>0.006850580205395447</v>
       </c>
     </row>
     <row r="12">
@@ -2650,11 +4150,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001934451077542527</v>
+        <v>0.006282901775732765</v>
       </c>
     </row>
     <row r="13">
@@ -2663,11 +4163,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001729292291145796</v>
+        <v>0.004204229016941893</v>
       </c>
     </row>
     <row r="14">
@@ -2676,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001627135550989605</v>
+        <v>0.002862490007269064</v>
       </c>
     </row>
     <row r="15">
@@ -2689,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001241403155364813</v>
+        <v>0.002270076568888336</v>
       </c>
     </row>
     <row r="16">
@@ -2702,11 +4202,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001131826872553171</v>
+        <v>0.00225963088193102</v>
       </c>
     </row>
     <row r="17">
@@ -2715,11 +4215,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001101670676905276</v>
+        <v>0.001364844683579517</v>
       </c>
     </row>
     <row r="18">
@@ -2728,11 +4228,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001076021648895751</v>
+        <v>0.001317236861904575</v>
       </c>
     </row>
     <row r="19">
@@ -2741,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001054235308444598</v>
+        <v>0.001301859257282997</v>
       </c>
     </row>
     <row r="20">
@@ -2754,11 +4254,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001012632241617861</v>
+        <v>0.00127938416420528</v>
       </c>
     </row>
     <row r="21">
@@ -2767,11 +4267,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.000616267317932914</v>
+        <v>0.00127044775560163</v>
       </c>
     </row>
     <row r="22">
@@ -2780,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0005552439466838009</v>
+        <v>0.001252252663216556</v>
       </c>
     </row>
     <row r="23">
@@ -2793,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004977819595329388</v>
+        <v>0.001185168703042303</v>
       </c>
     </row>
     <row r="24">
@@ -2806,11 +4306,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.001172804625687977</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.001121648991920873</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0009912261557726723</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0009767724073988632</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0009749774851976207</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0009664663431288174</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0009655402662797008</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0009551664113118747</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0009416747201330058</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.000933487076112565</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0009265011957629304</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.000888392709842498</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.0008788756963891966</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.0008648024995998908</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0008439315814980868</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.0008304877241044079</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.0007678261886064273</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0007525057352409966</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0007506174608899811</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0006595950789886791</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0005708097496547163</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0005316944652482683</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0004852459499602878</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0004779629780192875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.000476872713969579</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.000438946854662599</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0004301595968848989</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.000420697237944519</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0003700164525165009</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0.0001186360407289184</v>
+      <c r="C53" t="n">
+        <v>0.0001939323378855499</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.0001278686581038072</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +4714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2859,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.896995760783203</v>
+        <v>1.716374809820653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1496219257611114</v>
+        <v>0.07856259350207398</v>
       </c>
     </row>
     <row r="3">
@@ -2875,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09498283663706635</v>
+        <v>0.09580546699064142</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003361086306791278</v>
+        <v>0.008347833538365898</v>
       </c>
     </row>
     <row r="4">
@@ -2891,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06846314211187576</v>
+        <v>0.05403795099861045</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005664676002554827</v>
+        <v>0.006091575404357136</v>
       </c>
     </row>
     <row r="5">
@@ -2907,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01730137250248034</v>
+        <v>0.02481883644397202</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002302644845976127</v>
+        <v>0.002969792383778246</v>
       </c>
     </row>
     <row r="6">
@@ -2919,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01518133428992629</v>
+        <v>0.02327847696583166</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001820976828454975</v>
+        <v>0.003583200364413956</v>
       </c>
     </row>
     <row r="7">
@@ -2935,14 +4825,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.009939008654648441</v>
+        <v>0.0222445090788812</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002838958143354105</v>
+        <v>0.002647902235471919</v>
       </c>
     </row>
     <row r="8">
@@ -2951,14 +4841,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001262949775852151</v>
+        <v>0.00781935454004935</v>
       </c>
       <c r="D8" t="n">
-        <v>8.642741790681753e-05</v>
+        <v>0.002220243453168809</v>
       </c>
     </row>
     <row r="9">
@@ -2967,14 +4857,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0009103498877840787</v>
+        <v>0.0005290502901014738</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0003056095763762634</v>
+        <v>0.0002593682143750633</v>
       </c>
     </row>
     <row r="10">
@@ -2983,14 +4873,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0008934843093977074</v>
+        <v>0.0005094488461650393</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0002690928880676522</v>
+        <v>0.0001778806428961615</v>
       </c>
     </row>
     <row r="11">
@@ -2999,14 +4889,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0008623729204845998</v>
+        <v>0.0005062922773447998</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000215398262311075</v>
+        <v>0.0005642574761980698</v>
       </c>
     </row>
     <row r="12">
@@ -3015,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0007451898772962596</v>
+        <v>0.000480967553369394</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0003314616832248592</v>
+        <v>4.126683748901022e-05</v>
       </c>
     </row>
     <row r="13">
@@ -3031,14 +4921,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0004925752331383371</v>
+        <v>0.0004414328785109611</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0002360808677985225</v>
+        <v>0.0001053503090220816</v>
       </c>
     </row>
     <row r="14">
@@ -3047,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0003834401666479636</v>
+        <v>0.0004304776373687647</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001385475280464926</v>
+        <v>0.0003984310551087147</v>
       </c>
     </row>
     <row r="15">
@@ -3063,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0003831946832179245</v>
+        <v>0.0004260038654013032</v>
       </c>
       <c r="D15" t="n">
-        <v>5.473264948015688e-05</v>
+        <v>0.0004079183170933317</v>
       </c>
     </row>
     <row r="16">
@@ -3079,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0003129693806159795</v>
+        <v>0.0003334092436082625</v>
       </c>
       <c r="D16" t="n">
-        <v>9.713021731607376e-05</v>
+        <v>0.0001805462777049507</v>
       </c>
     </row>
     <row r="17">
@@ -3095,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0002548472917035527</v>
+        <v>0.00030907281911563</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0002269533484434109</v>
+        <v>0.0001160218681415015</v>
       </c>
     </row>
     <row r="18">
@@ -3111,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0001953221747326817</v>
+        <v>0.0002866632852076778</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001877135981960067</v>
+        <v>0.0001459550048228664</v>
       </c>
     </row>
     <row r="19">
@@ -3127,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.366449805519369e-05</v>
+        <v>0.0002686653235798641</v>
       </c>
       <c r="D19" t="n">
-        <v>6.97768668836411e-05</v>
+        <v>0.0001089246761980544</v>
       </c>
     </row>
     <row r="20">
@@ -3143,14 +5033,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-2.115942098724899e-05</v>
+        <v>0.0002300031859155394</v>
       </c>
       <c r="D20" t="n">
-        <v>6.069712988346158e-06</v>
+        <v>0.0001504050734485318</v>
       </c>
     </row>
     <row r="21">
@@ -3159,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-2.920791253500088e-05</v>
+        <v>0.0002139003216387048</v>
       </c>
       <c r="D21" t="n">
-        <v>2.242009929044458e-05</v>
+        <v>0.0002553776156497789</v>
       </c>
     </row>
     <row r="22">
@@ -3175,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-5.919866859200873e-05</v>
+        <v>0.0002101848453808008</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0003213964294287149</v>
+        <v>0.0001516477572168802</v>
       </c>
     </row>
     <row r="23">
@@ -3191,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.0005837023647143225</v>
+        <v>0.0001806327722099321</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000639010679765363</v>
+        <v>0.0001212977104113356</v>
       </c>
     </row>
     <row r="24">
@@ -3207,14 +5097,494 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.0001395679118505244</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0001367576450877502</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0001314299664285756</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0001488449691015427</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0001204278557299321</v>
+      </c>
+      <c r="D26" t="n">
+        <v>8.644715757184389e-05</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0001096498824923131</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3.887620502893994e-05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0001024960144341058</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0001360699212864369</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8.38183885920496e-05</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7.083324264083496e-05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7.847920351825577e-05</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6.27045661236686e-05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6.790068628048651e-05</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4.713395237781986e-05</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6.652102956079542e-05</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0001404280489174079</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5.389562769104738e-05</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.681769902342663e-05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>report_date_year</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3.689122070235085e-05</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2.071088956790754e-05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>report_year</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3.107875387381442e-05</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.746538395250021e-05</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3.081325731242312e-05</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0003232461847371366</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2.425820673009893e-05</v>
+      </c>
+      <c r="D37" t="n">
+        <v>5.521058900033662e-05</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1.84976308591045e-05</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.820730905639289e-05</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1.811809673091247e-05</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0001114114459944966</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>-2.52807225967766e-06</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.0001211611265717025</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-4.185863186412231e-06</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2.178328136355172e-06</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-7.455357771535276e-06</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.68455631717178e-05</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-8.474531482294268e-06</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3.331623040076253e-05</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-1.842118415588123e-05</v>
+      </c>
+      <c r="D44" t="n">
+        <v>6.219884701677125e-05</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-4.629870047615503e-05</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.139044055277633e-05</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-6.170482251288689e-05</v>
+      </c>
+      <c r="D46" t="n">
+        <v>7.684996192484445e-05</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.0001018963849096166</v>
+      </c>
+      <c r="D47" t="n">
+        <v>7.992522008522712e-05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.0001031818641623161</v>
+      </c>
+      <c r="D48" t="n">
+        <v>7.433215004380154e-05</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.0001079637018489787</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.0001474908991865691</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.000122722619602722</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.0001727897020824825</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.0001476851197737328</v>
+      </c>
+      <c r="D51" t="n">
+        <v>7.270388261475437e-05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.0001614084051627662</v>
+      </c>
+      <c r="D52" t="n">
+        <v>7.218516830803868e-05</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.0002243916088854991</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.000140330381700117</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>carbonated_pH</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>-0.001037664772678126</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0002266503947679808</v>
+      <c r="C54" t="n">
+        <v>-0.0006954477944202564</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.0003123775988620816</v>
       </c>
     </row>
   </sheetData>
@@ -3228,7 +5598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3258,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.364295226489566</v>
+        <v>1.46080402211227</v>
       </c>
     </row>
     <row r="3">
@@ -3271,7 +5641,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.096015046168342</v>
+        <v>1.241415499160037</v>
       </c>
     </row>
     <row r="4">
@@ -3280,11 +5650,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8493562573969222</v>
+        <v>1.108252928577687</v>
       </c>
     </row>
     <row r="5">
@@ -3293,11 +5663,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8289843043962586</v>
+        <v>0.9544387207107241</v>
       </c>
     </row>
     <row r="6">
@@ -3306,11 +5676,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.7606943922861409</v>
+        <v>0.950238284056983</v>
       </c>
     </row>
     <row r="7">
@@ -3319,11 +5689,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6364046570365809</v>
+        <v>0.8557199798313491</v>
       </c>
     </row>
     <row r="8">
@@ -3332,11 +5702,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.2327342654583391</v>
+        <v>0.7752739268555842</v>
       </c>
     </row>
     <row r="9">
@@ -3345,11 +5715,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.2096521009145822</v>
+        <v>0.691115068428279</v>
       </c>
     </row>
     <row r="10">
@@ -3358,11 +5728,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1930540242407095</v>
+        <v>0.6723410535432368</v>
       </c>
     </row>
     <row r="11">
@@ -3371,11 +5741,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1001185059481942</v>
+        <v>0.4582047093013486</v>
       </c>
     </row>
     <row r="12">
@@ -3384,11 +5754,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.09686951623215956</v>
+        <v>0.3376288728348107</v>
       </c>
     </row>
     <row r="13">
@@ -3397,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.09389834165287603</v>
+        <v>0.2904242566689663</v>
       </c>
     </row>
     <row r="14">
@@ -3410,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.07762246528209449</v>
+        <v>0.2876059388042056</v>
       </c>
     </row>
     <row r="15">
@@ -3423,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.07623042591435913</v>
+        <v>0.1943039087441263</v>
       </c>
     </row>
     <row r="16">
@@ -3436,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.06992645175208789</v>
+        <v>0.1898896484834935</v>
       </c>
     </row>
     <row r="17">
@@ -3449,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0625206972171175</v>
+        <v>0.1897455725824511</v>
       </c>
     </row>
     <row r="18">
@@ -3462,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.06250486034620684</v>
+        <v>0.1870865751752169</v>
       </c>
     </row>
     <row r="19">
@@ -3475,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.06222176896551357</v>
+        <v>0.1870093359082308</v>
       </c>
     </row>
     <row r="20">
@@ -3488,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.05329504018320641</v>
+        <v>0.1863432137872707</v>
       </c>
     </row>
     <row r="21">
@@ -3501,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.04799445060064622</v>
+        <v>0.1852204622860074</v>
       </c>
     </row>
     <row r="22">
@@ -3514,11 +5884,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01051214548129864</v>
+        <v>0.1830152428100216</v>
       </c>
     </row>
     <row r="23">
@@ -3527,23 +5897,413 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.1813992530194883</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1721664355155985</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1702745362477729</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.165977979793769</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1617144420372227</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.160548726236875</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1591691352498623</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1579236991637396</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1560730357989031</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1558927385142801</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1492943793711148</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1490607909920729</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>white_quality_apparent_color_2</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1476834725725422</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1434364390812606</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.141477787344328</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1326389331697615</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.128782645996957</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.1230074443286315</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.1183116735148451</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.09725371808717842</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.09670591672826001</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.09443301208759403</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.08944651907265522</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>standard_liquor_pH</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C46" t="n">
+        <v>0.07311181718503645</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.05251498539844945</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0400575501465541</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.02685289281413383</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.008242740809141669</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.004971275335964087</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.0007573068389503668</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3595,17 +6355,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 04:46:51 UTC</t>
+          <t>2026-06-11 05:08:00 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_ash.xlsx
+++ b/NN/reports/feature_importance_white_ash.xlsx
@@ -550,7 +550,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09580546699064142</v>
+        <v>0.09580546699064151</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05403795099861045</v>
+        <v>0.05403795099861055</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02481883644397202</v>
+        <v>0.0248188364439721</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02327847696583166</v>
+        <v>0.02327847696583174</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00781935454004935</v>
+        <v>0.00781935454004945</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -735,7 +735,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000480967553369394</v>
+        <v>0.0004809675534131369</v>
       </c>
       <c r="H8" t="n">
         <v>11</v>
@@ -772,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0222445090788812</v>
+        <v>0.02224450907888132</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -809,7 +809,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005094488461650393</v>
+        <v>0.0005094488461651281</v>
       </c>
       <c r="H10" t="n">
         <v>9</v>
@@ -846,7 +846,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0005062922773447998</v>
+        <v>0.0005062922773449108</v>
       </c>
       <c r="H11" t="n">
         <v>10</v>
@@ -883,7 +883,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002686653235798641</v>
+        <v>0.0002686653235799641</v>
       </c>
       <c r="H12" t="n">
         <v>18</v>
@@ -920,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004304776373687647</v>
+        <v>0.0004304776373688979</v>
       </c>
       <c r="H13" t="n">
         <v>13</v>
@@ -957,7 +957,7 @@
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002300031859155394</v>
+        <v>0.0002300031859156282</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -994,7 +994,7 @@
         <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0004260038654013032</v>
+        <v>0.0004260038654014253</v>
       </c>
       <c r="H15" t="n">
         <v>14</v>
@@ -1031,7 +1031,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001314299664285756</v>
+        <v>0.0001314299664286533</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -1068,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001395679118505244</v>
+        <v>0.0001395679118506243</v>
       </c>
       <c r="H17" t="n">
         <v>23</v>
@@ -1105,7 +1105,7 @@
         <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002866632852076778</v>
+        <v>0.0002866632852077999</v>
       </c>
       <c r="H18" t="n">
         <v>17</v>
@@ -1142,7 +1142,7 @@
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00030907281911563</v>
+        <v>0.0003090728191157299</v>
       </c>
       <c r="H19" t="n">
         <v>16</v>
@@ -1179,7 +1179,7 @@
         <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003334092436082625</v>
+        <v>0.0003334092436083847</v>
       </c>
       <c r="H20" t="n">
         <v>15</v>
@@ -1216,7 +1216,7 @@
         <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001024960144341058</v>
+        <v>0.0001024960144342502</v>
       </c>
       <c r="H21" t="n">
         <v>27</v>
@@ -1253,7 +1253,7 @@
         <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0001018963849096166</v>
+        <v>-0.0001018963849095167</v>
       </c>
       <c r="H22" t="n">
         <v>46</v>
@@ -1290,7 +1290,7 @@
         <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0002139003216387048</v>
+        <v>0.0002139003216388047</v>
       </c>
       <c r="H23" t="n">
         <v>20</v>
@@ -1327,7 +1327,7 @@
         <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0005290502901014738</v>
+        <v>0.0005290502901015515</v>
       </c>
       <c r="H24" t="n">
         <v>8</v>
@@ -1364,7 +1364,7 @@
         <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>6.652102956079542e-05</v>
+        <v>6.652102956095085e-05</v>
       </c>
       <c r="H25" t="n">
         <v>31</v>
@@ -1401,7 +1401,7 @@
         <v>38</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0004414328785109611</v>
+        <v>0.0004414328785111166</v>
       </c>
       <c r="H26" t="n">
         <v>12</v>
@@ -1438,7 +1438,7 @@
         <v>14</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0006954477944202564</v>
+        <v>-0.0006954477944201675</v>
       </c>
       <c r="H27" t="n">
         <v>53</v>
@@ -1475,7 +1475,7 @@
         <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>3.081325731242312e-05</v>
+        <v>3.081325731252305e-05</v>
       </c>
       <c r="H28" t="n">
         <v>35</v>
@@ -1512,7 +1512,7 @@
         <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>3.689122070235085e-05</v>
+        <v>3.689122070246187e-05</v>
       </c>
       <c r="H29" t="n">
         <v>33</v>
@@ -1549,7 +1549,7 @@
         <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>3.107875387381442e-05</v>
+        <v>3.107875387389214e-05</v>
       </c>
       <c r="H30" t="n">
         <v>34</v>
@@ -1586,7 +1586,7 @@
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0001806327722099321</v>
+        <v>0.0001806327722100654</v>
       </c>
       <c r="H31" t="n">
         <v>22</v>
@@ -1623,7 +1623,7 @@
         <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0002101848453808008</v>
+        <v>0.0002101848453809341</v>
       </c>
       <c r="H32" t="n">
         <v>21</v>
@@ -1660,7 +1660,7 @@
         <v>31</v>
       </c>
       <c r="G33" t="n">
-        <v>1.811809673091247e-05</v>
+        <v>1.811809673101239e-05</v>
       </c>
       <c r="H33" t="n">
         <v>38</v>
@@ -1697,7 +1697,7 @@
         <v>13</v>
       </c>
       <c r="G34" t="n">
-        <v>5.389562769104738e-05</v>
+        <v>5.389562769119172e-05</v>
       </c>
       <c r="H34" t="n">
         <v>32</v>
@@ -1734,7 +1734,7 @@
         <v>32</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0002243916088854991</v>
+        <v>-0.000224391608885377</v>
       </c>
       <c r="H35" t="n">
         <v>52</v>
@@ -1771,7 +1771,7 @@
         <v>23</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0001476851197737328</v>
+        <v>-0.0001476851197736218</v>
       </c>
       <c r="H36" t="n">
         <v>50</v>
@@ -1808,7 +1808,7 @@
         <v>34</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0001031818641623161</v>
+        <v>-0.0001031818641622384</v>
       </c>
       <c r="H37" t="n">
         <v>47</v>
@@ -1845,7 +1845,7 @@
         <v>40</v>
       </c>
       <c r="G38" t="n">
-        <v>-2.52807225967766e-06</v>
+        <v>-2.528072259555536e-06</v>
       </c>
       <c r="H38" t="n">
         <v>39</v>
@@ -1882,7 +1882,7 @@
         <v>39</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0001614084051627662</v>
+        <v>-0.0001614084051626663</v>
       </c>
       <c r="H39" t="n">
         <v>51</v>
@@ -1919,7 +1919,7 @@
         <v>36</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0001079637018489787</v>
+        <v>-0.0001079637018488566</v>
       </c>
       <c r="H40" t="n">
         <v>48</v>
@@ -1956,7 +1956,7 @@
         <v>42</v>
       </c>
       <c r="G41" t="n">
-        <v>2.425820673009893e-05</v>
+        <v>2.425820673022105e-05</v>
       </c>
       <c r="H41" t="n">
         <v>36</v>
@@ -1993,7 +1993,7 @@
         <v>43</v>
       </c>
       <c r="G42" t="n">
-        <v>8.38183885920496e-05</v>
+        <v>8.381838859216062e-05</v>
       </c>
       <c r="H42" t="n">
         <v>28</v>
@@ -2030,7 +2030,7 @@
         <v>41</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.842118415588123e-05</v>
+        <v>-1.842118415577021e-05</v>
       </c>
       <c r="H43" t="n">
         <v>43</v>
@@ -2067,7 +2067,7 @@
         <v>46</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0001096498824923131</v>
+        <v>0.0001096498824924574</v>
       </c>
       <c r="H44" t="n">
         <v>26</v>
@@ -2104,7 +2104,7 @@
         <v>33</v>
       </c>
       <c r="G45" t="n">
-        <v>-6.170482251288689e-05</v>
+        <v>-6.170482251274256e-05</v>
       </c>
       <c r="H45" t="n">
         <v>45</v>
@@ -2141,7 +2141,7 @@
         <v>50</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0001204278557299321</v>
+        <v>0.000120427855730032</v>
       </c>
       <c r="H46" t="n">
         <v>25</v>
@@ -2178,7 +2178,7 @@
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>6.790068628048651e-05</v>
+        <v>6.790068628058643e-05</v>
       </c>
       <c r="H47" t="n">
         <v>30</v>
@@ -2215,7 +2215,7 @@
         <v>48</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.000122722619602722</v>
+        <v>-0.0001227226196025777</v>
       </c>
       <c r="H48" t="n">
         <v>49</v>
@@ -2252,7 +2252,7 @@
         <v>51</v>
       </c>
       <c r="G49" t="n">
-        <v>7.847920351825577e-05</v>
+        <v>7.84792035183779e-05</v>
       </c>
       <c r="H49" t="n">
         <v>29</v>
@@ -2289,7 +2289,7 @@
         <v>47</v>
       </c>
       <c r="G50" t="n">
-        <v>1.84976308591045e-05</v>
+        <v>1.849763085917111e-05</v>
       </c>
       <c r="H50" t="n">
         <v>37</v>
@@ -2326,7 +2326,7 @@
         <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>-7.455357771535276e-06</v>
+        <v>-7.455357771435355e-06</v>
       </c>
       <c r="H51" t="n">
         <v>41</v>
@@ -2363,7 +2363,7 @@
         <v>44</v>
       </c>
       <c r="G52" t="n">
-        <v>-4.629870047615503e-05</v>
+        <v>-4.629870047606621e-05</v>
       </c>
       <c r="H52" t="n">
         <v>44</v>
@@ -2400,7 +2400,7 @@
         <v>53</v>
       </c>
       <c r="G53" t="n">
-        <v>-4.185863186412231e-06</v>
+        <v>-4.185863186256799e-06</v>
       </c>
       <c r="H53" t="n">
         <v>40</v>
@@ -2437,7 +2437,7 @@
         <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>-8.474531482294268e-06</v>
+        <v>-8.474531482216551e-06</v>
       </c>
       <c r="H54" t="n">
         <v>42</v>
@@ -2582,7 +2582,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09580546699064142</v>
+        <v>0.09580546699064151</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05403795099861045</v>
+        <v>0.05403795099861055</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02481883644397202</v>
+        <v>0.0248188364439721</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02327847696583166</v>
+        <v>0.02327847696583174</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00781935454004935</v>
+        <v>0.00781935454004945</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -2767,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000480967553369394</v>
+        <v>0.0004809675534131369</v>
       </c>
       <c r="H8" t="n">
         <v>11</v>
@@ -2804,7 +2804,7 @@
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0222445090788812</v>
+        <v>0.02224450907888132</v>
       </c>
       <c r="H9" t="n">
         <v>6</v>
@@ -2841,7 +2841,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005094488461650393</v>
+        <v>0.0005094488461651281</v>
       </c>
       <c r="H10" t="n">
         <v>9</v>
@@ -2878,7 +2878,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0005062922773447998</v>
+        <v>0.0005062922773449108</v>
       </c>
       <c r="H11" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002686653235798641</v>
+        <v>0.0002686653235799641</v>
       </c>
       <c r="H12" t="n">
         <v>18</v>
@@ -2952,7 +2952,7 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004304776373687647</v>
+        <v>0.0004304776373688979</v>
       </c>
       <c r="H13" t="n">
         <v>13</v>
@@ -2989,7 +2989,7 @@
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002300031859155394</v>
+        <v>0.0002300031859156282</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -3026,7 +3026,7 @@
         <v>18</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0004260038654013032</v>
+        <v>0.0004260038654014253</v>
       </c>
       <c r="H15" t="n">
         <v>14</v>
@@ -3063,7 +3063,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001314299664285756</v>
+        <v>0.0001314299664286533</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -3100,7 +3100,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001395679118505244</v>
+        <v>0.0001395679118506243</v>
       </c>
       <c r="H17" t="n">
         <v>23</v>
@@ -3137,7 +3137,7 @@
         <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002866632852076778</v>
+        <v>0.0002866632852077999</v>
       </c>
       <c r="H18" t="n">
         <v>17</v>
@@ -3174,7 +3174,7 @@
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00030907281911563</v>
+        <v>0.0003090728191157299</v>
       </c>
       <c r="H19" t="n">
         <v>16</v>
@@ -3211,7 +3211,7 @@
         <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003334092436082625</v>
+        <v>0.0003334092436083847</v>
       </c>
       <c r="H20" t="n">
         <v>15</v>
@@ -3248,7 +3248,7 @@
         <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001024960144341058</v>
+        <v>0.0001024960144342502</v>
       </c>
       <c r="H21" t="n">
         <v>27</v>
@@ -4752,7 +4752,7 @@
         <v>1.716374809820653</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07856259350207398</v>
+        <v>0.0785625935020739</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09580546699064142</v>
+        <v>0.09580546699064151</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008347833538365898</v>
+        <v>0.008347833538365906</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05403795099861045</v>
+        <v>0.05403795099861055</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006091575404357136</v>
+        <v>0.006091575404357176</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.02481883644397202</v>
+        <v>0.0248188364439721</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002969792383778246</v>
+        <v>0.002969792383778232</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02327847696583166</v>
+        <v>0.02327847696583174</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003583200364413956</v>
+        <v>0.003583200364413966</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0222445090788812</v>
+        <v>0.02224450907888132</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002647902235471919</v>
+        <v>0.002647902235471949</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.00781935454004935</v>
+        <v>0.00781935454004945</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002220243453168809</v>
+        <v>0.002220243453168804</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0005290502901014738</v>
+        <v>0.0005290502901015515</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0002593682143750633</v>
+        <v>0.000259368214375018</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0005094488461650393</v>
+        <v>0.0005094488461651281</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001778806428961615</v>
+        <v>0.0001778806428961804</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0005062922773447998</v>
+        <v>0.0005062922773449108</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0005642574761980698</v>
+        <v>0.0005642574761980767</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.000480967553369394</v>
+        <v>0.0004809675534131369</v>
       </c>
       <c r="D12" t="n">
-        <v>4.126683748901022e-05</v>
+        <v>4.126683748916188e-05</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0004414328785109611</v>
+        <v>0.0004414328785111166</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001053503090220816</v>
+        <v>0.0001053503090220675</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0004304776373687647</v>
+        <v>0.0004304776373688979</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0003984310551087147</v>
+        <v>0.0003984310551087081</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0004260038654013032</v>
+        <v>0.0004260038654014253</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0004079183170933317</v>
+        <v>0.0004079183170933347</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0003334092436082625</v>
+        <v>0.0003334092436083847</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001805462777049507</v>
+        <v>0.0001805462777049459</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.00030907281911563</v>
+        <v>0.0003090728191157299</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001160218681415015</v>
+        <v>0.0001160218681415018</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0002866632852076778</v>
+        <v>0.0002866632852077999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001459550048228664</v>
+        <v>0.0001459550048228453</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0002686653235798641</v>
+        <v>0.0002686653235799641</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0001089246761980544</v>
+        <v>0.0001089246761980513</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0002300031859155394</v>
+        <v>0.0002300031859156282</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001504050734485318</v>
+        <v>0.0001504050734485005</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0002139003216387048</v>
+        <v>0.0002139003216388047</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0002553776156497789</v>
+        <v>0.0002553776156497667</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0002101848453808008</v>
+        <v>0.0002101848453809341</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001516477572168802</v>
+        <v>0.0001516477572169163</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0001806327722099321</v>
+        <v>0.0001806327722100654</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001212977104113356</v>
+        <v>0.0001212977104113441</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0001395679118505244</v>
+        <v>0.0001395679118506243</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0001367576450877502</v>
+        <v>0.000136757645087713</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0001314299664285756</v>
+        <v>0.0001314299664286533</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001488449691015427</v>
+        <v>0.000148844969101574</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0001204278557299321</v>
+        <v>0.000120427855730032</v>
       </c>
       <c r="D26" t="n">
-        <v>8.644715757184389e-05</v>
+        <v>8.644715757184805e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0001096498824923131</v>
+        <v>0.0001096498824924574</v>
       </c>
       <c r="D27" t="n">
-        <v>3.887620502893994e-05</v>
+        <v>3.887620502892481e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0001024960144341058</v>
+        <v>0.0001024960144342502</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001360699212864369</v>
+        <v>0.0001360699212864287</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8.38183885920496e-05</v>
+        <v>8.381838859216062e-05</v>
       </c>
       <c r="D29" t="n">
-        <v>7.083324264083496e-05</v>
+        <v>7.083324264084419e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.847920351825577e-05</v>
+        <v>7.84792035183779e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>6.27045661236686e-05</v>
+        <v>6.270456612364253e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.790068628048651e-05</v>
+        <v>6.790068628058643e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>4.713395237781986e-05</v>
+        <v>4.713395237778151e-05</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6.652102956079542e-05</v>
+        <v>6.652102956095085e-05</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001404280489174079</v>
+        <v>0.0001404280489173892</v>
       </c>
     </row>
     <row r="33">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.389562769104738e-05</v>
+        <v>5.389562769119172e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>2.681769902342663e-05</v>
+        <v>2.681769902341101e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.689122070235085e-05</v>
+        <v>3.689122070246187e-05</v>
       </c>
       <c r="D34" t="n">
-        <v>2.071088956790754e-05</v>
+        <v>2.071088956789535e-05</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3.107875387381442e-05</v>
+        <v>3.107875387389214e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>3.746538395250021e-05</v>
+        <v>3.746538395252123e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.081325731242312e-05</v>
+        <v>3.081325731252305e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0003232461847371366</v>
+        <v>0.0003232461847371094</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2.425820673009893e-05</v>
+        <v>2.425820673022105e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>5.521058900033662e-05</v>
+        <v>5.521058900032648e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.84976308591045e-05</v>
+        <v>1.849763085917111e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>3.820730905639289e-05</v>
+        <v>3.820730905638803e-05</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.811809673091247e-05</v>
+        <v>1.811809673101239e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001114114459944966</v>
+        <v>0.0001114114459944835</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-2.52807225967766e-06</v>
+        <v>-2.528072259555536e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001211611265717025</v>
+        <v>0.0001211611265717333</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-4.185863186412231e-06</v>
+        <v>-4.185863186256799e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>2.178328136355172e-06</v>
+        <v>2.178328136386735e-06</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-7.455357771535276e-06</v>
+        <v>-7.455357771435355e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>1.68455631717178e-05</v>
+        <v>1.68455631717143e-05</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-8.474531482294268e-06</v>
+        <v>-8.474531482216551e-06</v>
       </c>
       <c r="D43" t="n">
-        <v>3.331623040076253e-05</v>
+        <v>3.331623040076339e-05</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1.842118415588123e-05</v>
+        <v>-1.842118415577021e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>6.219884701677125e-05</v>
+        <v>6.219884701675206e-05</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-4.629870047615503e-05</v>
+        <v>-4.629870047606621e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>1.139044055277633e-05</v>
+        <v>1.139044055274721e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-6.170482251288689e-05</v>
+        <v>-6.170482251274256e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>7.684996192484445e-05</v>
+        <v>7.684996192483314e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.0001018963849096166</v>
+        <v>-0.0001018963849095167</v>
       </c>
       <c r="D47" t="n">
-        <v>7.992522008522712e-05</v>
+        <v>7.992522008525504e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.0001031818641623161</v>
+        <v>-0.0001031818641622384</v>
       </c>
       <c r="D48" t="n">
-        <v>7.433215004380154e-05</v>
+        <v>7.43321500438121e-05</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.0001079637018489787</v>
+        <v>-0.0001079637018488566</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0001474908991865691</v>
+        <v>0.0001474908991865428</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.000122722619602722</v>
+        <v>-0.0001227226196025777</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001727897020824825</v>
+        <v>0.0001727897020824856</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.0001476851197737328</v>
+        <v>-0.0001476851197736218</v>
       </c>
       <c r="D51" t="n">
-        <v>7.270388261475437e-05</v>
+        <v>7.270388261472435e-05</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001614084051627662</v>
+        <v>-0.0001614084051626663</v>
       </c>
       <c r="D52" t="n">
-        <v>7.218516830803868e-05</v>
+        <v>7.218516830802884e-05</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0002243916088854991</v>
+        <v>-0.000224391608885377</v>
       </c>
       <c r="D53" t="n">
-        <v>0.000140330381700117</v>
+        <v>0.0001403303817001082</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0006954477944202564</v>
+        <v>-0.0006954477944201675</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003123775988620816</v>
+        <v>0.0003123775988620616</v>
       </c>
     </row>
   </sheetData>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 05:08:00 UTC</t>
+          <t>2026-06-11 09:54:28 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_ash.xlsx
+++ b/NN/reports/feature_importance_white_ash.xlsx
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6845825246565658</v>
+        <v>0.6800252181377466</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5382493457024158</v>
+        <v>0.5404917126438302</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.716374809820653</v>
+        <v>1.707635805653452</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.46080402211227</v>
+        <v>1.218640274671984</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -538,31 +538,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07229710297930352</v>
+        <v>0.07392078499358473</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08544705036925032</v>
+        <v>0.08883728100634161</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09580546699064151</v>
+        <v>0.09795943275339536</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.950238284056983</v>
+        <v>0.5949108055762866</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
@@ -575,25 +575,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06542633112881102</v>
+        <v>0.06370161228148555</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0733571523048489</v>
+        <v>0.06733485589348111</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05403795099861055</v>
+        <v>0.05354981604745403</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9544387207107241</v>
+        <v>0.6834105794958298</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04943422175665614</v>
+        <v>0.05278192226816866</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07674211600304734</v>
+        <v>0.06908023621794038</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0248188364439721</v>
+        <v>0.0267286212150805</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7752739268555842</v>
+        <v>0.5327029817778945</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -649,31 +649,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03095962366193929</v>
+        <v>0.03043172378276767</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0206178134549151</v>
+        <v>0.0200995544193493</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02327847696583174</v>
+        <v>0.02321682924137427</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.108252928577687</v>
+        <v>0.9740681227027399</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -686,25 +686,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01372099602664899</v>
+        <v>0.0137604941032536</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09700977603986639</v>
+        <v>0.103426408421673</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00781935454004945</v>
+        <v>0.007607948772168915</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4582047093013486</v>
+        <v>0.4455611388869869</v>
       </c>
       <c r="J7" t="n">
         <v>10</v>
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001710597127719114</v>
+        <v>0.0515097571401515</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03299938050792029</v>
+        <v>0.006375094879893506</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004809675534131369</v>
+        <v>0.02412762964736483</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.241415499160037</v>
+        <v>0.44686686725841</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04900116966437267</v>
+        <v>0.00171362734339567</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006282901775732765</v>
+        <v>0.03253781330641893</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02224450907888132</v>
+        <v>0.0003391445003130155</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.691115068428279</v>
+        <v>1.201473366213727</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="10">
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001510450875415741</v>
+        <v>0.002315328377349986</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008577984193002682</v>
+        <v>0.007884245401468069</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005094488461651281</v>
+        <v>0.0005898315449532676</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8557199798313491</v>
+        <v>0.5644010612379948</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002774283169211131</v>
+        <v>0.001410847217638958</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006850580205395447</v>
+        <v>0.009682915578592115</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0005062922773449108</v>
+        <v>0.0003414091818776388</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6723410535432368</v>
+        <v>0.6077038077134711</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="12">
@@ -871,31 +871,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001127500295513923</v>
+        <v>0.001127989024976822</v>
       </c>
       <c r="D12" t="n">
         <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004204229016941893</v>
+        <v>0.005239581557694383</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002686653235799641</v>
+        <v>0.0002622409575994022</v>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3376288728348107</v>
+        <v>0.3562349381719732</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="13">
@@ -908,31 +908,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001989528458822621</v>
+        <v>0.001931453353223641</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01061077153102466</v>
+        <v>0.0101044505328351</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004304776373688979</v>
+        <v>0.0003118967992993826</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1434364390812606</v>
+        <v>0.1392444540454294</v>
       </c>
       <c r="J13" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K13" t="n">
-        <v>16.25</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="14">
@@ -941,29 +941,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0007892185650921092</v>
+        <v>0.0007530207133825601</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001317236861904575</v>
+        <v>0.001732056320379423</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002300031859156282</v>
+        <v>0.0002677155603517445</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2876059388042056</v>
+        <v>0.2985215123421208</v>
       </c>
       <c r="J14" t="n">
         <v>13</v>
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001671802649962494</v>
+        <v>0.0009714177272542936</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001301859257282997</v>
+        <v>0.001045429611593098</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0004260038654014253</v>
+        <v>0.0003836315463246143</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1476834725725422</v>
+        <v>0.1608506193713617</v>
       </c>
       <c r="J15" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
-        <v>19.25</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0007484733299693599</v>
+        <v>0.000753187083975863</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00225963088193102</v>
+        <v>0.001562364279675974</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001314299664286533</v>
+        <v>0.0001394017991636964</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2904242566689663</v>
+        <v>0.3028255227289747</v>
       </c>
       <c r="J16" t="n">
         <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0009911985965783464</v>
+        <v>0.001662572814679323</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001252252663216556</v>
+        <v>0.001231933398416441</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001395679118506243</v>
+        <v>0.0002794175086170636</v>
       </c>
       <c r="H17" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1813992530194883</v>
+        <v>0.1156273001088381</v>
       </c>
       <c r="J17" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K17" t="n">
-        <v>20.75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0009669290773591936</v>
+        <v>0.0008749662157914575</v>
       </c>
       <c r="D18" t="n">
+        <v>19</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.001285376198568808</v>
+      </c>
+      <c r="F18" t="n">
         <v>18</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.0009551664113118747</v>
-      </c>
-      <c r="F18" t="n">
-        <v>30</v>
-      </c>
       <c r="G18" t="n">
-        <v>0.0002866632852077999</v>
+        <v>0.0002076550830599877</v>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1830152428100216</v>
+        <v>0.142136826352941</v>
       </c>
       <c r="J18" t="n">
+        <v>26</v>
+      </c>
+      <c r="K18" t="n">
         <v>21</v>
-      </c>
-      <c r="K18" t="n">
-        <v>21.5</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0007132990845621818</v>
+        <v>0.0008170537327478026</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0009767724073988632</v>
+        <v>0.0009767968116605645</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003090728191157299</v>
+        <v>0.0003451852789800203</v>
       </c>
       <c r="H19" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1898896484834935</v>
+        <v>0.1578182754973589</v>
       </c>
       <c r="J19" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K19" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0009472842970054597</v>
+        <v>0.0009295933489872375</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0008788756963891966</v>
+        <v>0.0008239475207759243</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003334092436083847</v>
+        <v>0.0003046542802608299</v>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1852204622860074</v>
+        <v>0.160961821883415</v>
       </c>
       <c r="J20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>22.25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0007956209360197645</v>
+        <v>0.0009548430510591239</v>
       </c>
       <c r="D21" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0009749774851976207</v>
+        <v>0.001147792281952532</v>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001024960144342502</v>
+        <v>-2.377115489509141e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1897455725824511</v>
+        <v>0.2031090687824775</v>
       </c>
       <c r="J21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>23</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001093656776562284</v>
+        <v>0.0007364780952855083</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001364844683579517</v>
+        <v>0.0009365356081720283</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0001018963849095167</v>
+        <v>0.0001718180908426681</v>
       </c>
       <c r="H22" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1870093359082308</v>
+        <v>0.1759561832904888</v>
       </c>
       <c r="J22" t="n">
         <v>18</v>
       </c>
       <c r="K22" t="n">
-        <v>24</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0007833738412022525</v>
+        <v>0.000764784068205422</v>
       </c>
       <c r="D23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0009664663431288174</v>
+        <v>0.0008940465367908252</v>
       </c>
       <c r="F23" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0002139003216388047</v>
+        <v>0.0003204965668262783</v>
       </c>
       <c r="H23" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1617144420372227</v>
+        <v>0.1299171094960583</v>
       </c>
       <c r="J23" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K23" t="n">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0007680844327823844</v>
+        <v>0.001278061659875439</v>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0008439315814980868</v>
+        <v>0.002266155656213529</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0005290502901015515</v>
+        <v>-0.0007979795144487101</v>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1579236991637396</v>
+        <v>0.1603958110615249</v>
       </c>
       <c r="J24" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K24" t="n">
-        <v>24.75</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="25">
@@ -1348,32 +1348,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0007582790424622805</v>
+        <v>0.0007388168646070414</v>
       </c>
       <c r="D25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001185168703042303</v>
+        <v>0.000914489129873333</v>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>6.652102956095085e-05</v>
+        <v>7.508100486477431e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1560730357989031</v>
+        <v>0.1908368699036518</v>
       </c>
       <c r="J25" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K25" t="n">
         <v>27.25</v>
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0006972640002841054</v>
+        <v>0.0007492711216848783</v>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0008304877241044079</v>
+        <v>0.001151634058644568</v>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0004414328785111166</v>
+        <v>-0.0001431098473282488</v>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1490607909920729</v>
+        <v>0.1973511154055063</v>
       </c>
       <c r="J26" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="K26" t="n">
-        <v>28.75</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.00122477645199416</v>
+        <v>0.0008731865929501511</v>
       </c>
       <c r="D27" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E27" t="n">
-        <v>0.002270076568888336</v>
+        <v>0.0009843768218952846</v>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0006954477944201675</v>
+        <v>4.451721783136353e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.141477787344328</v>
+        <v>0.106134402203919</v>
       </c>
       <c r="J27" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>29</v>
+        <v>28.75</v>
       </c>
     </row>
     <row r="28">
@@ -1463,31 +1463,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001224198408668698</v>
+        <v>0.001235049220102229</v>
       </c>
       <c r="D28" t="n">
         <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>0.001121648991920873</v>
+        <v>0.00114859057407371</v>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G28" t="n">
-        <v>3.081325731252305e-05</v>
+        <v>-1.667800517023421e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I28" t="n">
-        <v>0.05251498539844945</v>
+        <v>0.09370761658679161</v>
       </c>
       <c r="J28" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="K28" t="n">
-        <v>29.75</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.698978141619845e-05</v>
+        <v>0.0006949505915132396</v>
       </c>
       <c r="D29" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="E29" t="n">
-        <v>0.00127938416420528</v>
+        <v>0.0008045754841196324</v>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>3.689122070246187e-05</v>
+        <v>0.0003785540810612442</v>
       </c>
       <c r="H29" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1870865751752169</v>
+        <v>0.09402228325438222</v>
       </c>
       <c r="J29" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="K29" t="n">
-        <v>29.75</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.30899383212723e-05</v>
+        <v>0.000680633210097839</v>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00127044775560163</v>
+        <v>0.0009270566805049732</v>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="G30" t="n">
-        <v>3.107875387389214e-05</v>
+        <v>0.0001149755631063343</v>
       </c>
       <c r="H30" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1863432137872707</v>
+        <v>0.1420112271327061</v>
       </c>
       <c r="J30" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K30" t="n">
-        <v>30.25</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0007240075033226553</v>
+        <v>0.0006771796699707807</v>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0009655402662797008</v>
+        <v>0.001066974667715616</v>
       </c>
       <c r="F31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0001806327722100654</v>
+        <v>0.0002799502317631264</v>
       </c>
       <c r="H31" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I31" t="n">
-        <v>0.08944651907265522</v>
+        <v>0.07572692342308374</v>
       </c>
       <c r="J31" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K31" t="n">
-        <v>31</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0006390868063306954</v>
+        <v>0.0007528476815906711</v>
       </c>
       <c r="D32" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0009912261557726723</v>
+        <v>0.000936578222737565</v>
       </c>
       <c r="F32" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0002101848453809341</v>
+        <v>0.0001678774978638109</v>
       </c>
       <c r="H32" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09443301208759403</v>
+        <v>0.08127930939985895</v>
       </c>
       <c r="J32" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K32" t="n">
-        <v>31</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="33">
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0007280861185023606</v>
+        <v>0.0007650726116266919</v>
       </c>
       <c r="D33" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0009416747201330058</v>
+        <v>0.001095407100862121</v>
       </c>
       <c r="F33" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G33" t="n">
-        <v>1.811809673101239e-05</v>
+        <v>-6.855343983093176e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1591691352498623</v>
+        <v>0.1005288743794375</v>
       </c>
       <c r="J33" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K33" t="n">
-        <v>31.25</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9.076134271550499e-05</v>
+        <v>0.0006396837141306384</v>
       </c>
       <c r="D34" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E34" t="n">
-        <v>0.002862490007269064</v>
+        <v>0.001114783575473459</v>
       </c>
       <c r="F34" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G34" t="n">
-        <v>5.389562769119172e-05</v>
+        <v>-0.0002577785125864707</v>
       </c>
       <c r="H34" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1558927385142801</v>
+        <v>0.1958234914034658</v>
       </c>
       <c r="J34" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="K34" t="n">
-        <v>31.25</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="35">
@@ -1718,32 +1718,32 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0008132295048725146</v>
+        <v>8.562452054369228e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="E35" t="n">
-        <v>0.000933487076112565</v>
+        <v>0.001182741465926917</v>
       </c>
       <c r="F35" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.514813604096224e-05</v>
+      </c>
+      <c r="H35" t="n">
         <v>32</v>
       </c>
-      <c r="G35" t="n">
-        <v>-0.000224391608885377</v>
-      </c>
-      <c r="H35" t="n">
-        <v>52</v>
-      </c>
       <c r="I35" t="n">
-        <v>0.1702745362477729</v>
+        <v>0.1408883484035341</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K35" t="n">
         <v>32.25</v>
@@ -1755,35 +1755,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0005035863633431989</v>
+        <v>7.506604669526684e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001172804625687977</v>
+        <v>0.001476740898676021</v>
       </c>
       <c r="F36" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0001476851197736218</v>
+        <v>3.269396022548277e-05</v>
       </c>
       <c r="H36" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1721664355155985</v>
+        <v>0.1277389310575956</v>
       </c>
       <c r="J36" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K36" t="n">
-        <v>33.75</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0006584575605353089</v>
+        <v>0.0004917288969004438</v>
       </c>
       <c r="D37" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E37" t="n">
-        <v>0.000888392709842498</v>
+        <v>0.001077189467018785</v>
       </c>
       <c r="F37" t="n">
+        <v>26</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.301514620210888e-05</v>
+      </c>
+      <c r="H37" t="n">
         <v>34</v>
       </c>
-      <c r="G37" t="n">
-        <v>-0.0001031818641622384</v>
-      </c>
-      <c r="H37" t="n">
-        <v>47</v>
-      </c>
       <c r="I37" t="n">
-        <v>0.165977979793769</v>
+        <v>0.1038183200160381</v>
       </c>
       <c r="J37" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K37" t="n">
-        <v>34.75</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="38">
@@ -1829,35 +1829,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0006455006670693641</v>
+        <v>0.0001184967251699587</v>
       </c>
       <c r="D38" t="n">
+        <v>47</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.003100019448663352</v>
+      </c>
+      <c r="F38" t="n">
+        <v>13</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.188194014031032e-05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>36</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.07872194941866106</v>
+      </c>
+      <c r="J38" t="n">
+        <v>40</v>
+      </c>
+      <c r="K38" t="n">
         <v>34</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.0007525057352409966</v>
-      </c>
-      <c r="F38" t="n">
-        <v>40</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-2.528072259555536e-06</v>
-      </c>
-      <c r="H38" t="n">
-        <v>39</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.160548726236875</v>
-      </c>
-      <c r="J38" t="n">
-        <v>27</v>
-      </c>
-      <c r="K38" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.000616693724746763</v>
+        <v>0.0007156167008854237</v>
       </c>
       <c r="D39" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0007678261886064273</v>
+        <v>0.0008004214651009396</v>
       </c>
       <c r="F39" t="n">
         <v>39</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.0001614084051626663</v>
+        <v>5.396597271619674e-05</v>
       </c>
       <c r="H39" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1943039087441263</v>
+        <v>0.0746105968709756</v>
       </c>
       <c r="J39" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="K39" t="n">
-        <v>35.25</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0008855942243954736</v>
+        <v>0.000667528872681199</v>
       </c>
       <c r="D40" t="n">
+        <v>35</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.000623085078194488</v>
+      </c>
+      <c r="F40" t="n">
+        <v>42</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-7.676763974000523e-05</v>
+      </c>
+      <c r="H40" t="n">
+        <v>47</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.1647514728112884</v>
+      </c>
+      <c r="J40" t="n">
         <v>20</v>
       </c>
-      <c r="E40" t="n">
-        <v>0.0008648024995998908</v>
-      </c>
-      <c r="F40" t="n">
+      <c r="K40" t="n">
         <v>36</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-0.0001079637018488566</v>
-      </c>
-      <c r="H40" t="n">
-        <v>48</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.128782645996957</v>
-      </c>
-      <c r="J40" t="n">
-        <v>38</v>
-      </c>
-      <c r="K40" t="n">
-        <v>35.5</v>
       </c>
     </row>
     <row r="41">
@@ -1944,31 +1944,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.000472529583246803</v>
+        <v>0.0005384728880622172</v>
       </c>
       <c r="D41" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0006595950789886791</v>
+        <v>0.0006650763710833805</v>
       </c>
       <c r="F41" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G41" t="n">
-        <v>2.425820673022105e-05</v>
+        <v>9.737969164342885e-05</v>
       </c>
       <c r="H41" t="n">
+        <v>27</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.09968889310613394</v>
+      </c>
+      <c r="J41" t="n">
         <v>36</v>
       </c>
-      <c r="I41" t="n">
-        <v>0.1492943793711148</v>
-      </c>
-      <c r="J41" t="n">
-        <v>32</v>
-      </c>
       <c r="K41" t="n">
-        <v>38.25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0005468799884780956</v>
+        <v>0.0006701088738634766</v>
       </c>
       <c r="D42" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0005708097496547163</v>
+        <v>0.0006842171394645225</v>
       </c>
       <c r="F42" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>8.381838859216062e-05</v>
+        <v>-7.059586605757673e-05</v>
       </c>
       <c r="H42" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I42" t="n">
-        <v>0.07311181718503645</v>
+        <v>0.1559329730828996</v>
       </c>
       <c r="J42" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K42" t="n">
-        <v>38.5</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0007162777074455035</v>
+        <v>0.0006088353991203538</v>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0007506174608899811</v>
+        <v>0.0008351610162686362</v>
       </c>
       <c r="F43" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G43" t="n">
-        <v>-1.842118415577021e-05</v>
+        <v>-0.0002784330466673035</v>
       </c>
       <c r="H43" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1183116735148451</v>
+        <v>0.1739358867039082</v>
       </c>
       <c r="J43" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>38.5</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="44">
@@ -2055,31 +2055,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0004809459134601496</v>
+        <v>0.0004512986664809379</v>
       </c>
       <c r="D44" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0004779629780192875</v>
+        <v>0.0004959209443196723</v>
       </c>
       <c r="F44" t="n">
+        <v>44</v>
+      </c>
+      <c r="G44" t="n">
+        <v>7.943631783050576e-05</v>
+      </c>
+      <c r="H44" t="n">
+        <v>28</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.0466126146370085</v>
+      </c>
+      <c r="J44" t="n">
         <v>46</v>
       </c>
-      <c r="G44" t="n">
-        <v>0.0001096498824924574</v>
-      </c>
-      <c r="H44" t="n">
-        <v>26</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.09670591672826001</v>
-      </c>
-      <c r="J44" t="n">
-        <v>42</v>
-      </c>
       <c r="K44" t="n">
-        <v>39</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="45">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0004924684336355406</v>
+        <v>0.0004718788337140494</v>
       </c>
       <c r="D45" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0009265011957629304</v>
+        <v>0.0004455040804141887</v>
       </c>
       <c r="F45" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="G45" t="n">
-        <v>-6.170482251274256e-05</v>
+        <v>0.0001032949656526116</v>
       </c>
       <c r="H45" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1230074443286315</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K45" t="n">
-        <v>39.25</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="46">
@@ -2125,35 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0003904569279833252</v>
+        <v>0.0005432771320032983</v>
       </c>
       <c r="D46" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E46" t="n">
-        <v>0.000420697237944519</v>
+        <v>0.0005849586898043011</v>
       </c>
       <c r="F46" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G46" t="n">
-        <v>0.000120427855730032</v>
+        <v>2.541221249653392e-05</v>
       </c>
       <c r="H46" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I46" t="n">
-        <v>0.09725371808717842</v>
+        <v>0.03224518135769872</v>
       </c>
       <c r="J46" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K46" t="n">
-        <v>40</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="47">
@@ -2166,31 +2166,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0002457714656790424</v>
+        <v>0.0002296868419742113</v>
       </c>
       <c r="D47" t="n">
         <v>45</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0004852459499602878</v>
+        <v>0.0004402655751033603</v>
       </c>
       <c r="F47" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G47" t="n">
-        <v>6.790068628058643e-05</v>
+        <v>7.591721942727947e-05</v>
       </c>
       <c r="H47" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I47" t="n">
-        <v>0.008242740809141669</v>
+        <v>0.03167145573501529</v>
       </c>
       <c r="J47" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K47" t="n">
-        <v>42.25</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="48">
@@ -2203,31 +2203,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0006351413567515426</v>
+        <v>0.0006392316186347107</v>
       </c>
       <c r="D48" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E48" t="n">
-        <v>0.000438946854662599</v>
+        <v>0.0004585252415905689</v>
       </c>
       <c r="F48" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.0001227226196025777</v>
+        <v>-9.471982957667268e-05</v>
       </c>
       <c r="H48" t="n">
         <v>49</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1326389331697615</v>
+        <v>0.07006369108004318</v>
       </c>
       <c r="J48" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K48" t="n">
-        <v>42.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
@@ -2236,35 +2236,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0004855531946411347</v>
+        <v>0.0004077400538995397</v>
       </c>
       <c r="D49" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E49" t="n">
-        <v>0.0003700164525165009</v>
+        <v>0.0003989023369340952</v>
       </c>
       <c r="F49" t="n">
         <v>51</v>
       </c>
       <c r="G49" t="n">
-        <v>7.84792035183779e-05</v>
+        <v>9.887444687772806e-06</v>
       </c>
       <c r="H49" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>0.07444809598034219</v>
       </c>
       <c r="J49" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="K49" t="n">
-        <v>43.25</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="50">
@@ -2277,31 +2277,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0001535210752696423</v>
+        <v>0.000192427640655558</v>
       </c>
       <c r="D50" t="n">
         <v>46</v>
       </c>
       <c r="E50" t="n">
-        <v>0.000476872713969579</v>
+        <v>0.000473015342762744</v>
       </c>
       <c r="F50" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G50" t="n">
-        <v>1.849763085917111e-05</v>
+        <v>-8.463044702849976e-05</v>
       </c>
       <c r="H50" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0400575501465541</v>
+        <v>0.04807124431972998</v>
       </c>
       <c r="J50" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K50" t="n">
-        <v>44.25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
@@ -2314,31 +2314,31 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0001188637430725328</v>
+        <v>0.0001146541490661912</v>
       </c>
       <c r="D51" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0004301595968848989</v>
+        <v>0.0004139810386876009</v>
       </c>
       <c r="F51" t="n">
         <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>-7.455357771435355e-06</v>
+        <v>-5.715355416913149e-06</v>
       </c>
       <c r="H51" t="n">
         <v>41</v>
       </c>
       <c r="I51" t="n">
-        <v>0.004971275335964087</v>
+        <v>0.02092021476374217</v>
       </c>
       <c r="J51" t="n">
         <v>50</v>
       </c>
       <c r="K51" t="n">
-        <v>46.75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52">
@@ -2351,31 +2351,31 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5.268053962815199e-05</v>
+        <v>1.221535404480305e-05</v>
       </c>
       <c r="D52" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0005316944652482683</v>
+        <v>0.0004128940098443284</v>
       </c>
       <c r="F52" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>-4.629870047606621e-05</v>
+        <v>1.367625866949274e-05</v>
       </c>
       <c r="H52" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I52" t="n">
-        <v>0.02685289281413383</v>
+        <v>0.02793674948181502</v>
       </c>
       <c r="J52" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K52" t="n">
-        <v>46.75</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="53">
@@ -2388,25 +2388,25 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8.533205717533462e-06</v>
+        <v>6.773975045052927e-06</v>
       </c>
       <c r="D53" t="n">
         <v>53</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0001278686581038072</v>
+        <v>8.802555512954454e-05</v>
       </c>
       <c r="F53" t="n">
         <v>53</v>
       </c>
       <c r="G53" t="n">
-        <v>-4.185863186256799e-06</v>
+        <v>-3.37317632691514e-06</v>
       </c>
       <c r="H53" t="n">
         <v>40</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0007573068389503668</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>51</v>
@@ -2425,28 +2425,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.750403793454735e-05</v>
+        <v>2.590899729806618e-05</v>
       </c>
       <c r="D54" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0001939323378855499</v>
+        <v>0.0002023044353954326</v>
       </c>
       <c r="F54" t="n">
         <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>-8.474531482216551e-06</v>
+        <v>-2.704625013825179e-05</v>
       </c>
       <c r="H54" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K54" t="n">
         <v>49.5</v>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6845825246565658</v>
+        <v>0.6800252181377466</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5382493457024158</v>
+        <v>0.5404917126438302</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1.716374809820653</v>
+        <v>1.707635805653452</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.46080402211227</v>
+        <v>1.218640274671984</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -2570,31 +2570,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07229710297930352</v>
+        <v>0.07392078499358473</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08544705036925032</v>
+        <v>0.08883728100634161</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09580546699064151</v>
+        <v>0.09795943275339536</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.950238284056983</v>
+        <v>0.5949108055762866</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
@@ -2607,25 +2607,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06542633112881102</v>
+        <v>0.06370161228148555</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0733571523048489</v>
+        <v>0.06733485589348111</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05403795099861055</v>
+        <v>0.05354981604745403</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9544387207107241</v>
+        <v>0.6834105794958298</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -2644,31 +2644,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04943422175665614</v>
+        <v>0.05278192226816866</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07674211600304734</v>
+        <v>0.06908023621794038</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0248188364439721</v>
+        <v>0.0267286212150805</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7752739268555842</v>
+        <v>0.5327029817778945</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2681,31 +2681,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03095962366193929</v>
+        <v>0.03043172378276767</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0206178134549151</v>
+        <v>0.0200995544193493</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02327847696583174</v>
+        <v>0.02321682924137427</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.108252928577687</v>
+        <v>0.9740681227027399</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -2718,25 +2718,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01372099602664899</v>
+        <v>0.0137604941032536</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09700977603986639</v>
+        <v>0.103426408421673</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00781935454004945</v>
+        <v>0.007607948772168915</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4582047093013486</v>
+        <v>0.4455611388869869</v>
       </c>
       <c r="J7" t="n">
         <v>10</v>
@@ -2751,35 +2751,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001710597127719114</v>
+        <v>0.0515097571401515</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03299938050792029</v>
+        <v>0.006375094879893506</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0004809675534131369</v>
+        <v>0.02412762964736483</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.241415499160037</v>
+        <v>0.44686686725841</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9">
@@ -2788,35 +2788,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.04900116966437267</v>
+        <v>0.00171362734339567</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006282901775732765</v>
+        <v>0.03253781330641893</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02224450907888132</v>
+        <v>0.0003391445003130155</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.691115068428279</v>
+        <v>1.201473366213727</v>
       </c>
       <c r="J9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="10">
@@ -2825,35 +2825,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001510450875415741</v>
+        <v>0.002315328377349986</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008577984193002682</v>
+        <v>0.007884245401468069</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005094488461651281</v>
+        <v>0.0005898315449532676</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8557199798313491</v>
+        <v>0.5644010612379948</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>9</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="11">
@@ -2862,35 +2862,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002774283169211131</v>
+        <v>0.001410847217638958</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.006850580205395447</v>
+        <v>0.009682915578592115</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0005062922773449108</v>
+        <v>0.0003414091818776388</v>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6723410535432368</v>
+        <v>0.6077038077134711</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="12">
@@ -2903,31 +2903,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001127500295513923</v>
+        <v>0.001127989024976822</v>
       </c>
       <c r="D12" t="n">
         <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004204229016941893</v>
+        <v>0.005239581557694383</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002686653235799641</v>
+        <v>0.0002622409575994022</v>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3376288728348107</v>
+        <v>0.3562349381719732</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="13">
@@ -2940,31 +2940,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001989528458822621</v>
+        <v>0.001931453353223641</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01061077153102466</v>
+        <v>0.0101044505328351</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0004304776373688979</v>
+        <v>0.0003118967992993826</v>
       </c>
       <c r="H13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1434364390812606</v>
+        <v>0.1392444540454294</v>
       </c>
       <c r="J13" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K13" t="n">
-        <v>16.25</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="14">
@@ -2973,29 +2973,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0007892185650921092</v>
+        <v>0.0007530207133825601</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001317236861904575</v>
+        <v>0.001732056320379423</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002300031859156282</v>
+        <v>0.0002677155603517445</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2876059388042056</v>
+        <v>0.2985215123421208</v>
       </c>
       <c r="J14" t="n">
         <v>13</v>
@@ -3010,35 +3010,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001671802649962494</v>
+        <v>0.0009714177272542936</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001301859257282997</v>
+        <v>0.001045429611593098</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0004260038654014253</v>
+        <v>0.0003836315463246143</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1476834725725422</v>
+        <v>0.1608506193713617</v>
       </c>
       <c r="J15" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
-        <v>19.25</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="16">
@@ -3047,35 +3047,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0007484733299693599</v>
+        <v>0.000753187083975863</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00225963088193102</v>
+        <v>0.001562364279675974</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001314299664286533</v>
+        <v>0.0001394017991636964</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2904242566689663</v>
+        <v>0.3028255227289747</v>
       </c>
       <c r="J16" t="n">
         <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3084,35 +3084,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0009911985965783464</v>
+        <v>0.001662572814679323</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001252252663216556</v>
+        <v>0.001231933398416441</v>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0001395679118506243</v>
+        <v>0.0002794175086170636</v>
       </c>
       <c r="H17" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1813992530194883</v>
+        <v>0.1156273001088381</v>
       </c>
       <c r="J17" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K17" t="n">
-        <v>20.75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -3121,35 +3121,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0009669290773591936</v>
+        <v>0.0008749662157914575</v>
       </c>
       <c r="D18" t="n">
+        <v>19</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.001285376198568808</v>
+      </c>
+      <c r="F18" t="n">
         <v>18</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.0009551664113118747</v>
-      </c>
-      <c r="F18" t="n">
-        <v>30</v>
-      </c>
       <c r="G18" t="n">
-        <v>0.0002866632852077999</v>
+        <v>0.0002076550830599877</v>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1830152428100216</v>
+        <v>0.142136826352941</v>
       </c>
       <c r="J18" t="n">
+        <v>26</v>
+      </c>
+      <c r="K18" t="n">
         <v>21</v>
-      </c>
-      <c r="K18" t="n">
-        <v>21.5</v>
       </c>
     </row>
     <row r="19">
@@ -3158,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0007132990845621818</v>
+        <v>0.0008170537327478026</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0009767724073988632</v>
+        <v>0.0009767968116605645</v>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003090728191157299</v>
+        <v>0.0003451852789800203</v>
       </c>
       <c r="H19" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1898896484834935</v>
+        <v>0.1578182754973589</v>
       </c>
       <c r="J19" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K19" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0009472842970054597</v>
+        <v>0.0009295933489872375</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0008788756963891966</v>
+        <v>0.0008239475207759243</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003334092436083847</v>
+        <v>0.0003046542802608299</v>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1852204622860074</v>
+        <v>0.160961821883415</v>
       </c>
       <c r="J20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>22.25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -3232,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0007956209360197645</v>
+        <v>0.0009548430510591239</v>
       </c>
       <c r="D21" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0009749774851976207</v>
+        <v>0.001147792281952532</v>
       </c>
       <c r="F21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0001024960144342502</v>
+        <v>-2.377115489509141e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1897455725824511</v>
+        <v>0.2031090687824775</v>
       </c>
       <c r="J21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K21" t="n">
-        <v>23</v>
+        <v>24.25</v>
       </c>
     </row>
   </sheetData>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6845825246565658</v>
+        <v>0.6800252181377466</v>
       </c>
     </row>
     <row r="3">
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07229710297930352</v>
+        <v>0.07392078499358473</v>
       </c>
     </row>
     <row r="4">
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06542633112881102</v>
+        <v>0.06370161228148555</v>
       </c>
     </row>
     <row r="5">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04943422175665614</v>
+        <v>0.05278192226816866</v>
       </c>
     </row>
     <row r="6">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04900116966437267</v>
+        <v>0.0515097571401515</v>
       </c>
     </row>
     <row r="7">
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03095962366193929</v>
+        <v>0.03043172378276767</v>
       </c>
     </row>
     <row r="8">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01372099602664899</v>
+        <v>0.0137604941032536</v>
       </c>
     </row>
     <row r="9">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002774283169211131</v>
+        <v>0.002315328377349986</v>
       </c>
     </row>
     <row r="10">
@@ -3408,7 +3408,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001989528458822621</v>
+        <v>0.001931453353223641</v>
       </c>
     </row>
     <row r="11">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001710597127719114</v>
+        <v>0.00171362734339567</v>
       </c>
     </row>
     <row r="12">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001671802649962494</v>
+        <v>0.001662572814679323</v>
       </c>
     </row>
     <row r="13">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001510450875415741</v>
+        <v>0.001410847217638958</v>
       </c>
     </row>
     <row r="14">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00122477645199416</v>
+        <v>0.001278061659875439</v>
       </c>
     </row>
     <row r="15">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001224198408668698</v>
+        <v>0.001235049220102229</v>
       </c>
     </row>
     <row r="16">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001127500295513923</v>
+        <v>0.001127989024976822</v>
       </c>
     </row>
     <row r="17">
@@ -3495,11 +3495,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001093656776562284</v>
+        <v>0.0009714177272542936</v>
       </c>
     </row>
     <row r="18">
@@ -3508,11 +3508,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0009911985965783464</v>
+        <v>0.0009548430510591239</v>
       </c>
     </row>
     <row r="19">
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0009669290773591936</v>
+        <v>0.0009295933489872375</v>
       </c>
     </row>
     <row r="20">
@@ -3534,11 +3534,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0009472842970054597</v>
+        <v>0.0008749662157914575</v>
       </c>
     </row>
     <row r="21">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0008855942243954736</v>
+        <v>0.0008731865929501511</v>
       </c>
     </row>
     <row r="22">
@@ -3560,11 +3560,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0008132295048725146</v>
+        <v>0.0008170537327478026</v>
       </c>
     </row>
     <row r="23">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0007956209360197645</v>
+        <v>0.0007650726116266919</v>
       </c>
     </row>
     <row r="24">
@@ -3586,11 +3586,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0007892185650921092</v>
+        <v>0.000764784068205422</v>
       </c>
     </row>
     <row r="25">
@@ -3599,11 +3599,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0007833738412022525</v>
+        <v>0.000753187083975863</v>
       </c>
     </row>
     <row r="26">
@@ -3612,11 +3612,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0007680844327823844</v>
+        <v>0.0007530207133825601</v>
       </c>
     </row>
     <row r="27">
@@ -3625,11 +3625,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0007582790424622805</v>
+        <v>0.0007528476815906711</v>
       </c>
     </row>
     <row r="28">
@@ -3638,11 +3638,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0007484733299693599</v>
+        <v>0.0007492711216848783</v>
       </c>
     </row>
     <row r="29">
@@ -3651,11 +3651,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0007280861185023606</v>
+        <v>0.0007388168646070414</v>
       </c>
     </row>
     <row r="30">
@@ -3664,11 +3664,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0007240075033226553</v>
+        <v>0.0007364780952855083</v>
       </c>
     </row>
     <row r="31">
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0007162777074455035</v>
+        <v>0.0007156167008854237</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3690,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0007132990845621818</v>
+        <v>0.0006949505915132396</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3703,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0006972640002841054</v>
+        <v>0.000680633210097839</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3716,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0006584575605353089</v>
+        <v>0.0006771796699707807</v>
       </c>
     </row>
     <row r="35">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0006455006670693641</v>
+        <v>0.0006701088738634766</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3742,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0006390868063306954</v>
+        <v>0.000667528872681199</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3755,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0006351413567515426</v>
+        <v>0.0006396837141306384</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.000616693724746763</v>
+        <v>0.0006392316186347107</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3781,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0005468799884780956</v>
+        <v>0.0006088353991203538</v>
       </c>
     </row>
     <row r="40">
@@ -3794,11 +3794,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0005035863633431989</v>
+        <v>0.0005432771320032983</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3807,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0004924684336355406</v>
+        <v>0.0005384728880622172</v>
       </c>
     </row>
     <row r="42">
@@ -3820,11 +3820,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0004855531946411347</v>
+        <v>0.0004917288969004438</v>
       </c>
     </row>
     <row r="43">
@@ -3833,11 +3833,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0004809459134601496</v>
+        <v>0.0004718788337140494</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3846,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.000472529583246803</v>
+        <v>0.0004512986664809379</v>
       </c>
     </row>
     <row r="45">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0003904569279833252</v>
+        <v>0.0004077400538995397</v>
       </c>
     </row>
     <row r="46">
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0002457714656790424</v>
+        <v>0.0002296868419742113</v>
       </c>
     </row>
     <row r="47">
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0001535210752696423</v>
+        <v>0.000192427640655558</v>
       </c>
     </row>
     <row r="48">
@@ -3898,11 +3898,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0001188637430725328</v>
+        <v>0.0001184967251699587</v>
       </c>
     </row>
     <row r="49">
@@ -3911,11 +3911,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>9.30899383212723e-05</v>
+        <v>0.0001146541490661912</v>
       </c>
     </row>
     <row r="50">
@@ -3924,11 +3924,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9.076134271550499e-05</v>
+        <v>8.562452054369228e-05</v>
       </c>
     </row>
     <row r="51">
@@ -3937,11 +3937,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6.698978141619845e-05</v>
+        <v>7.506604669526684e-05</v>
       </c>
     </row>
     <row r="52">
@@ -3950,11 +3950,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5.268053962815199e-05</v>
+        <v>2.590899729806618e-05</v>
       </c>
     </row>
     <row r="53">
@@ -3963,11 +3963,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.750403793454735e-05</v>
+        <v>1.221535404480305e-05</v>
       </c>
     </row>
     <row r="54">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8.533205717533462e-06</v>
+        <v>6.773975045052927e-06</v>
       </c>
     </row>
   </sheetData>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5382493457024158</v>
+        <v>0.5404917126438302</v>
       </c>
     </row>
     <row r="3">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09700977603986639</v>
+        <v>0.103426408421673</v>
       </c>
     </row>
     <row r="4">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08544705036925032</v>
+        <v>0.08883728100634161</v>
       </c>
     </row>
     <row r="5">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07674211600304734</v>
+        <v>0.06908023621794038</v>
       </c>
     </row>
     <row r="6">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0733571523048489</v>
+        <v>0.06733485589348111</v>
       </c>
     </row>
     <row r="7">
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03299938050792029</v>
+        <v>0.03253781330641893</v>
       </c>
     </row>
     <row r="8">
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0206178134549151</v>
+        <v>0.0200995544193493</v>
       </c>
     </row>
     <row r="9">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01061077153102466</v>
+        <v>0.0101044505328351</v>
       </c>
     </row>
     <row r="10">
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.008577984193002682</v>
+        <v>0.009682915578592115</v>
       </c>
     </row>
     <row r="11">
@@ -4141,7 +4141,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006850580205395447</v>
+        <v>0.007884245401468069</v>
       </c>
     </row>
     <row r="12">
@@ -4154,7 +4154,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.006282901775732765</v>
+        <v>0.006375094879893506</v>
       </c>
     </row>
     <row r="13">
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.004204229016941893</v>
+        <v>0.005239581557694383</v>
       </c>
     </row>
     <row r="14">
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002862490007269064</v>
+        <v>0.003100019448663352</v>
       </c>
     </row>
     <row r="15">
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002270076568888336</v>
+        <v>0.002266155656213529</v>
       </c>
     </row>
     <row r="16">
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00225963088193102</v>
+        <v>0.001732056320379423</v>
       </c>
     </row>
     <row r="17">
@@ -4215,11 +4215,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001364844683579517</v>
+        <v>0.001562364279675974</v>
       </c>
     </row>
     <row r="18">
@@ -4228,11 +4228,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001317236861904575</v>
+        <v>0.001476740898676021</v>
       </c>
     </row>
     <row r="19">
@@ -4241,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001301859257282997</v>
+        <v>0.001285376198568808</v>
       </c>
     </row>
     <row r="20">
@@ -4254,11 +4254,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.00127938416420528</v>
+        <v>0.001231933398416441</v>
       </c>
     </row>
     <row r="21">
@@ -4267,11 +4267,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.00127044775560163</v>
+        <v>0.001182741465926917</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001252252663216556</v>
+        <v>0.001151634058644568</v>
       </c>
     </row>
     <row r="23">
@@ -4293,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001185168703042303</v>
+        <v>0.00114859057407371</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +4306,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001172804625687977</v>
+        <v>0.001147792281952532</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001121648991920873</v>
+        <v>0.001114783575473459</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0009912261557726723</v>
+        <v>0.001095407100862121</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0009767724073988632</v>
+        <v>0.001077189467018785</v>
       </c>
     </row>
     <row r="28">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0009749774851976207</v>
+        <v>0.001066974667715616</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +4371,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0009664663431288174</v>
+        <v>0.001045429611593098</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +4384,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0009655402662797008</v>
+        <v>0.0009843768218952846</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0009551664113118747</v>
+        <v>0.0009767968116605645</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4410,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0009416747201330058</v>
+        <v>0.000936578222737565</v>
       </c>
     </row>
     <row r="33">
@@ -4423,11 +4423,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.000933487076112565</v>
+        <v>0.0009365356081720283</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4436,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0009265011957629304</v>
+        <v>0.0009270566805049732</v>
       </c>
     </row>
     <row r="35">
@@ -4449,11 +4449,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.000888392709842498</v>
+        <v>0.000914489129873333</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4462,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0008788756963891966</v>
+        <v>0.0008940465367908252</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4475,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0008648024995998908</v>
+        <v>0.0008351610162686362</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0008439315814980868</v>
+        <v>0.0008239475207759243</v>
       </c>
     </row>
     <row r="39">
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0008304877241044079</v>
+        <v>0.0008045754841196324</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4514,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0007678261886064273</v>
+        <v>0.0008004214651009396</v>
       </c>
     </row>
     <row r="41">
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0007525057352409966</v>
+        <v>0.0006842171394645225</v>
       </c>
     </row>
     <row r="42">
@@ -4540,11 +4540,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0007506174608899811</v>
+        <v>0.0006650763710833805</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4553,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0006595950789886791</v>
+        <v>0.000623085078194488</v>
       </c>
     </row>
     <row r="44">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0005708097496547163</v>
+        <v>0.0005849586898043011</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4579,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0005316944652482683</v>
+        <v>0.0004959209443196723</v>
       </c>
     </row>
     <row r="46">
@@ -4592,11 +4592,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0004852459499602878</v>
+        <v>0.000473015342762744</v>
       </c>
     </row>
     <row r="47">
@@ -4605,11 +4605,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0004779629780192875</v>
+        <v>0.0004585252415905689</v>
       </c>
     </row>
     <row r="48">
@@ -4618,11 +4618,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.000476872713969579</v>
+        <v>0.0004455040804141887</v>
       </c>
     </row>
     <row r="49">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.000438946854662599</v>
+        <v>0.0004402655751033603</v>
       </c>
     </row>
     <row r="50">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0004301595968848989</v>
+        <v>0.0004139810386876009</v>
       </c>
     </row>
     <row r="51">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.000420697237944519</v>
+        <v>0.0004128940098443284</v>
       </c>
     </row>
     <row r="52">
@@ -4670,11 +4670,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.0003700164525165009</v>
+        <v>0.0003989023369340952</v>
       </c>
     </row>
     <row r="53">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0001939323378855499</v>
+        <v>0.0002023044353954326</v>
       </c>
     </row>
     <row r="54">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.0001278686581038072</v>
+        <v>8.802555512954454e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.716374809820653</v>
+        <v>1.707635805653452</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0785625935020739</v>
+        <v>0.07801799479420515</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09580546699064151</v>
+        <v>0.09795943275339536</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008347833538365906</v>
+        <v>0.008682725788401426</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05403795099861055</v>
+        <v>0.05354981604745403</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006091575404357176</v>
+        <v>0.005935131558129029</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0248188364439721</v>
+        <v>0.0267286212150805</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002969792383778232</v>
+        <v>0.003212245253402749</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02327847696583174</v>
+        <v>0.02412762964736483</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003583200364413966</v>
+        <v>0.002811931222986497</v>
       </c>
     </row>
     <row r="7">
@@ -4825,14 +4825,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02224450907888132</v>
+        <v>0.02321682924137427</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002647902235471949</v>
+        <v>0.003626306122843932</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.00781935454004945</v>
+        <v>0.007607948772168915</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002220243453168804</v>
+        <v>0.002231029644669918</v>
       </c>
     </row>
     <row r="9">
@@ -4857,14 +4857,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0005290502901015515</v>
+        <v>0.0005898315449532676</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000259368214375018</v>
+        <v>0.0004752076410622965</v>
       </c>
     </row>
     <row r="10">
@@ -4873,14 +4873,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0005094488461651281</v>
+        <v>0.0003836315463246143</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001778806428961804</v>
+        <v>0.0001569891301369052</v>
       </c>
     </row>
     <row r="11">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0005062922773449108</v>
+        <v>0.0003785540810612442</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0005642574761980767</v>
+        <v>9.320889179858812e-05</v>
       </c>
     </row>
     <row r="12">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0004809675534131369</v>
+        <v>0.0003451852789800203</v>
       </c>
       <c r="D12" t="n">
-        <v>4.126683748916188e-05</v>
+        <v>0.0001229530453033242</v>
       </c>
     </row>
     <row r="13">
@@ -4921,14 +4921,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0004414328785111166</v>
+        <v>0.0003414091818776388</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001053503090220675</v>
+        <v>0.0001949165249264165</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0004304776373688979</v>
+        <v>0.0003391445003130155</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0003984310551087081</v>
+        <v>3.707081220569008e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0004260038654014253</v>
+        <v>0.0003204965668262783</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0004079183170933347</v>
+        <v>0.0001922446410491603</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0003334092436083847</v>
+        <v>0.0003118967992993826</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001805462777049459</v>
+        <v>0.0003173268004239832</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0003090728191157299</v>
+        <v>0.0003046542802608299</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001160218681415018</v>
+        <v>0.0001439406965768496</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0002866632852077999</v>
+        <v>0.0002799502317631264</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001459550048228453</v>
+        <v>0.0001280604313256435</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0002686653235799641</v>
+        <v>0.0002794175086170636</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0001089246761980513</v>
+        <v>0.0003944946494375706</v>
       </c>
     </row>
     <row r="20">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0002300031859156282</v>
+        <v>0.0002677155603517445</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001504050734485005</v>
+        <v>0.0001647124028711472</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0002139003216388047</v>
+        <v>0.0002622409575994022</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0002553776156497667</v>
+        <v>7.740803687130581e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0002101848453809341</v>
+        <v>0.0002076550830599877</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001516477572169163</v>
+        <v>0.0001455212522585836</v>
       </c>
     </row>
     <row r="23">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0001806327722100654</v>
+        <v>0.0001718180908426681</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001212977104113441</v>
+        <v>0.0001570658298068233</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0001395679118506243</v>
+        <v>0.0001678774978638109</v>
       </c>
       <c r="D24" t="n">
-        <v>0.000136757645087713</v>
+        <v>0.0001349968981410332</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +5113,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0001314299664286533</v>
+        <v>0.0001394017991636964</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000148844969101574</v>
+        <v>0.000220205941170529</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.000120427855730032</v>
+        <v>0.0001149755631063343</v>
       </c>
       <c r="D26" t="n">
-        <v>8.644715757184805e-05</v>
+        <v>6.155517252700753e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0001096498824924574</v>
+        <v>0.0001032949656526116</v>
       </c>
       <c r="D27" t="n">
-        <v>3.887620502892481e-05</v>
+        <v>6.520066052022178e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0001024960144342502</v>
+        <v>9.737969164342885e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001360699212864287</v>
+        <v>4.872398371474235e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +5177,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8.381838859216062e-05</v>
+        <v>7.943631783050576e-05</v>
       </c>
       <c r="D29" t="n">
-        <v>7.083324264084419e-05</v>
+        <v>5.051636987226809e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +5193,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.84792035183779e-05</v>
+        <v>7.591721942727947e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>6.270456612364253e-05</v>
+        <v>6.203837256941819e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.790068628058643e-05</v>
+        <v>7.508100486477431e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>4.713395237778151e-05</v>
+        <v>0.0001249166349489409</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +5225,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6.652102956095085e-05</v>
+        <v>5.396597271619674e-05</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001404280489173892</v>
+        <v>7.491467483872107e-05</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.389562769119172e-05</v>
+        <v>4.514813604096224e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>2.681769902341101e-05</v>
+        <v>2.601168765519987e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.689122070246187e-05</v>
+        <v>4.451721783136353e-05</v>
       </c>
       <c r="D34" t="n">
-        <v>2.071088956789535e-05</v>
+        <v>0.0001464450104960018</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3.107875387389214e-05</v>
+        <v>3.301514620210888e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>3.746538395252123e-05</v>
+        <v>6.669297915275336e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5289,14 +5289,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.081325731252305e-05</v>
+        <v>3.269396022548277e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0003232461847371094</v>
+        <v>2.519865399273078e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2.425820673022105e-05</v>
+        <v>3.188194014031032e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>5.521058900032648e-05</v>
+        <v>2.528221235999303e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.849763085917111e-05</v>
+        <v>2.541221249653392e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>3.820730905638803e-05</v>
+        <v>5.84706564231459e-05</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.811809673101239e-05</v>
+        <v>1.367625866949274e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001114114459944835</v>
+        <v>7.824739093467306e-06</v>
       </c>
     </row>
     <row r="40">
@@ -5353,14 +5353,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-2.528072259555536e-06</v>
+        <v>9.887444687772806e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001211611265717333</v>
+        <v>0.0001154125676430098</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-4.185863186256799e-06</v>
+        <v>-3.37317632691514e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>2.178328136386735e-06</v>
+        <v>3.103601093983625e-06</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-7.455357771435355e-06</v>
+        <v>-5.715355416913149e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>1.68455631717143e-05</v>
+        <v>1.861720893452239e-05</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +5401,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-8.474531482216551e-06</v>
+        <v>-1.667800517023421e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>3.331623040076339e-05</v>
+        <v>0.0003124043520494461</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1.842118415577021e-05</v>
+        <v>-2.377115489509141e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>6.219884701675206e-05</v>
+        <v>0.0001786426619872065</v>
       </c>
     </row>
     <row r="45">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-4.629870047606621e-05</v>
+        <v>-2.704625013825179e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>1.139044055274721e-05</v>
+        <v>1.552544431576424e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5449,14 +5449,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-6.170482251274256e-05</v>
+        <v>-6.855343983093176e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>7.684996192483314e-05</v>
+        <v>0.0001749117956052541</v>
       </c>
     </row>
     <row r="47">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-0.0001018963849095167</v>
+        <v>-7.059586605757673e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>7.992522008525504e-05</v>
+        <v>0.0001541723545647746</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-0.0001031818641622384</v>
+        <v>-7.676763974000523e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>7.43321500438121e-05</v>
+        <v>9.031310258090133e-05</v>
       </c>
     </row>
     <row r="49">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-0.0001079637018488566</v>
+        <v>-8.463044702849976e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0001474908991865428</v>
+        <v>3.332377236627358e-05</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.0001227226196025777</v>
+        <v>-9.471982957667268e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001727897020824856</v>
+        <v>0.0001419861488978549</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.0001476851197736218</v>
+        <v>-0.0001431098473282488</v>
       </c>
       <c r="D51" t="n">
-        <v>7.270388261472435e-05</v>
+        <v>0.0001179461880385185</v>
       </c>
     </row>
     <row r="52">
@@ -5545,14 +5545,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0001614084051626663</v>
+        <v>-0.0002577785125864707</v>
       </c>
       <c r="D52" t="n">
-        <v>7.218516830802884e-05</v>
+        <v>0.0001257590458424681</v>
       </c>
     </row>
     <row r="53">
@@ -5561,14 +5561,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.000224391608885377</v>
+        <v>-0.0002784330466673035</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0001403303817001082</v>
+        <v>8.788422570898574e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0006954477944201675</v>
+        <v>-0.0007979795144487101</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003123775988620616</v>
+        <v>0.0003239428442837587</v>
       </c>
     </row>
   </sheetData>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.46080402211227</v>
+        <v>1.218640274671984</v>
       </c>
     </row>
     <row r="3">
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.241415499160037</v>
+        <v>1.201473366213727</v>
       </c>
     </row>
     <row r="4">
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.108252928577687</v>
+        <v>0.9740681227027399</v>
       </c>
     </row>
     <row r="5">
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9544387207107241</v>
+        <v>0.6834105794958298</v>
       </c>
     </row>
     <row r="6">
@@ -5676,11 +5676,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.950238284056983</v>
+        <v>0.6077038077134711</v>
       </c>
     </row>
     <row r="7">
@@ -5689,11 +5689,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8557199798313491</v>
+        <v>0.5949108055762866</v>
       </c>
     </row>
     <row r="8">
@@ -5702,11 +5702,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7752739268555842</v>
+        <v>0.5644010612379948</v>
       </c>
     </row>
     <row r="9">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.691115068428279</v>
+        <v>0.5327029817778945</v>
       </c>
     </row>
     <row r="10">
@@ -5728,11 +5728,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6723410535432368</v>
+        <v>0.44686686725841</v>
       </c>
     </row>
     <row r="11">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.4582047093013486</v>
+        <v>0.4455611388869869</v>
       </c>
     </row>
     <row r="12">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.3376288728348107</v>
+        <v>0.3562349381719732</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2904242566689663</v>
+        <v>0.3028255227289747</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2876059388042056</v>
+        <v>0.2985215123421208</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1943039087441263</v>
+        <v>0.2031090687824775</v>
       </c>
     </row>
     <row r="16">
@@ -5806,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1898896484834935</v>
+        <v>0.1973511154055063</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.1897455725824511</v>
+        <v>0.1958234914034658</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1870865751752169</v>
+        <v>0.1908368699036518</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1870093359082308</v>
+        <v>0.1759561832904888</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1863432137872707</v>
+        <v>0.1739358867039082</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1852204622860074</v>
+        <v>0.1647514728112884</v>
       </c>
     </row>
     <row r="22">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1830152428100216</v>
+        <v>0.160961821883415</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5897,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1813992530194883</v>
+        <v>0.1608506193713617</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5910,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1721664355155985</v>
+        <v>0.1603958110615249</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5923,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1702745362477729</v>
+        <v>0.1578182754973589</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5936,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.165977979793769</v>
+        <v>0.1559329730828996</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5949,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.1617144420372227</v>
+        <v>0.142136826352941</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5962,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.160548726236875</v>
+        <v>0.1420112271327061</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5975,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1591691352498623</v>
+        <v>0.1408883484035341</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1579236991637396</v>
+        <v>0.1392444540454294</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +6001,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1560730357989031</v>
+        <v>0.1299171094960583</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1558927385142801</v>
+        <v>0.1277389310575956</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +6027,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1492943793711148</v>
+        <v>0.1156273001088381</v>
       </c>
     </row>
     <row r="34">
@@ -6040,11 +6040,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1490607909920729</v>
+        <v>0.106134402203919</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +6053,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1476834725725422</v>
+        <v>0.1038183200160381</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +6066,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1434364390812606</v>
+        <v>0.1005288743794375</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +6079,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.141477787344328</v>
+        <v>0.09968889310613394</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +6092,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1326389331697615</v>
+        <v>0.09402228325438222</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +6105,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.128782645996957</v>
+        <v>0.09370761658679161</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +6118,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.1230074443286315</v>
+        <v>0.08127930939985895</v>
       </c>
     </row>
     <row r="41">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.1183116735148451</v>
+        <v>0.07872194941866106</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +6144,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.09725371808717842</v>
+        <v>0.07572692342308374</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +6157,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.09670591672826001</v>
+        <v>0.0746105968709756</v>
       </c>
     </row>
     <row r="44">
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.09443301208759403</v>
+        <v>0.07444809598034219</v>
       </c>
     </row>
     <row r="45">
@@ -6183,11 +6183,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.08944651907265522</v>
+        <v>0.07006369108004318</v>
       </c>
     </row>
     <row r="46">
@@ -6196,11 +6196,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.07311181718503645</v>
+        <v>0.04807124431972998</v>
       </c>
     </row>
     <row r="47">
@@ -6209,11 +6209,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.05251498539844945</v>
+        <v>0.0466126146370085</v>
       </c>
     </row>
     <row r="48">
@@ -6222,11 +6222,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0400575501465541</v>
+        <v>0.03224518135769872</v>
       </c>
     </row>
     <row r="49">
@@ -6235,11 +6235,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.02685289281413383</v>
+        <v>0.03167145573501529</v>
       </c>
     </row>
     <row r="50">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.008242740809141669</v>
+        <v>0.02793674948181502</v>
       </c>
     </row>
     <row r="51">
@@ -6265,7 +6265,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.004971275335964087</v>
+        <v>0.02092021476374217</v>
       </c>
     </row>
     <row r="52">
@@ -6274,20 +6274,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.0007573068389503668</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6296,7 +6296,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6334,15 +6334,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>training_rows_used</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>permutation_rows_used</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>source_variables_ranked</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>encoded_feature_count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>preprocessing_scope</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>created_at_utc</t>
         </is>
@@ -6358,14 +6373,25 @@
         <v>788</v>
       </c>
       <c r="C2" t="n">
+        <v>591</v>
+      </c>
+      <c r="D2" t="n">
+        <v>197</v>
+      </c>
+      <c r="E2" t="n">
         <v>53</v>
       </c>
-      <c r="D2" t="n">
-        <v>446</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-11 09:54:28 UTC</t>
+      <c r="F2" t="n">
+        <v>414</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>fit_on_training_split_only</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-06-14 21:59:55 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_ash.xlsx
+++ b/NN/reports/feature_importance_white_ash.xlsx
@@ -550,7 +550,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09795943275339536</v>
+        <v>0.09795943275339533</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02321682924137427</v>
+        <v>0.02321682924137426</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007607948772168915</v>
+        <v>0.007607948772168904</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02412762964736483</v>
+        <v>0.02412762964736486</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003391445003130155</v>
+        <v>0.0003391445003128593</v>
       </c>
       <c r="H9" t="n">
         <v>13</v>
@@ -809,7 +809,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005898315449532676</v>
+        <v>0.0005898315449532788</v>
       </c>
       <c r="H10" t="n">
         <v>8</v>
@@ -846,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003414091818776388</v>
+        <v>0.0003414091818776499</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -883,7 +883,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002622409575994022</v>
+        <v>0.0002622409575994133</v>
       </c>
       <c r="H12" t="n">
         <v>20</v>
@@ -920,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003118967992993826</v>
+        <v>0.0003118967992993493</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -957,7 +957,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002677155603517445</v>
+        <v>0.0002677155603517556</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -994,7 +994,7 @@
         <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003836315463246143</v>
+        <v>0.0003836315463246365</v>
       </c>
       <c r="H15" t="n">
         <v>9</v>
@@ -1031,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001394017991636964</v>
+        <v>0.0001394017991636853</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -1068,7 +1068,7 @@
         <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0002794175086170636</v>
+        <v>0.0002794175086170525</v>
       </c>
       <c r="H17" t="n">
         <v>18</v>
@@ -1105,7 +1105,7 @@
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002076550830599877</v>
+        <v>0.0002076550830599655</v>
       </c>
       <c r="H18" t="n">
         <v>21</v>
@@ -1142,7 +1142,7 @@
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003451852789800203</v>
+        <v>0.0003451852789800536</v>
       </c>
       <c r="H19" t="n">
         <v>11</v>
@@ -1179,7 +1179,7 @@
         <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003046542802608299</v>
+        <v>0.0003046542802608076</v>
       </c>
       <c r="H20" t="n">
         <v>16</v>
@@ -1253,7 +1253,7 @@
         <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001718180908426681</v>
+        <v>0.0001718180908426348</v>
       </c>
       <c r="H22" t="n">
         <v>22</v>
@@ -1290,7 +1290,7 @@
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0003204965668262783</v>
+        <v>0.0003204965668263004</v>
       </c>
       <c r="H23" t="n">
         <v>14</v>
@@ -1327,7 +1327,7 @@
         <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0007979795144487101</v>
+        <v>-0.000797979514448699</v>
       </c>
       <c r="H24" t="n">
         <v>53</v>
@@ -1364,7 +1364,7 @@
         <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>7.508100486477431e-05</v>
+        <v>7.508100486476321e-05</v>
       </c>
       <c r="H25" t="n">
         <v>30</v>
@@ -1401,7 +1401,7 @@
         <v>21</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0001431098473282488</v>
+        <v>-0.000143109847328271</v>
       </c>
       <c r="H26" t="n">
         <v>50</v>
@@ -1438,7 +1438,7 @@
         <v>29</v>
       </c>
       <c r="G27" t="n">
-        <v>4.451721783136353e-05</v>
+        <v>4.451721783134132e-05</v>
       </c>
       <c r="H27" t="n">
         <v>33</v>
@@ -1475,7 +1475,7 @@
         <v>22</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.667800517023421e-05</v>
+        <v>-1.667800517024531e-05</v>
       </c>
       <c r="H28" t="n">
         <v>42</v>
@@ -1512,7 +1512,7 @@
         <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0003785540810612442</v>
+        <v>0.0003785540810612664</v>
       </c>
       <c r="H29" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
         <v>33</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0001149755631063343</v>
+        <v>0.0001149755631063232</v>
       </c>
       <c r="H30" t="n">
         <v>25</v>
@@ -1586,7 +1586,7 @@
         <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0002799502317631264</v>
+        <v>0.0002799502317631153</v>
       </c>
       <c r="H31" t="n">
         <v>17</v>
@@ -1660,7 +1660,7 @@
         <v>25</v>
       </c>
       <c r="G33" t="n">
-        <v>-6.855343983093176e-05</v>
+        <v>-6.855343983092066e-05</v>
       </c>
       <c r="H33" t="n">
         <v>45</v>
@@ -1697,7 +1697,7 @@
         <v>24</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0002577785125864707</v>
+        <v>-0.0002577785125864818</v>
       </c>
       <c r="H34" t="n">
         <v>51</v>
@@ -1734,7 +1734,7 @@
         <v>20</v>
       </c>
       <c r="G35" t="n">
-        <v>4.514813604096224e-05</v>
+        <v>4.514813604091783e-05</v>
       </c>
       <c r="H35" t="n">
         <v>32</v>
@@ -1771,7 +1771,7 @@
         <v>17</v>
       </c>
       <c r="G36" t="n">
-        <v>3.269396022548277e-05</v>
+        <v>3.269396022550497e-05</v>
       </c>
       <c r="H36" t="n">
         <v>35</v>
@@ -1808,7 +1808,7 @@
         <v>26</v>
       </c>
       <c r="G37" t="n">
-        <v>3.301514620210888e-05</v>
+        <v>3.301514620209778e-05</v>
       </c>
       <c r="H37" t="n">
         <v>34</v>
@@ -1845,7 +1845,7 @@
         <v>13</v>
       </c>
       <c r="G38" t="n">
-        <v>3.188194014031032e-05</v>
+        <v>3.188194014028811e-05</v>
       </c>
       <c r="H38" t="n">
         <v>36</v>
@@ -1882,7 +1882,7 @@
         <v>39</v>
       </c>
       <c r="G39" t="n">
-        <v>5.396597271619674e-05</v>
+        <v>5.396597271620784e-05</v>
       </c>
       <c r="H39" t="n">
         <v>31</v>
@@ -1956,7 +1956,7 @@
         <v>41</v>
       </c>
       <c r="G41" t="n">
-        <v>9.737969164342885e-05</v>
+        <v>9.737969164343995e-05</v>
       </c>
       <c r="H41" t="n">
         <v>27</v>
@@ -1993,7 +1993,7 @@
         <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>-7.059586605757673e-05</v>
+        <v>-7.059586605756563e-05</v>
       </c>
       <c r="H42" t="n">
         <v>46</v>
@@ -2030,7 +2030,7 @@
         <v>36</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.0002784330466673035</v>
+        <v>-0.0002784330466673479</v>
       </c>
       <c r="H43" t="n">
         <v>52</v>
@@ -2067,7 +2067,7 @@
         <v>44</v>
       </c>
       <c r="G44" t="n">
-        <v>7.943631783050576e-05</v>
+        <v>7.943631783049465e-05</v>
       </c>
       <c r="H44" t="n">
         <v>28</v>
@@ -2104,7 +2104,7 @@
         <v>47</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0001032949656526116</v>
+        <v>0.0001032949656526339</v>
       </c>
       <c r="H45" t="n">
         <v>26</v>
@@ -2141,7 +2141,7 @@
         <v>43</v>
       </c>
       <c r="G46" t="n">
-        <v>2.541221249653392e-05</v>
+        <v>2.541221249652281e-05</v>
       </c>
       <c r="H46" t="n">
         <v>37</v>
@@ -2178,7 +2178,7 @@
         <v>48</v>
       </c>
       <c r="G47" t="n">
-        <v>7.591721942727947e-05</v>
+        <v>7.591721942730167e-05</v>
       </c>
       <c r="H47" t="n">
         <v>29</v>
@@ -2215,7 +2215,7 @@
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>-9.471982957667268e-05</v>
+        <v>-9.471982957668379e-05</v>
       </c>
       <c r="H48" t="n">
         <v>49</v>
@@ -2289,7 +2289,7 @@
         <v>45</v>
       </c>
       <c r="G50" t="n">
-        <v>-8.463044702849976e-05</v>
+        <v>-8.463044702848866e-05</v>
       </c>
       <c r="H50" t="n">
         <v>48</v>
@@ -2326,7 +2326,7 @@
         <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>-5.715355416913149e-06</v>
+        <v>-5.715355416946455e-06</v>
       </c>
       <c r="H51" t="n">
         <v>41</v>
@@ -2363,7 +2363,7 @@
         <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>1.367625866949274e-05</v>
+        <v>1.367625866948163e-05</v>
       </c>
       <c r="H52" t="n">
         <v>38</v>
@@ -2437,7 +2437,7 @@
         <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>-2.704625013825179e-05</v>
+        <v>-2.704625013826289e-05</v>
       </c>
       <c r="H54" t="n">
         <v>44</v>
@@ -2582,7 +2582,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09795943275339536</v>
+        <v>0.09795943275339533</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02321682924137427</v>
+        <v>0.02321682924137426</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -2730,7 +2730,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007607948772168915</v>
+        <v>0.007607948772168904</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -2767,7 +2767,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02412762964736483</v>
+        <v>0.02412762964736486</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -2804,7 +2804,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003391445003130155</v>
+        <v>0.0003391445003128593</v>
       </c>
       <c r="H9" t="n">
         <v>13</v>
@@ -2841,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005898315449532676</v>
+        <v>0.0005898315449532788</v>
       </c>
       <c r="H10" t="n">
         <v>8</v>
@@ -2878,7 +2878,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003414091818776388</v>
+        <v>0.0003414091818776499</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -2915,7 +2915,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002622409575994022</v>
+        <v>0.0002622409575994133</v>
       </c>
       <c r="H12" t="n">
         <v>20</v>
@@ -2952,7 +2952,7 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003118967992993826</v>
+        <v>0.0003118967992993493</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -2989,7 +2989,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002677155603517445</v>
+        <v>0.0002677155603517556</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -3026,7 +3026,7 @@
         <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003836315463246143</v>
+        <v>0.0003836315463246365</v>
       </c>
       <c r="H15" t="n">
         <v>9</v>
@@ -3063,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001394017991636964</v>
+        <v>0.0001394017991636853</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -3100,7 +3100,7 @@
         <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0002794175086170636</v>
+        <v>0.0002794175086170525</v>
       </c>
       <c r="H17" t="n">
         <v>18</v>
@@ -3137,7 +3137,7 @@
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002076550830599877</v>
+        <v>0.0002076550830599655</v>
       </c>
       <c r="H18" t="n">
         <v>21</v>
@@ -3174,7 +3174,7 @@
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003451852789800203</v>
+        <v>0.0003451852789800536</v>
       </c>
       <c r="H19" t="n">
         <v>11</v>
@@ -3211,7 +3211,7 @@
         <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003046542802608299</v>
+        <v>0.0003046542802608076</v>
       </c>
       <c r="H20" t="n">
         <v>16</v>
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09795943275339536</v>
+        <v>0.09795943275339533</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008682725788401426</v>
+        <v>0.008682725788401445</v>
       </c>
     </row>
     <row r="4">
@@ -4784,7 +4784,7 @@
         <v>0.05354981604745403</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005935131558129029</v>
+        <v>0.005935131558128987</v>
       </c>
     </row>
     <row r="5">
@@ -4800,7 +4800,7 @@
         <v>0.0267286212150805</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003212245253402749</v>
+        <v>0.00321224525340277</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02412762964736483</v>
+        <v>0.02412762964736486</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002811931222986497</v>
+        <v>0.002811931222986509</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02321682924137427</v>
+        <v>0.02321682924137426</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003626306122843932</v>
+        <v>0.003626306122843931</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007607948772168915</v>
+        <v>0.007607948772168904</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002231029644669918</v>
+        <v>0.002231029644669934</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0005898315449532676</v>
+        <v>0.0005898315449532788</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004752076410622965</v>
+        <v>0.0004752076410622969</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0003836315463246143</v>
+        <v>0.0003836315463246365</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001569891301369052</v>
+        <v>0.0001569891301368575</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0003785540810612442</v>
+        <v>0.0003785540810612664</v>
       </c>
       <c r="D11" t="n">
-        <v>9.320889179858812e-05</v>
+        <v>9.320889179857302e-05</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0003451852789800203</v>
+        <v>0.0003451852789800536</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0001229530453033242</v>
+        <v>0.0001229530453033222</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0003414091818776388</v>
+        <v>0.0003414091818776499</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001949165249264165</v>
+        <v>0.0001949165249263923</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0003391445003130155</v>
+        <v>0.0003391445003128593</v>
       </c>
       <c r="D14" t="n">
-        <v>3.707081220569008e-05</v>
+        <v>3.707081220570067e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0003204965668262783</v>
+        <v>0.0003204965668263004</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001922446410491603</v>
+        <v>0.0001922446410491312</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0003118967992993826</v>
+        <v>0.0003118967992993493</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0003173268004239832</v>
+        <v>0.0003173268004240187</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0003046542802608299</v>
+        <v>0.0003046542802608076</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001439406965768496</v>
+        <v>0.0001439406965768579</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0002799502317631264</v>
+        <v>0.0002799502317631153</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001280604313256435</v>
+        <v>0.0001280604313256441</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0002794175086170636</v>
+        <v>0.0002794175086170525</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0003944946494375706</v>
+        <v>0.0003944946494375634</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0002677155603517445</v>
+        <v>0.0002677155603517556</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001647124028711472</v>
+        <v>0.0001647124028711367</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0002622409575994022</v>
+        <v>0.0002622409575994133</v>
       </c>
       <c r="D21" t="n">
-        <v>7.740803687130581e-05</v>
+        <v>7.740803687131447e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0002076550830599877</v>
+        <v>0.0002076550830599655</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001455212522585836</v>
+        <v>0.0001455212522585809</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0001718180908426681</v>
+        <v>0.0001718180908426348</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001570658298068233</v>
+        <v>0.0001570658298068005</v>
       </c>
     </row>
     <row r="24">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0001394017991636964</v>
+        <v>0.0001394017991636853</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000220205941170529</v>
+        <v>0.0002202059411705579</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0001149755631063343</v>
+        <v>0.0001149755631063232</v>
       </c>
       <c r="D26" t="n">
-        <v>6.155517252700753e-05</v>
+        <v>6.155517252706295e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0001032949656526116</v>
+        <v>0.0001032949656526339</v>
       </c>
       <c r="D27" t="n">
-        <v>6.520066052022178e-05</v>
+        <v>6.520066052020055e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9.737969164342885e-05</v>
+        <v>9.737969164343995e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>4.872398371474235e-05</v>
+        <v>4.872398371471293e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5181,10 +5181,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.943631783050576e-05</v>
+        <v>7.943631783049465e-05</v>
       </c>
       <c r="D29" t="n">
-        <v>5.051636987226809e-05</v>
+        <v>5.051636987226733e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.591721942727947e-05</v>
+        <v>7.591721942730167e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>6.203837256941819e-05</v>
+        <v>6.203837256942163e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7.508100486477431e-05</v>
+        <v>7.508100486476321e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001249166349489409</v>
+        <v>0.0001249166349489615</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5.396597271619674e-05</v>
+        <v>5.396597271620784e-05</v>
       </c>
       <c r="D32" t="n">
-        <v>7.491467483872107e-05</v>
+        <v>7.491467483872731e-05</v>
       </c>
     </row>
     <row r="33">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.514813604096224e-05</v>
+        <v>4.514813604091783e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>2.601168765519987e-05</v>
+        <v>2.601168765522396e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4.451721783136353e-05</v>
+        <v>4.451721783134132e-05</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001464450104960018</v>
+        <v>0.0001464450104960041</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3.301514620210888e-05</v>
+        <v>3.301514620209778e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>6.669297915275336e-05</v>
+        <v>6.669297915273512e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.269396022548277e-05</v>
+        <v>3.269396022550497e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>2.519865399273078e-05</v>
+        <v>2.519865399270891e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3.188194014031032e-05</v>
+        <v>3.188194014028811e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>2.528221235999303e-05</v>
+        <v>2.52822123599876e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.541221249653392e-05</v>
+        <v>2.541221249652281e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>5.84706564231459e-05</v>
+        <v>5.847065642315276e-05</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.367625866949274e-05</v>
+        <v>1.367625866948163e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>7.824739093467306e-06</v>
+        <v>7.824739093504678e-06</v>
       </c>
     </row>
     <row r="40">
@@ -5360,7 +5360,7 @@
         <v>9.887444687772806e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001154125676430098</v>
+        <v>0.0001154125676429848</v>
       </c>
     </row>
     <row r="41">
@@ -5376,7 +5376,7 @@
         <v>-3.37317632691514e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>3.103601093983625e-06</v>
+        <v>3.103601093988273e-06</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-5.715355416913149e-06</v>
+        <v>-5.715355416946455e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>1.861720893452239e-05</v>
+        <v>1.861720893452552e-05</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-1.667800517023421e-05</v>
+        <v>-1.667800517024531e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0003124043520494461</v>
+        <v>0.0003124043520494439</v>
       </c>
     </row>
     <row r="44">
@@ -5424,7 +5424,7 @@
         <v>-2.377115489509141e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001786426619872065</v>
+        <v>0.0001786426619872305</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-2.704625013825179e-05</v>
+        <v>-2.704625013826289e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>1.552544431576424e-05</v>
+        <v>1.552544431575823e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-6.855343983093176e-05</v>
+        <v>-6.855343983092066e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0001749117956052541</v>
+        <v>0.0001749117956052606</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-7.059586605757673e-05</v>
+        <v>-7.059586605756563e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0001541723545647746</v>
+        <v>0.000154172354564766</v>
       </c>
     </row>
     <row r="48">
@@ -5488,7 +5488,7 @@
         <v>-7.676763974000523e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>9.031310258090133e-05</v>
+        <v>9.031310258090518e-05</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-8.463044702849976e-05</v>
+        <v>-8.463044702848866e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>3.332377236627358e-05</v>
+        <v>3.332377236625676e-05</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-9.471982957667268e-05</v>
+        <v>-9.471982957668379e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001419861488978549</v>
+        <v>0.0001419861488978646</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.0001431098473282488</v>
+        <v>-0.000143109847328271</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0001179461880385185</v>
+        <v>0.0001179461880385015</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0002577785125864707</v>
+        <v>-0.0002577785125864818</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0001257590458424681</v>
+        <v>0.0001257590458424292</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0002784330466673035</v>
+        <v>-0.0002784330466673479</v>
       </c>
       <c r="D53" t="n">
-        <v>8.788422570898574e-05</v>
+        <v>8.788422570899487e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0007979795144487101</v>
+        <v>-0.000797979514448699</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003239428442837587</v>
+        <v>0.0003239428442837299</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 21:59:55 UTC</t>
+          <t>2026-06-15 07:24:57 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_ash.xlsx
+++ b/NN/reports/feature_importance_white_ash.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,35 +497,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6800252181377466</v>
+        <v>0.1887256363355426</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5404917126438302</v>
+        <v>0.1521486878328943</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.707635805653452</v>
+        <v>0.2154246116620057</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.218640274671984</v>
+        <v>0.6024653931586257</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -534,35 +534,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07392078499358473</v>
+        <v>0.1420745617409387</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08883728100634161</v>
+        <v>0.1365515247217552</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09795943275339533</v>
+        <v>0.1088415266228941</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5949108055762866</v>
+        <v>0.6816869476946867</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -571,35 +571,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06370161228148555</v>
+        <v>0.1036036164221331</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06733485589348111</v>
+        <v>0.04880593020395663</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05354981604745403</v>
+        <v>0.1234950401155566</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6834105794958298</v>
+        <v>0.9621316924038448</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="5">
@@ -608,35 +608,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05278192226816866</v>
+        <v>0.08324052845910307</v>
       </c>
       <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2850487579936362</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.009544224846933692</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.101184650283743</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.06908023621794038</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0267286212150805</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.5327029817778945</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -645,35 +645,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03043172378276767</v>
+        <v>0.07080544393170783</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0200995544193493</v>
+        <v>0.1294691036035181</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02321682924137426</v>
+        <v>0.04068447534612057</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9740681227027399</v>
+        <v>0.5395616793636768</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -682,35 +682,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0137604941032536</v>
+        <v>0.02238603911108551</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.103426408421673</v>
+        <v>0.01752359950529689</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007607948772168904</v>
+        <v>0.0193915821436946</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4455611388869869</v>
+        <v>0.5671407408639033</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="8">
@@ -723,31 +723,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0515097571401515</v>
+        <v>0.0770237695356389</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006375094879893506</v>
+        <v>0.01256455187584946</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02412762964736486</v>
+        <v>0.04146228699703602</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.44686686725841</v>
+        <v>0.4390111655153612</v>
       </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.00171362734339567</v>
+        <v>0.1074433402182227</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03253781330641893</v>
+        <v>0.04099540415835496</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003391445003128593</v>
+        <v>0.07313631731292095</v>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.201473366213727</v>
+        <v>0.1300828311467801</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>7.75</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="10">
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002315328377349986</v>
+        <v>0.02116261349918513</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007884245401468069</v>
+        <v>0.01826404347092722</v>
       </c>
       <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.007081922240861027</v>
+      </c>
+      <c r="H10" t="n">
         <v>10</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0005898315449532788</v>
-      </c>
-      <c r="H10" t="n">
-        <v>8</v>
-      </c>
       <c r="I10" t="n">
-        <v>0.5644010612379948</v>
+        <v>0.2855334252973867</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001410847217638958</v>
+        <v>0.01255965703293054</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009682915578592115</v>
+        <v>0.02779300581058208</v>
       </c>
       <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.00116731946576254</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3584051527160685</v>
+      </c>
+      <c r="J11" t="n">
         <v>9</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.0003414091818776499</v>
-      </c>
-      <c r="H11" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.6077038077134711</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
       <c r="K11" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001127989024976822</v>
+        <v>0.01222738315544579</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005239581557694383</v>
+        <v>0.007523539457223542</v>
       </c>
       <c r="F12" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.003669765706062567</v>
+      </c>
+      <c r="H12" t="n">
         <v>12</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.0002622409575994133</v>
-      </c>
-      <c r="H12" t="n">
-        <v>20</v>
-      </c>
       <c r="I12" t="n">
-        <v>0.3562349381719732</v>
+        <v>0.1988847543436636</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001931453353223641</v>
+        <v>0.0040256475836703</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0101044505328351</v>
+        <v>0.02493966697959183</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003118967992993493</v>
+        <v>0.002347657338847642</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1392444540454294</v>
+        <v>0.6000338949969537</v>
       </c>
       <c r="J13" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>15.25</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0007530207133825601</v>
+        <v>0.01794369145717459</v>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001732056320379423</v>
+        <v>0.007577637070931578</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002677155603517556</v>
+        <v>0.009675222109604443</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2985215123421208</v>
+        <v>0.09070745312095241</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="K14" t="n">
-        <v>18</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="15">
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0009714177272542936</v>
+        <v>0.01110082680568815</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001045429611593098</v>
+        <v>0.004065159766783968</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003836315463246365</v>
+        <v>0.002200612697474002</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1608506193713617</v>
+        <v>0.1622920319430938</v>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
-        <v>18.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.000753187083975863</v>
+        <v>0.0091534412157659</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001562364279675974</v>
+        <v>0.005712197148551049</v>
       </c>
       <c r="F16" t="n">
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001394017991636853</v>
+        <v>0.004257424079439265</v>
       </c>
       <c r="H16" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3028255227289747</v>
+        <v>0.1426148604252817</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>19</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001662572814679323</v>
+        <v>0.00708503912188317</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001231933398416441</v>
+        <v>0.004018221113907879</v>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0002794175086170525</v>
+        <v>0.0004731324973604401</v>
       </c>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1156273001088381</v>
+        <v>0.202752008909449</v>
       </c>
       <c r="J17" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>20</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0008749662157914575</v>
+        <v>0.00495329366890413</v>
       </c>
       <c r="D18" t="n">
+        <v>22</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.003772135730873312</v>
+      </c>
+      <c r="F18" t="n">
         <v>19</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.001285376198568808</v>
-      </c>
-      <c r="F18" t="n">
-        <v>18</v>
-      </c>
       <c r="G18" t="n">
-        <v>0.0002076550830599655</v>
+        <v>0.001557680894965208</v>
       </c>
       <c r="H18" t="n">
         <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.142136826352941</v>
+        <v>0.1818766355602026</v>
       </c>
       <c r="J18" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K18" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0008170537327478026</v>
+        <v>0.01356968019450394</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0009767968116605645</v>
+        <v>0.007136391318386267</v>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003451852789800536</v>
+        <v>-0.000356172619705486</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1578182754973589</v>
+        <v>0.2887485604509674</v>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0009295933489872375</v>
+        <v>0.006220683136873107</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0008239475207759243</v>
+        <v>0.003595695699161286</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003046542802608076</v>
+        <v>0.0004374426895113359</v>
       </c>
       <c r="H20" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
-        <v>0.160961821883415</v>
+        <v>0.1941174532058252</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>23</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0009548430510591239</v>
+        <v>0.005593866533387598</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001147792281952532</v>
+        <v>0.00312639717490473</v>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.377115489509141e-05</v>
+        <v>0.001158717634249862</v>
       </c>
       <c r="H21" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2031090687824775</v>
+        <v>0.1819457259261128</v>
       </c>
       <c r="J21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>24.25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0007364780952855083</v>
+        <v>0.008109665704164904</v>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0009365356081720283</v>
+        <v>0.001678725102212855</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001718180908426348</v>
+        <v>0.001815440161301596</v>
       </c>
       <c r="H22" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1759561832904888</v>
+        <v>0.1566058110248951</v>
       </c>
       <c r="J22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>25.25</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.000764784068205422</v>
+        <v>0.004129327630145909</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0008940465367908252</v>
+        <v>0.002762938626936052</v>
       </c>
       <c r="F23" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0003204965668263004</v>
+        <v>0.001854788330938895</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1299171094960583</v>
+        <v>0.1473970865416119</v>
       </c>
       <c r="J23" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K23" t="n">
-        <v>25.5</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001278061659875439</v>
+        <v>0.004564996773249123</v>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E24" t="n">
-        <v>0.002266155656213529</v>
+        <v>0.003450417184599063</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.000797979514448699</v>
+        <v>0.0005228209926651961</v>
       </c>
       <c r="H24" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1603958110615249</v>
+        <v>0.137194221917365</v>
       </c>
       <c r="J24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>25.75</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="25">
@@ -1348,35 +1348,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0007388168646070414</v>
+        <v>0.008376341143111856</v>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000914489129873333</v>
+        <v>0.003571426468083794</v>
       </c>
       <c r="F25" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>7.508100486476321e-05</v>
+        <v>-0.0007288706209371387</v>
       </c>
       <c r="H25" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1908368699036518</v>
+        <v>0.1700856585894175</v>
       </c>
       <c r="J25" t="n">
         <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>27.25</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0007492711216848783</v>
+        <v>0.005460930679095976</v>
       </c>
       <c r="D26" t="n">
+        <v>21</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.003372041766189656</v>
+      </c>
+      <c r="F26" t="n">
+        <v>23</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0005601140805585825</v>
+      </c>
+      <c r="H26" t="n">
         <v>27</v>
       </c>
-      <c r="E26" t="n">
-        <v>0.001151634058644568</v>
-      </c>
-      <c r="F26" t="n">
-        <v>21</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.000143109847328271</v>
-      </c>
-      <c r="H26" t="n">
-        <v>50</v>
-      </c>
       <c r="I26" t="n">
-        <v>0.1973511154055063</v>
+        <v>0.09742503609965758</v>
       </c>
       <c r="J26" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K26" t="n">
-        <v>28.25</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0008731865929501511</v>
+        <v>0.003942589456721862</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0009843768218952846</v>
+        <v>0.001690670480360779</v>
       </c>
       <c r="F27" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>4.451721783134132e-05</v>
+        <v>0.00122806842735762</v>
       </c>
       <c r="H27" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I27" t="n">
-        <v>0.106134402203919</v>
+        <v>0.1678988720230379</v>
       </c>
       <c r="J27" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="K27" t="n">
-        <v>28.75</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -1459,35 +1459,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001235049220102229</v>
+        <v>0.004045270483074639</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E28" t="n">
-        <v>0.00114859057407371</v>
+        <v>0.002194166745328697</v>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.667800517024531e-05</v>
+        <v>0.00171971692051659</v>
       </c>
       <c r="H28" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09370761658679161</v>
+        <v>0.1067579909826857</v>
       </c>
       <c r="J28" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
-        <v>29</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0006949505915132396</v>
+        <v>0.001746298113170297</v>
       </c>
       <c r="D29" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0008045754841196324</v>
+        <v>0.0149169762005839</v>
       </c>
       <c r="F29" t="n">
+        <v>11</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.001854266814861505</v>
+      </c>
+      <c r="H29" t="n">
+        <v>17</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.0620183183041334</v>
+      </c>
+      <c r="J29" t="n">
         <v>38</v>
       </c>
-      <c r="G29" t="n">
-        <v>0.0003785540810612664</v>
-      </c>
-      <c r="H29" t="n">
-        <v>10</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09402228325438222</v>
-      </c>
-      <c r="J29" t="n">
-        <v>37</v>
-      </c>
       <c r="K29" t="n">
-        <v>29</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.000680633210097839</v>
+        <v>0.004230931609307848</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0009270566805049732</v>
+        <v>0.001660640897440414</v>
       </c>
       <c r="F30" t="n">
+        <v>35</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.001753806644895284</v>
+      </c>
+      <c r="H30" t="n">
+        <v>19</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.08173331081734592</v>
+      </c>
+      <c r="J30" t="n">
         <v>33</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.0001149755631063232</v>
-      </c>
-      <c r="H30" t="n">
-        <v>25</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.1420112271327061</v>
-      </c>
-      <c r="J30" t="n">
-        <v>27</v>
-      </c>
       <c r="K30" t="n">
-        <v>29.25</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0006771796699707807</v>
+        <v>0.004513287600545732</v>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001066974667715616</v>
+        <v>0.002593552130038242</v>
       </c>
       <c r="F31" t="n">
         <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0002799502317631153</v>
+        <v>0.0003738514379423741</v>
       </c>
       <c r="H31" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I31" t="n">
-        <v>0.07572692342308374</v>
+        <v>0.09858140517611114</v>
       </c>
       <c r="J31" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="K31" t="n">
-        <v>29.5</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0007528476815906711</v>
+        <v>0.003676835935823874</v>
       </c>
       <c r="D32" t="n">
+        <v>32</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.001585985869050237</v>
+      </c>
+      <c r="F32" t="n">
+        <v>36</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0009890090611721302</v>
+      </c>
+      <c r="H32" t="n">
         <v>26</v>
       </c>
-      <c r="E32" t="n">
-        <v>0.000936578222737565</v>
-      </c>
-      <c r="F32" t="n">
-        <v>31</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.0001678774978638109</v>
-      </c>
-      <c r="H32" t="n">
-        <v>23</v>
-      </c>
       <c r="I32" t="n">
-        <v>0.08127930939985895</v>
+        <v>0.1613503572422621</v>
       </c>
       <c r="J32" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="K32" t="n">
-        <v>29.75</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="33">
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0007650726116266919</v>
+        <v>0.004525678610649985</v>
       </c>
       <c r="D33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E33" t="n">
-        <v>0.001095407100862121</v>
+        <v>0.001363792424073551</v>
       </c>
       <c r="F33" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="G33" t="n">
-        <v>-6.855343983092066e-05</v>
+        <v>0.002313667322257817</v>
       </c>
       <c r="H33" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1005288743794375</v>
+        <v>0.03383869674795958</v>
       </c>
       <c r="J33" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K33" t="n">
-        <v>31.75</v>
+        <v>29.25</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0006396837141306384</v>
+        <v>0.003893566694808915</v>
       </c>
       <c r="D34" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001114783575473459</v>
+        <v>0.001468228851051083</v>
       </c>
       <c r="F34" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0002577785125864818</v>
+        <v>0.001464157095111918</v>
       </c>
       <c r="H34" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1958234914034658</v>
+        <v>0.04786084275164715</v>
       </c>
       <c r="J34" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="K34" t="n">
-        <v>31.75</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="35">
@@ -1722,31 +1722,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8.562452054369228e-05</v>
+        <v>0.0003038200630622453</v>
       </c>
       <c r="D35" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E35" t="n">
-        <v>0.001182741465926917</v>
+        <v>0.003060533353637416</v>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>4.514813604091783e-05</v>
+        <v>-0.0001852744188726718</v>
       </c>
       <c r="H35" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1408883484035341</v>
+        <v>0.1400777777885083</v>
       </c>
       <c r="J35" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>32.25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="36">
@@ -1755,32 +1755,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7.506604669526684e-05</v>
+        <v>0.003256094873574887</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001476740898676021</v>
+        <v>0.001743955361656358</v>
       </c>
       <c r="F36" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G36" t="n">
-        <v>3.269396022550497e-05</v>
+        <v>0.0002535083457601006</v>
       </c>
       <c r="H36" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1277389310575956</v>
+        <v>0.07216616430500356</v>
       </c>
       <c r="J36" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K36" t="n">
         <v>33.25</v>
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0004917288969004438</v>
+        <v>0.0002260105365881688</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E37" t="n">
-        <v>0.001077189467018785</v>
+        <v>0.002481348547534156</v>
       </c>
       <c r="F37" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G37" t="n">
-        <v>3.301514620209778e-05</v>
+        <v>4.58058941945727e-05</v>
       </c>
       <c r="H37" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1038183200160381</v>
+        <v>0.1109769442419932</v>
       </c>
       <c r="J37" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K37" t="n">
-        <v>33.75</v>
+        <v>33.25</v>
       </c>
     </row>
     <row r="38">
@@ -1829,35 +1829,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0001184967251699587</v>
+        <v>0.002865749745253993</v>
       </c>
       <c r="D38" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="E38" t="n">
-        <v>0.003100019448663352</v>
+        <v>0.001765385230591706</v>
       </c>
       <c r="F38" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G38" t="n">
-        <v>3.188194014028811e-05</v>
+        <v>7.982958698583564e-05</v>
       </c>
       <c r="H38" t="n">
+        <v>34</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.07434657562092495</v>
+      </c>
+      <c r="J38" t="n">
         <v>36</v>
       </c>
-      <c r="I38" t="n">
-        <v>0.07872194941866106</v>
-      </c>
-      <c r="J38" t="n">
-        <v>40</v>
-      </c>
       <c r="K38" t="n">
-        <v>34</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0007156167008854237</v>
+        <v>0.00294892951993711</v>
       </c>
       <c r="D39" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0008004214651009396</v>
+        <v>0.001211045960421835</v>
       </c>
       <c r="F39" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>5.396597271620784e-05</v>
+        <v>0.000191604288994196</v>
       </c>
       <c r="H39" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0746105968709756</v>
+        <v>0.1055627686810054</v>
       </c>
       <c r="J39" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="K39" t="n">
-        <v>35.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.000667528872681199</v>
+        <v>0.00232013926897213</v>
       </c>
       <c r="D40" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E40" t="n">
-        <v>0.000623085078194488</v>
+        <v>0.00171031580369273</v>
       </c>
       <c r="F40" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G40" t="n">
-        <v>-7.676763974000523e-05</v>
+        <v>-0.0003614879095182877</v>
       </c>
       <c r="H40" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1647514728112884</v>
+        <v>0.07767109781360348</v>
       </c>
       <c r="J40" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K40" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="41">
@@ -1940,35 +1940,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0005384728880622172</v>
+        <v>0.002290547722010455</v>
       </c>
       <c r="D41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0006650763710833805</v>
+        <v>0.001143116203853851</v>
       </c>
       <c r="F41" t="n">
         <v>41</v>
       </c>
       <c r="G41" t="n">
-        <v>9.737969164343995e-05</v>
+        <v>-7.045442892575915e-05</v>
       </c>
       <c r="H41" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I41" t="n">
-        <v>0.09968889310613394</v>
+        <v>0.07443367943814927</v>
       </c>
       <c r="J41" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K41" t="n">
-        <v>36</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0006701088738634766</v>
+        <v>0.0001216287670557282</v>
       </c>
       <c r="D42" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0006842171394645225</v>
+        <v>0.001283508655007311</v>
       </c>
       <c r="F42" t="n">
+        <v>39</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.929368774837627e-05</v>
+      </c>
+      <c r="H42" t="n">
+        <v>37</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.03951371912528678</v>
+      </c>
+      <c r="J42" t="n">
         <v>40</v>
       </c>
-      <c r="G42" t="n">
-        <v>-7.059586605756563e-05</v>
-      </c>
-      <c r="H42" t="n">
-        <v>46</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.1559329730828996</v>
-      </c>
-      <c r="J42" t="n">
-        <v>25</v>
-      </c>
       <c r="K42" t="n">
-        <v>36.25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0006088353991203538</v>
+        <v>0.002773423062589148</v>
       </c>
       <c r="D43" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0008351610162686362</v>
+        <v>0.00111164760445486</v>
       </c>
       <c r="F43" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.0002784330466673479</v>
+        <v>-0.0003790091634006343</v>
       </c>
       <c r="H43" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1739358867039082</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="K43" t="n">
-        <v>36.25</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0004512986664809379</v>
+        <v>0.0005323178190829865</v>
       </c>
       <c r="D44" t="n">
+        <v>40</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0008142332393203022</v>
+      </c>
+      <c r="F44" t="n">
         <v>43</v>
       </c>
-      <c r="E44" t="n">
-        <v>0.0004959209443196723</v>
-      </c>
-      <c r="F44" t="n">
-        <v>44</v>
-      </c>
       <c r="G44" t="n">
-        <v>7.943631783049465e-05</v>
+        <v>-0.0002079511254434285</v>
       </c>
       <c r="H44" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0466126146370085</v>
+        <v>0.001225907812150817</v>
       </c>
       <c r="J44" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="K44" t="n">
-        <v>40.25</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="45">
@@ -2088,32 +2088,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0004718788337140494</v>
+        <v>0.0001855570732839209</v>
       </c>
       <c r="D45" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0004455040804141887</v>
+        <v>0.0002519691588108682</v>
       </c>
       <c r="F45" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0001032949656526339</v>
+        <v>4.713116728115585e-05</v>
       </c>
       <c r="H45" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="K45" t="n">
         <v>41.5</v>
@@ -2125,331 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0005432771320032983</v>
+        <v>6.130195493366994e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0005849586898043011</v>
+        <v>0.0004817274979841906</v>
       </c>
       <c r="F46" t="n">
+        <v>44</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-1.386100759229736e-05</v>
+      </c>
+      <c r="H46" t="n">
+        <v>38</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
         <v>43</v>
       </c>
-      <c r="G46" t="n">
-        <v>2.541221249652281e-05</v>
-      </c>
-      <c r="H46" t="n">
-        <v>37</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.03224518135769872</v>
-      </c>
-      <c r="J46" t="n">
-        <v>47</v>
-      </c>
       <c r="K46" t="n">
-        <v>41.5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.0002296868419742113</v>
-      </c>
-      <c r="D47" t="n">
-        <v>45</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.0004402655751033603</v>
-      </c>
-      <c r="F47" t="n">
-        <v>48</v>
-      </c>
-      <c r="G47" t="n">
-        <v>7.591721942730167e-05</v>
-      </c>
-      <c r="H47" t="n">
-        <v>29</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.03167145573501529</v>
-      </c>
-      <c r="J47" t="n">
-        <v>48</v>
-      </c>
-      <c r="K47" t="n">
         <v>42.5</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>filtercake_sugar</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0006392316186347107</v>
-      </c>
-      <c r="D48" t="n">
-        <v>37</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.0004585252415905689</v>
-      </c>
-      <c r="F48" t="n">
-        <v>46</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-9.471982957668379e-05</v>
-      </c>
-      <c r="H48" t="n">
-        <v>49</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.07006369108004318</v>
-      </c>
-      <c r="J48" t="n">
-        <v>44</v>
-      </c>
-      <c r="K48" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>boiling_r3_q</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0004077400538995397</v>
-      </c>
-      <c r="D49" t="n">
-        <v>44</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.0003989023369340952</v>
-      </c>
-      <c r="F49" t="n">
-        <v>51</v>
-      </c>
-      <c r="G49" t="n">
-        <v>9.887444687772806e-06</v>
-      </c>
-      <c r="H49" t="n">
-        <v>39</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.07444809598034219</v>
-      </c>
-      <c r="J49" t="n">
-        <v>43</v>
-      </c>
-      <c r="K49" t="n">
-        <v>44.25</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.000192427640655558</v>
-      </c>
-      <c r="D50" t="n">
-        <v>46</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.000473015342762744</v>
-      </c>
-      <c r="F50" t="n">
-        <v>45</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-8.463044702848866e-05</v>
-      </c>
-      <c r="H50" t="n">
-        <v>48</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.04807124431972998</v>
-      </c>
-      <c r="J50" t="n">
-        <v>45</v>
-      </c>
-      <c r="K50" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0001146541490661912</v>
-      </c>
-      <c r="D51" t="n">
-        <v>48</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.0004139810386876009</v>
-      </c>
-      <c r="F51" t="n">
-        <v>49</v>
-      </c>
-      <c r="G51" t="n">
-        <v>-5.715355416946455e-06</v>
-      </c>
-      <c r="H51" t="n">
-        <v>41</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.02092021476374217</v>
-      </c>
-      <c r="J51" t="n">
-        <v>50</v>
-      </c>
-      <c r="K51" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1.221535404480305e-05</v>
-      </c>
-      <c r="D52" t="n">
-        <v>52</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.0004128940098443284</v>
-      </c>
-      <c r="F52" t="n">
-        <v>50</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1.367625866948163e-05</v>
-      </c>
-      <c r="H52" t="n">
-        <v>38</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.02793674948181502</v>
-      </c>
-      <c r="J52" t="n">
-        <v>49</v>
-      </c>
-      <c r="K52" t="n">
-        <v>47.25</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>6.773975045052927e-06</v>
-      </c>
-      <c r="D53" t="n">
-        <v>53</v>
-      </c>
-      <c r="E53" t="n">
-        <v>8.802555512954454e-05</v>
-      </c>
-      <c r="F53" t="n">
-        <v>53</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-3.37317632691514e-06</v>
-      </c>
-      <c r="H53" t="n">
-        <v>40</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>51</v>
-      </c>
-      <c r="K53" t="n">
-        <v>49.25</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>2.590899729806618e-05</v>
-      </c>
-      <c r="D54" t="n">
-        <v>51</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.0002023044353954326</v>
-      </c>
-      <c r="F54" t="n">
-        <v>52</v>
-      </c>
-      <c r="G54" t="n">
-        <v>-2.704625013826289e-05</v>
-      </c>
-      <c r="H54" t="n">
-        <v>44</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>51</v>
-      </c>
-      <c r="K54" t="n">
-        <v>49.5</v>
       </c>
     </row>
   </sheetData>
@@ -2529,35 +2233,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6800252181377466</v>
+        <v>0.1887256363355426</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5404917126438302</v>
+        <v>0.1521486878328943</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.707635805653452</v>
+        <v>0.2154246116620057</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.218640274671984</v>
+        <v>0.6024653931586257</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2566,35 +2270,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07392078499358473</v>
+        <v>0.1420745617409387</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08883728100634161</v>
+        <v>0.1365515247217552</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09795943275339533</v>
+        <v>0.1088415266228941</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5949108055762866</v>
+        <v>0.6816869476946867</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2603,35 +2307,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06370161228148555</v>
+        <v>0.1036036164221331</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06733485589348111</v>
+        <v>0.04880593020395663</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05354981604745403</v>
+        <v>0.1234950401155566</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6834105794958298</v>
+        <v>0.9621316924038448</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="5">
@@ -2640,35 +2344,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05278192226816866</v>
+        <v>0.08324052845910307</v>
       </c>
       <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2850487579936362</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.009544224846933692</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.101184650283743</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.06908023621794038</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0267286212150805</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.5327029817778945</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2677,35 +2381,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03043172378276767</v>
+        <v>0.07080544393170783</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0200995544193493</v>
+        <v>0.1294691036035181</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02321682924137426</v>
+        <v>0.04068447534612057</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9740681227027399</v>
+        <v>0.5395616793636768</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -2714,35 +2418,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0137604941032536</v>
+        <v>0.02238603911108551</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.103426408421673</v>
+        <v>0.01752359950529689</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007607948772168904</v>
+        <v>0.0193915821436946</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4455611388869869</v>
+        <v>0.5671407408639033</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="8">
@@ -2755,31 +2459,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0515097571401515</v>
+        <v>0.0770237695356389</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006375094879893506</v>
+        <v>0.01256455187584946</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02412762964736486</v>
+        <v>0.04146228699703602</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.44686686725841</v>
+        <v>0.4390111655153612</v>
       </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="9">
@@ -2788,35 +2492,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.00171362734339567</v>
+        <v>0.1074433402182227</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03253781330641893</v>
+        <v>0.04099540415835496</v>
       </c>
       <c r="F9" t="n">
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003391445003128593</v>
+        <v>0.07313631731292095</v>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.201473366213727</v>
+        <v>0.1300828311467801</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>7.75</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="10">
@@ -2825,35 +2529,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002315328377349986</v>
+        <v>0.02116261349918513</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007884245401468069</v>
+        <v>0.01826404347092722</v>
       </c>
       <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.007081922240861027</v>
+      </c>
+      <c r="H10" t="n">
         <v>10</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.0005898315449532788</v>
-      </c>
-      <c r="H10" t="n">
-        <v>8</v>
-      </c>
       <c r="I10" t="n">
-        <v>0.5644010612379948</v>
+        <v>0.2855334252973867</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K10" t="n">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="11">
@@ -2862,35 +2566,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001410847217638958</v>
+        <v>0.01255965703293054</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009682915578592115</v>
+        <v>0.02779300581058208</v>
       </c>
       <c r="F11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.00116731946576254</v>
+      </c>
+      <c r="H11" t="n">
+        <v>24</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3584051527160685</v>
+      </c>
+      <c r="J11" t="n">
         <v>9</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.0003414091818776499</v>
-      </c>
-      <c r="H11" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.6077038077134711</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
       <c r="K11" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -2899,35 +2603,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001127989024976822</v>
+        <v>0.01222738315544579</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005239581557694383</v>
+        <v>0.007523539457223542</v>
       </c>
       <c r="F12" t="n">
+        <v>14</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.003669765706062567</v>
+      </c>
+      <c r="H12" t="n">
         <v>12</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.0002622409575994133</v>
-      </c>
-      <c r="H12" t="n">
-        <v>20</v>
-      </c>
       <c r="I12" t="n">
-        <v>0.3562349381719732</v>
+        <v>0.1988847543436636</v>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -2936,35 +2640,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001931453353223641</v>
+        <v>0.0040256475836703</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0101044505328351</v>
+        <v>0.02493966697959183</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003118967992993493</v>
+        <v>0.002347657338847642</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1392444540454294</v>
+        <v>0.6000338949969537</v>
       </c>
       <c r="J13" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>15.25</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="14">
@@ -2973,35 +2677,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0007530207133825601</v>
+        <v>0.01794369145717459</v>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001732056320379423</v>
+        <v>0.007577637070931578</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002677155603517556</v>
+        <v>0.009675222109604443</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2985215123421208</v>
+        <v>0.09070745312095241</v>
       </c>
       <c r="J14" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="K14" t="n">
-        <v>18</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="15">
@@ -3010,35 +2714,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0009714177272542936</v>
+        <v>0.01110082680568815</v>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001045429611593098</v>
+        <v>0.004065159766783968</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003836315463246365</v>
+        <v>0.002200612697474002</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1608506193713617</v>
+        <v>0.1622920319430938</v>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
-        <v>18.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="16">
@@ -3047,35 +2751,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.000753187083975863</v>
+        <v>0.0091534412157659</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001562364279675974</v>
+        <v>0.005712197148551049</v>
       </c>
       <c r="F16" t="n">
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001394017991636853</v>
+        <v>0.004257424079439265</v>
       </c>
       <c r="H16" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3028255227289747</v>
+        <v>0.1426148604252817</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>19</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="17">
@@ -3084,35 +2788,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001662572814679323</v>
+        <v>0.00708503912188317</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001231933398416441</v>
+        <v>0.004018221113907879</v>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0002794175086170525</v>
+        <v>0.0004731324973604401</v>
       </c>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1156273001088381</v>
+        <v>0.202752008909449</v>
       </c>
       <c r="J17" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>20</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="18">
@@ -3121,35 +2825,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0008749662157914575</v>
+        <v>0.00495329366890413</v>
       </c>
       <c r="D18" t="n">
+        <v>22</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.003772135730873312</v>
+      </c>
+      <c r="F18" t="n">
         <v>19</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.001285376198568808</v>
-      </c>
-      <c r="F18" t="n">
-        <v>18</v>
-      </c>
       <c r="G18" t="n">
-        <v>0.0002076550830599655</v>
+        <v>0.001557680894965208</v>
       </c>
       <c r="H18" t="n">
         <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.142136826352941</v>
+        <v>0.1818766355602026</v>
       </c>
       <c r="J18" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K18" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="19">
@@ -3158,35 +2862,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0008170537327478026</v>
+        <v>0.01356968019450394</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0009767968116605645</v>
+        <v>0.007136391318386267</v>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003451852789800536</v>
+        <v>-0.000356172619705486</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1578182754973589</v>
+        <v>0.2887485604509674</v>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +2899,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0009295933489872375</v>
+        <v>0.006220683136873107</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0008239475207759243</v>
+        <v>0.003595695699161286</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003046542802608076</v>
+        <v>0.0004374426895113359</v>
       </c>
       <c r="H20" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
-        <v>0.160961821883415</v>
+        <v>0.1941174532058252</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>23</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="21">
@@ -3232,35 +2936,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0009548430510591239</v>
+        <v>0.005593866533387598</v>
       </c>
       <c r="D21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001147792281952532</v>
+        <v>0.00312639717490473</v>
       </c>
       <c r="F21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.377115489509141e-05</v>
+        <v>0.001158717634249862</v>
       </c>
       <c r="H21" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2031090687824775</v>
+        <v>0.1819457259261128</v>
       </c>
       <c r="J21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>24.25</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +2978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3300,11 +3004,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6800252181377466</v>
+        <v>0.1887256363355426</v>
       </c>
     </row>
     <row r="3">
@@ -3313,11 +3017,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.07392078499358473</v>
+        <v>0.1420745617409387</v>
       </c>
     </row>
     <row r="4">
@@ -3326,11 +3030,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06370161228148555</v>
+        <v>0.1074433402182227</v>
       </c>
     </row>
     <row r="5">
@@ -3339,11 +3043,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05278192226816866</v>
+        <v>0.1036036164221331</v>
       </c>
     </row>
     <row r="6">
@@ -3352,11 +3056,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0515097571401515</v>
+        <v>0.08324052845910307</v>
       </c>
     </row>
     <row r="7">
@@ -3365,11 +3069,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03043172378276767</v>
+        <v>0.0770237695356389</v>
       </c>
     </row>
     <row r="8">
@@ -3378,11 +3082,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0137604941032536</v>
+        <v>0.07080544393170783</v>
       </c>
     </row>
     <row r="9">
@@ -3395,7 +3099,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002315328377349986</v>
+        <v>0.02238603911108551</v>
       </c>
     </row>
     <row r="10">
@@ -3404,11 +3108,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.001931453353223641</v>
+        <v>0.02116261349918513</v>
       </c>
     </row>
     <row r="11">
@@ -3417,11 +3121,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.00171362734339567</v>
+        <v>0.01794369145717459</v>
       </c>
     </row>
     <row r="12">
@@ -3430,11 +3134,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001662572814679323</v>
+        <v>0.01356968019450394</v>
       </c>
     </row>
     <row r="13">
@@ -3443,11 +3147,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001410847217638958</v>
+        <v>0.01255965703293054</v>
       </c>
     </row>
     <row r="14">
@@ -3456,11 +3160,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001278061659875439</v>
+        <v>0.01222738315544579</v>
       </c>
     </row>
     <row r="15">
@@ -3469,11 +3173,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001235049220102229</v>
+        <v>0.01110082680568815</v>
       </c>
     </row>
     <row r="16">
@@ -3482,11 +3186,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001127989024976822</v>
+        <v>0.0091534412157659</v>
       </c>
     </row>
     <row r="17">
@@ -3495,11 +3199,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0009714177272542936</v>
+        <v>0.008376341143111856</v>
       </c>
     </row>
     <row r="18">
@@ -3508,11 +3212,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0009548430510591239</v>
+        <v>0.008109665704164904</v>
       </c>
     </row>
     <row r="19">
@@ -3521,11 +3225,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0009295933489872375</v>
+        <v>0.00708503912188317</v>
       </c>
     </row>
     <row r="20">
@@ -3534,11 +3238,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0008749662157914575</v>
+        <v>0.006220683136873107</v>
       </c>
     </row>
     <row r="21">
@@ -3547,11 +3251,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0008731865929501511</v>
+        <v>0.005593866533387598</v>
       </c>
     </row>
     <row r="22">
@@ -3560,11 +3264,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0008170537327478026</v>
+        <v>0.005460930679095976</v>
       </c>
     </row>
     <row r="23">
@@ -3573,11 +3277,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0007650726116266919</v>
+        <v>0.00495329366890413</v>
       </c>
     </row>
     <row r="24">
@@ -3586,11 +3290,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.000764784068205422</v>
+        <v>0.004564996773249123</v>
       </c>
     </row>
     <row r="25">
@@ -3599,11 +3303,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.000753187083975863</v>
+        <v>0.004525678610649985</v>
       </c>
     </row>
     <row r="26">
@@ -3612,11 +3316,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0007530207133825601</v>
+        <v>0.004513287600545732</v>
       </c>
     </row>
     <row r="27">
@@ -3625,11 +3329,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0007528476815906711</v>
+        <v>0.004230931609307848</v>
       </c>
     </row>
     <row r="28">
@@ -3638,11 +3342,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0007492711216848783</v>
+        <v>0.004129327630145909</v>
       </c>
     </row>
     <row r="29">
@@ -3651,11 +3355,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0007388168646070414</v>
+        <v>0.004045270483074639</v>
       </c>
     </row>
     <row r="30">
@@ -3664,11 +3368,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0007364780952855083</v>
+        <v>0.0040256475836703</v>
       </c>
     </row>
     <row r="31">
@@ -3677,11 +3381,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0007156167008854237</v>
+        <v>0.003942589456721862</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3394,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0006949505915132396</v>
+        <v>0.003893566694808915</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3407,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.000680633210097839</v>
+        <v>0.003676835935823874</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3420,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0006771796699707807</v>
+        <v>0.003256094873574887</v>
       </c>
     </row>
     <row r="35">
@@ -3729,11 +3433,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0006701088738634766</v>
+        <v>0.00294892951993711</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3446,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.000667528872681199</v>
+        <v>0.002865749745253993</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3459,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0006396837141306384</v>
+        <v>0.002773423062589148</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3472,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0006392316186347107</v>
+        <v>0.00232013926897213</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3485,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0006088353991203538</v>
+        <v>0.002290547722010455</v>
       </c>
     </row>
     <row r="40">
@@ -3794,11 +3498,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0005432771320032983</v>
+        <v>0.001746298113170297</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3511,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0005384728880622172</v>
+        <v>0.0005323178190829865</v>
       </c>
     </row>
     <row r="42">
@@ -3820,11 +3524,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0004917288969004438</v>
+        <v>0.0003038200630622453</v>
       </c>
     </row>
     <row r="43">
@@ -3833,11 +3537,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0004718788337140494</v>
+        <v>0.0002260105365881688</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3550,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0004512986664809379</v>
+        <v>0.0001855570732839209</v>
       </c>
     </row>
     <row r="45">
@@ -3859,11 +3563,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0004077400538995397</v>
+        <v>0.0001216287670557282</v>
       </c>
     </row>
     <row r="46">
@@ -3872,115 +3576,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0002296868419742113</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.000192427640655558</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>work_period</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0001184967251699587</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0001146541490661912</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>report_date_year</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>8.562452054369228e-05</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>report_year</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>7.506604669526684e-05</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2.590899729806618e-05</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>1.221535404480305e-05</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>6.773975045052927e-06</v>
+        <v>6.130195493366994e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3994,7 +3594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4020,11 +3620,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5404917126438302</v>
+        <v>0.2850487579936362</v>
       </c>
     </row>
     <row r="3">
@@ -4033,11 +3633,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.103426408421673</v>
+        <v>0.1521486878328943</v>
       </c>
     </row>
     <row r="4">
@@ -4046,11 +3646,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.08883728100634161</v>
+        <v>0.1365515247217552</v>
       </c>
     </row>
     <row r="5">
@@ -4063,7 +3663,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.06908023621794038</v>
+        <v>0.1294691036035181</v>
       </c>
     </row>
     <row r="6">
@@ -4072,11 +3672,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.06733485589348111</v>
+        <v>0.04880593020395663</v>
       </c>
     </row>
     <row r="7">
@@ -4085,11 +3685,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03253781330641893</v>
+        <v>0.04099540415835496</v>
       </c>
     </row>
     <row r="8">
@@ -4098,11 +3698,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0200995544193493</v>
+        <v>0.02779300581058208</v>
       </c>
     </row>
     <row r="9">
@@ -4111,11 +3711,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0101044505328351</v>
+        <v>0.02493966697959183</v>
       </c>
     </row>
     <row r="10">
@@ -4124,11 +3724,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.009682915578592115</v>
+        <v>0.01826404347092722</v>
       </c>
     </row>
     <row r="11">
@@ -4141,7 +3741,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.007884245401468069</v>
+        <v>0.01752359950529689</v>
       </c>
     </row>
     <row r="12">
@@ -4150,11 +3750,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.006375094879893506</v>
+        <v>0.0149169762005839</v>
       </c>
     </row>
     <row r="13">
@@ -4163,11 +3763,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.005239581557694383</v>
+        <v>0.01256455187584946</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +3776,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.003100019448663352</v>
+        <v>0.007577637070931578</v>
       </c>
     </row>
     <row r="15">
@@ -4189,11 +3789,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002266155656213529</v>
+        <v>0.007523539457223542</v>
       </c>
     </row>
     <row r="16">
@@ -4202,11 +3802,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001732056320379423</v>
+        <v>0.007136391318386267</v>
       </c>
     </row>
     <row r="17">
@@ -4215,11 +3815,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001562364279675974</v>
+        <v>0.005712197148551049</v>
       </c>
     </row>
     <row r="18">
@@ -4228,11 +3828,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001476740898676021</v>
+        <v>0.004065159766783968</v>
       </c>
     </row>
     <row r="19">
@@ -4241,11 +3841,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001285376198568808</v>
+        <v>0.004018221113907879</v>
       </c>
     </row>
     <row r="20">
@@ -4254,11 +3854,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001231933398416441</v>
+        <v>0.003772135730873312</v>
       </c>
     </row>
     <row r="21">
@@ -4267,11 +3867,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001182741465926917</v>
+        <v>0.003595695699161286</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +3880,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001151634058644568</v>
+        <v>0.003571426468083794</v>
       </c>
     </row>
     <row r="23">
@@ -4293,11 +3893,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.00114859057407371</v>
+        <v>0.003450417184599063</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +3906,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001147792281952532</v>
+        <v>0.003372041766189656</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +3919,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001114783575473459</v>
+        <v>0.00312639717490473</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +3932,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001095407100862121</v>
+        <v>0.003060533353637416</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +3945,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001077189467018785</v>
+        <v>0.002762938626936052</v>
       </c>
     </row>
     <row r="28">
@@ -4358,11 +3958,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001066974667715616</v>
+        <v>0.002593552130038242</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +3971,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001045429611593098</v>
+        <v>0.002481348547534156</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +3984,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0009843768218952846</v>
+        <v>0.002194166745328697</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +3997,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0009767968116605645</v>
+        <v>0.001765385230591706</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4010,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.000936578222737565</v>
+        <v>0.001743955361656358</v>
       </c>
     </row>
     <row r="33">
@@ -4423,11 +4023,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0009365356081720283</v>
+        <v>0.00171031580369273</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4036,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0009270566805049732</v>
+        <v>0.001690670480360779</v>
       </c>
     </row>
     <row r="35">
@@ -4449,11 +4049,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.000914489129873333</v>
+        <v>0.001678725102212855</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4062,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.0008940465367908252</v>
+        <v>0.001660640897440414</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4075,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0008351610162686362</v>
+        <v>0.001585985869050237</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4088,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0008239475207759243</v>
+        <v>0.001468228851051083</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4101,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0008045754841196324</v>
+        <v>0.001363792424073551</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4114,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0008004214651009396</v>
+        <v>0.001283508655007311</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4127,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0006842171394645225</v>
+        <v>0.001211045960421835</v>
       </c>
     </row>
     <row r="42">
@@ -4540,11 +4140,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0006650763710833805</v>
+        <v>0.001143116203853851</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4153,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.000623085078194488</v>
+        <v>0.00111164760445486</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4166,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0005849586898043011</v>
+        <v>0.0008142332393203022</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4179,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0004959209443196723</v>
+        <v>0.0004817274979841906</v>
       </c>
     </row>
     <row r="46">
@@ -4592,115 +4192,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.000473015342762744</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>filtercake_sugar</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.0004585252415905689</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0004455040804141887</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0004402655751033603</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0004139810386876009</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0004128940098443284</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiling_r3_q</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0003989023369340952</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.0002023044353954326</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>8.802555512954454e-05</v>
+        <v>0.0002519691588108682</v>
       </c>
     </row>
   </sheetData>
@@ -4714,7 +4210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4745,14 +4241,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.707635805653452</v>
+        <v>0.2154246116620057</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07801799479420515</v>
+        <v>0.0280854242934123</v>
       </c>
     </row>
     <row r="3">
@@ -4761,14 +4257,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.09795943275339533</v>
+        <v>0.1234950401155566</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008682725788401445</v>
+        <v>0.01378019701006951</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4277,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.05354981604745403</v>
+        <v>0.1088415266228941</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005935131558128987</v>
+        <v>0.01863672268410216</v>
       </c>
     </row>
     <row r="5">
@@ -4793,14 +4289,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0267286212150805</v>
+        <v>0.07313631731292095</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00321224525340277</v>
+        <v>0.02194149750989389</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4309,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02412762964736486</v>
+        <v>0.04146228699703602</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002811931222986509</v>
+        <v>0.005809587909893908</v>
       </c>
     </row>
     <row r="7">
@@ -4825,14 +4321,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02321682924137426</v>
+        <v>0.04068447534612057</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003626306122843931</v>
+        <v>0.006685098577247548</v>
       </c>
     </row>
     <row r="8">
@@ -4841,14 +4337,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007607948772168904</v>
+        <v>0.0193915821436946</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002231029644669934</v>
+        <v>0.002489699165584057</v>
       </c>
     </row>
     <row r="9">
@@ -4857,14 +4353,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0005898315449532788</v>
+        <v>0.009675222109604443</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004752076410622969</v>
+        <v>0.003445595970613595</v>
       </c>
     </row>
     <row r="10">
@@ -4873,14 +4369,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0003836315463246365</v>
+        <v>0.009544224846933692</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001569891301368575</v>
+        <v>0.000854619388731301</v>
       </c>
     </row>
     <row r="11">
@@ -4889,14 +4385,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0003785540810612664</v>
+        <v>0.007081922240861027</v>
       </c>
       <c r="D11" t="n">
-        <v>9.320889179857302e-05</v>
+        <v>0.004405778210307919</v>
       </c>
     </row>
     <row r="12">
@@ -4905,14 +4401,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0003451852789800536</v>
+        <v>0.004257424079439265</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0001229530453033222</v>
+        <v>0.0008371371528291755</v>
       </c>
     </row>
     <row r="13">
@@ -4921,14 +4417,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0003414091818776499</v>
+        <v>0.003669765706062567</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001949165249263923</v>
+        <v>0.006367042308607121</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4433,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0003391445003128593</v>
+        <v>0.002347657338847642</v>
       </c>
       <c r="D14" t="n">
-        <v>3.707081220570067e-05</v>
+        <v>0.001388178255553533</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4449,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0003204965668263004</v>
+        <v>0.002313667322257817</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001922446410491312</v>
+        <v>0.001302615063205645</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4465,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0003118967992993493</v>
+        <v>0.002200612697474002</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0003173268004240187</v>
+        <v>0.001640237144867066</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4481,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0003046542802608076</v>
+        <v>0.001854788330938895</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001439406965768579</v>
+        <v>0.0008958620777341456</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +4497,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0002799502317631153</v>
+        <v>0.001854266814861505</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001280604313256441</v>
+        <v>0.0008280998316244544</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +4513,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0002794175086170525</v>
+        <v>0.001815440161301596</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0003944946494375634</v>
+        <v>0.00220321137527468</v>
       </c>
     </row>
     <row r="20">
@@ -5033,14 +4529,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0002677155603517556</v>
+        <v>0.001753806644895284</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001647124028711367</v>
+        <v>0.0007011217938123543</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +4545,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0002622409575994133</v>
+        <v>0.00171971692051659</v>
       </c>
       <c r="D21" t="n">
-        <v>7.740803687131447e-05</v>
+        <v>0.001167759873172892</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +4561,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0002076550830599655</v>
+        <v>0.001557680894965208</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001455212522585809</v>
+        <v>0.001107361403705591</v>
       </c>
     </row>
     <row r="23">
@@ -5081,14 +4577,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0001718180908426348</v>
+        <v>0.001464157095111918</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001570658298068005</v>
+        <v>0.0002388191188903144</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +4593,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0001678774978638109</v>
+        <v>0.00122806842735762</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0001349968981410332</v>
+        <v>0.0008702151334907058</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +4609,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0001394017991636853</v>
+        <v>0.00116731946576254</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0002202059411705579</v>
+        <v>0.003100860501643399</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +4625,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0001149755631063232</v>
+        <v>0.001158717634249862</v>
       </c>
       <c r="D26" t="n">
-        <v>6.155517252706295e-05</v>
+        <v>0.00107372735173241</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +4641,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0001032949656526339</v>
+        <v>0.0009890090611721302</v>
       </c>
       <c r="D27" t="n">
-        <v>6.520066052020055e-05</v>
+        <v>0.00113813189538075</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +4657,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9.737969164343995e-05</v>
+        <v>0.0005601140805585825</v>
       </c>
       <c r="D28" t="n">
-        <v>4.872398371471293e-05</v>
+        <v>0.0004434803375421925</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +4673,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.943631783049465e-05</v>
+        <v>0.0005228209926651961</v>
       </c>
       <c r="D29" t="n">
-        <v>5.051636987226733e-05</v>
+        <v>0.0005133725593386572</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +4689,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.591721942730167e-05</v>
+        <v>0.0004731324973604401</v>
       </c>
       <c r="D30" t="n">
-        <v>6.203837256942163e-05</v>
+        <v>0.001653268709317335</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +4705,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7.508100486476321e-05</v>
+        <v>0.0004374426895113359</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001249166349489615</v>
+        <v>0.001379879424497482</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +4721,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5.396597271620784e-05</v>
+        <v>0.0003738514379423741</v>
       </c>
       <c r="D32" t="n">
-        <v>7.491467483872731e-05</v>
+        <v>0.0006258970832914081</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +4737,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.514813604091783e-05</v>
+        <v>0.0002535083457601006</v>
       </c>
       <c r="D33" t="n">
-        <v>2.601168765522396e-05</v>
+        <v>0.0004960798918776066</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +4753,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4.451721783134132e-05</v>
+        <v>0.000191604288994196</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001464450104960041</v>
+        <v>0.0005096524084213707</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +4769,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3.301514620209778e-05</v>
+        <v>7.982958698583564e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>6.669297915273512e-05</v>
+        <v>0.0005867689384628775</v>
       </c>
     </row>
     <row r="36">
@@ -5289,14 +4785,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.269396022550497e-05</v>
+        <v>4.713116728115585e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>2.519865399270891e-05</v>
+        <v>5.447493510930545e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +4801,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3.188194014028811e-05</v>
+        <v>4.58058941945727e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>2.52822123599876e-05</v>
+        <v>0.0001011902536356641</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +4817,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.541221249652281e-05</v>
+        <v>3.929368774837627e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>5.847065642315276e-05</v>
+        <v>1.77424920512469e-05</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +4833,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.367625866948163e-05</v>
+        <v>-1.386100759229736e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>7.824739093504678e-06</v>
+        <v>1.383000399694354e-05</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +4853,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9.887444687772806e-06</v>
+        <v>-7.045442892575915e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001154125676429848</v>
+        <v>0.0004115422248265498</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +4865,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-3.37317632691514e-06</v>
+        <v>-0.0001852744188726718</v>
       </c>
       <c r="D41" t="n">
-        <v>3.103601093988273e-06</v>
+        <v>0.0001474809906507178</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +4885,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-5.715355416946455e-06</v>
+        <v>-0.0002079511254434285</v>
       </c>
       <c r="D42" t="n">
-        <v>1.861720893452552e-05</v>
+        <v>0.000165171276314547</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +4897,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-1.667800517024531e-05</v>
+        <v>-0.000356172619705486</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0003124043520494439</v>
+        <v>0.004190309319738993</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +4913,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-2.377115489509141e-05</v>
+        <v>-0.0003614879095182877</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001786426619872305</v>
+        <v>0.0005902871062728733</v>
       </c>
     </row>
     <row r="45">
@@ -5433,14 +4929,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-2.704625013826289e-05</v>
+        <v>-0.0003790091634006343</v>
       </c>
       <c r="D45" t="n">
-        <v>1.552544431575823e-05</v>
+        <v>0.0002888491131521819</v>
       </c>
     </row>
     <row r="46">
@@ -5449,142 +4945,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-6.855343983092066e-05</v>
+        <v>-0.0007288706209371387</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0001749117956052606</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>sweetwater_brix</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>-7.059586605756563e-05</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0.000154172354564766</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>raw_syrup_brix</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>-7.676763974000523e-05</v>
-      </c>
-      <c r="D48" t="n">
-        <v>9.031310258090518e-05</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>-8.463044702848866e-05</v>
-      </c>
-      <c r="D49" t="n">
-        <v>3.332377236625676e-05</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>filtercake_sugar</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>-9.471982957668379e-05</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.0001419861488978646</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>boiling_r2_q</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.000143109847328271</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.0001179461880385015</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>wastewater_r2_q</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.0002577785125864818</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.0001257590458424292</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>white_quality_solution_color_1</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.0002784330466673479</v>
-      </c>
-      <c r="D53" t="n">
-        <v>8.788422570899487e-05</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>carbonated_pH</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.000797979514448699</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.0003239428442837299</v>
+        <v>0.001728379781492033</v>
       </c>
     </row>
   </sheetData>
@@ -5598,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5624,11 +4992,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.218640274671984</v>
+        <v>1.101184650283743</v>
       </c>
     </row>
     <row r="3">
@@ -5637,11 +5005,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.201473366213727</v>
+        <v>0.9621316924038448</v>
       </c>
     </row>
     <row r="4">
@@ -5650,11 +5018,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_apparent_color</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9740681227027399</v>
+        <v>0.6816869476946867</v>
       </c>
     </row>
     <row r="5">
@@ -5663,11 +5031,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_apparent_color</t>
+          <t>white_solution_color</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6834105794958298</v>
+        <v>0.6024653931586257</v>
       </c>
     </row>
     <row r="6">
@@ -5680,7 +5048,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6077038077134711</v>
+        <v>0.6000338949969537</v>
       </c>
     </row>
     <row r="7">
@@ -5689,11 +5057,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_solution_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5949108055762866</v>
+        <v>0.5671407408639033</v>
       </c>
     </row>
     <row r="8">
@@ -5702,11 +5070,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.5644010612379948</v>
+        <v>0.5395616793636768</v>
       </c>
     </row>
     <row r="9">
@@ -5715,11 +5083,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.5327029817778945</v>
+        <v>0.4390111655153612</v>
       </c>
     </row>
     <row r="10">
@@ -5728,11 +5096,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.44686686725841</v>
+        <v>0.3584051527160685</v>
       </c>
     </row>
     <row r="11">
@@ -5741,11 +5109,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.4455611388869869</v>
+        <v>0.2887485604509674</v>
       </c>
     </row>
     <row r="12">
@@ -5754,11 +5122,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.3562349381719732</v>
+        <v>0.2855334252973867</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5135,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.3028255227289747</v>
+        <v>0.202752008909449</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5148,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2985215123421208</v>
+        <v>0.1988847543436636</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5161,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2031090687824775</v>
+        <v>0.1941174532058252</v>
       </c>
     </row>
     <row r="16">
@@ -5806,11 +5174,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.1973511154055063</v>
+        <v>0.1819457259261128</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5187,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.1958234914034658</v>
+        <v>0.1818766355602026</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5200,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1908368699036518</v>
+        <v>0.1700856585894175</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5213,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1759561832904888</v>
+        <v>0.1678988720230379</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5226,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1739358867039082</v>
+        <v>0.1622920319430938</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5239,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1647514728112884</v>
+        <v>0.1613503572422621</v>
       </c>
     </row>
     <row r="22">
@@ -5884,11 +5252,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.160961821883415</v>
+        <v>0.1566058110248951</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5265,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1608506193713617</v>
+        <v>0.1473970865416119</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5278,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1603958110615249</v>
+        <v>0.1426148604252817</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5291,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1578182754973589</v>
+        <v>0.1400777777885083</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5304,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1559329730828996</v>
+        <v>0.137194221917365</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5317,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.142136826352941</v>
+        <v>0.1300828311467801</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5330,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1420112271327061</v>
+        <v>0.1109769442419932</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5343,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1408883484035341</v>
+        <v>0.1067579909826857</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5356,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1392444540454294</v>
+        <v>0.1055627686810054</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +5369,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1299171094960583</v>
+        <v>0.09858140517611114</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +5382,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1277389310575956</v>
+        <v>0.09742503609965758</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +5395,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1156273001088381</v>
+        <v>0.09070745312095241</v>
       </c>
     </row>
     <row r="34">
@@ -6040,11 +5408,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.106134402203919</v>
+        <v>0.08173331081734592</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +5421,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1038183200160381</v>
+        <v>0.07767109781360348</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +5434,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1005288743794375</v>
+        <v>0.07443367943814927</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +5447,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.09968889310613394</v>
+        <v>0.07434657562092495</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +5460,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.09402228325438222</v>
+        <v>0.07216616430500356</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +5473,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.09370761658679161</v>
+        <v>0.0620183183041334</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +5486,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.08127930939985895</v>
+        <v>0.04786084275164715</v>
       </c>
     </row>
     <row r="41">
@@ -6131,11 +5499,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.07872194941866106</v>
+        <v>0.03951371912528678</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +5512,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.07572692342308374</v>
+        <v>0.03383869674795958</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +5525,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0746105968709756</v>
+        <v>0.001225907812150817</v>
       </c>
     </row>
     <row r="44">
@@ -6170,140 +5538,36 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.07444809598034219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.07006369108004318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.04807124431972998</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>filtercake_moisture</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.0466126146370085</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>standard_liquor_pH</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.03224518135769872</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.03167145573501529</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.02793674948181502</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.02092021476374217</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>51</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6379,10 +5643,10 @@
         <v>197</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -6391,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:24:57 UTC</t>
+          <t>2026-06-16 11:49:32 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_ash.xlsx
+++ b/NN/reports/feature_importance_white_ash.xlsx
@@ -624,7 +624,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009544224846933692</v>
+        <v>0.00954422484693343</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -735,7 +735,7 @@
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04146228699703602</v>
+        <v>0.04146228699703606</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07313631731292095</v>
+        <v>0.07313631731292096</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -809,7 +809,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007081922240861027</v>
+        <v>0.007081922240861072</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
@@ -846,7 +846,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00116731946576254</v>
+        <v>0.001167319465762529</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -883,7 +883,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003669765706062567</v>
+        <v>0.003669765706062533</v>
       </c>
       <c r="H12" t="n">
         <v>12</v>
@@ -920,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002347657338847642</v>
+        <v>0.00234765733884762</v>
       </c>
       <c r="H13" t="n">
         <v>13</v>
@@ -957,7 +957,7 @@
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.009675222109604443</v>
+        <v>0.00967522210960442</v>
       </c>
       <c r="H14" t="n">
         <v>8</v>
@@ -994,7 +994,7 @@
         <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002200612697474002</v>
+        <v>0.002200612697474014</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
@@ -1068,7 +1068,7 @@
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004731324973604401</v>
+        <v>0.0004731324973604622</v>
       </c>
       <c r="H17" t="n">
         <v>29</v>
@@ -1105,7 +1105,7 @@
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001557680894965208</v>
+        <v>0.001557680894965219</v>
       </c>
       <c r="H18" t="n">
         <v>21</v>
@@ -1142,7 +1142,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.000356172619705486</v>
+        <v>-0.0003561726197054416</v>
       </c>
       <c r="H19" t="n">
         <v>42</v>
@@ -1216,7 +1216,7 @@
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001158717634249862</v>
+        <v>0.001158717634249884</v>
       </c>
       <c r="H21" t="n">
         <v>25</v>
@@ -1253,7 +1253,7 @@
         <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001815440161301596</v>
+        <v>0.001815440161301607</v>
       </c>
       <c r="H22" t="n">
         <v>18</v>
@@ -1290,7 +1290,7 @@
         <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001854788330938895</v>
+        <v>0.001854788330938906</v>
       </c>
       <c r="H23" t="n">
         <v>16</v>
@@ -1327,7 +1327,7 @@
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0005228209926651961</v>
+        <v>0.0005228209926652183</v>
       </c>
       <c r="H24" t="n">
         <v>28</v>
@@ -1364,7 +1364,7 @@
         <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0007288706209371387</v>
+        <v>-0.0007288706209371498</v>
       </c>
       <c r="H25" t="n">
         <v>45</v>
@@ -1401,7 +1401,7 @@
         <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0005601140805585825</v>
+        <v>0.0005601140805585713</v>
       </c>
       <c r="H26" t="n">
         <v>27</v>
@@ -1438,7 +1438,7 @@
         <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>0.00122806842735762</v>
+        <v>0.001228068427357631</v>
       </c>
       <c r="H27" t="n">
         <v>23</v>
@@ -1475,7 +1475,7 @@
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.00171971692051659</v>
+        <v>0.001719716920516601</v>
       </c>
       <c r="H28" t="n">
         <v>20</v>
@@ -1549,7 +1549,7 @@
         <v>35</v>
       </c>
       <c r="G30" t="n">
-        <v>0.001753806644895284</v>
+        <v>0.001753806644895251</v>
       </c>
       <c r="H30" t="n">
         <v>19</v>
@@ -1586,7 +1586,7 @@
         <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003738514379423741</v>
+        <v>0.0003738514379423852</v>
       </c>
       <c r="H31" t="n">
         <v>31</v>
@@ -1623,7 +1623,7 @@
         <v>36</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0009890090611721302</v>
+        <v>0.0009890090611721525</v>
       </c>
       <c r="H32" t="n">
         <v>26</v>
@@ -1660,7 +1660,7 @@
         <v>38</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002313667322257817</v>
+        <v>0.002313667322257829</v>
       </c>
       <c r="H33" t="n">
         <v>14</v>
@@ -1697,7 +1697,7 @@
         <v>37</v>
       </c>
       <c r="G34" t="n">
-        <v>0.001464157095111918</v>
+        <v>0.001464157095111895</v>
       </c>
       <c r="H34" t="n">
         <v>22</v>
@@ -1734,7 +1734,7 @@
         <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0001852744188726718</v>
+        <v>-0.0001852744188726829</v>
       </c>
       <c r="H35" t="n">
         <v>40</v>
@@ -1771,7 +1771,7 @@
         <v>31</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0002535083457601006</v>
+        <v>0.0002535083457600895</v>
       </c>
       <c r="H36" t="n">
         <v>32</v>
@@ -1808,7 +1808,7 @@
         <v>28</v>
       </c>
       <c r="G37" t="n">
-        <v>4.58058941945727e-05</v>
+        <v>4.58058941945616e-05</v>
       </c>
       <c r="H37" t="n">
         <v>36</v>
@@ -1845,7 +1845,7 @@
         <v>30</v>
       </c>
       <c r="G38" t="n">
-        <v>7.982958698583564e-05</v>
+        <v>7.982958698586895e-05</v>
       </c>
       <c r="H38" t="n">
         <v>34</v>
@@ -1882,7 +1882,7 @@
         <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>0.000191604288994196</v>
+        <v>0.0001916042889941849</v>
       </c>
       <c r="H39" t="n">
         <v>33</v>
@@ -1919,7 +1919,7 @@
         <v>32</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0003614879095182877</v>
+        <v>-0.0003614879095183099</v>
       </c>
       <c r="H40" t="n">
         <v>43</v>
@@ -1993,7 +1993,7 @@
         <v>39</v>
       </c>
       <c r="G42" t="n">
-        <v>3.929368774837627e-05</v>
+        <v>3.929368774836517e-05</v>
       </c>
       <c r="H42" t="n">
         <v>37</v>
@@ -2030,7 +2030,7 @@
         <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.0003790091634006343</v>
+        <v>-0.0003790091634006454</v>
       </c>
       <c r="H43" t="n">
         <v>44</v>
@@ -2067,7 +2067,7 @@
         <v>43</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.0002079511254434285</v>
+        <v>-0.0002079511254434618</v>
       </c>
       <c r="H44" t="n">
         <v>41</v>
@@ -2104,7 +2104,7 @@
         <v>45</v>
       </c>
       <c r="G45" t="n">
-        <v>4.713116728115585e-05</v>
+        <v>4.713116728114475e-05</v>
       </c>
       <c r="H45" t="n">
         <v>35</v>
@@ -2360,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009544224846933692</v>
+        <v>0.00954422484693343</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -2471,7 +2471,7 @@
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04146228699703602</v>
+        <v>0.04146228699703606</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -2508,7 +2508,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07313631731292095</v>
+        <v>0.07313631731292096</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -2545,7 +2545,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007081922240861027</v>
+        <v>0.007081922240861072</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
@@ -2582,7 +2582,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00116731946576254</v>
+        <v>0.001167319465762529</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -2619,7 +2619,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003669765706062567</v>
+        <v>0.003669765706062533</v>
       </c>
       <c r="H12" t="n">
         <v>12</v>
@@ -2656,7 +2656,7 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002347657338847642</v>
+        <v>0.00234765733884762</v>
       </c>
       <c r="H13" t="n">
         <v>13</v>
@@ -2693,7 +2693,7 @@
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.009675222109604443</v>
+        <v>0.00967522210960442</v>
       </c>
       <c r="H14" t="n">
         <v>8</v>
@@ -2730,7 +2730,7 @@
         <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002200612697474002</v>
+        <v>0.002200612697474014</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
@@ -2804,7 +2804,7 @@
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004731324973604401</v>
+        <v>0.0004731324973604622</v>
       </c>
       <c r="H17" t="n">
         <v>29</v>
@@ -2841,7 +2841,7 @@
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001557680894965208</v>
+        <v>0.001557680894965219</v>
       </c>
       <c r="H18" t="n">
         <v>21</v>
@@ -2878,7 +2878,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.000356172619705486</v>
+        <v>-0.0003561726197054416</v>
       </c>
       <c r="H19" t="n">
         <v>42</v>
@@ -2952,7 +2952,7 @@
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001158717634249862</v>
+        <v>0.001158717634249884</v>
       </c>
       <c r="H21" t="n">
         <v>25</v>
@@ -4248,7 +4248,7 @@
         <v>0.2154246116620057</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0280854242934123</v>
+        <v>0.02808542429341231</v>
       </c>
     </row>
     <row r="3">
@@ -4264,7 +4264,7 @@
         <v>0.1234950401155566</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01378019701006951</v>
+        <v>0.01378019701006953</v>
       </c>
     </row>
     <row r="4">
@@ -4280,7 +4280,7 @@
         <v>0.1088415266228941</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01863672268410216</v>
+        <v>0.01863672268410217</v>
       </c>
     </row>
     <row r="5">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07313631731292095</v>
+        <v>0.07313631731292096</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02194149750989389</v>
+        <v>0.02194149750989386</v>
       </c>
     </row>
     <row r="6">
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04146228699703602</v>
+        <v>0.04146228699703606</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005809587909893908</v>
+        <v>0.005809587909893889</v>
       </c>
     </row>
     <row r="7">
@@ -4328,7 +4328,7 @@
         <v>0.04068447534612057</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006685098577247548</v>
+        <v>0.006685098577247514</v>
       </c>
     </row>
     <row r="8">
@@ -4344,7 +4344,7 @@
         <v>0.0193915821436946</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002489699165584057</v>
+        <v>0.002489699165584055</v>
       </c>
     </row>
     <row r="9">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.009675222109604443</v>
+        <v>0.00967522210960442</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003445595970613595</v>
+        <v>0.00344559597061358</v>
       </c>
     </row>
     <row r="10">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.009544224846933692</v>
+        <v>0.00954422484693343</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000854619388731301</v>
+        <v>0.000854619388731545</v>
       </c>
     </row>
     <row r="11">
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.007081922240861027</v>
+        <v>0.007081922240861072</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004405778210307919</v>
+        <v>0.004405778210307942</v>
       </c>
     </row>
     <row r="12">
@@ -4408,7 +4408,7 @@
         <v>0.004257424079439265</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008371371528291755</v>
+        <v>0.0008371371528291806</v>
       </c>
     </row>
     <row r="13">
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.003669765706062567</v>
+        <v>0.003669765706062533</v>
       </c>
       <c r="D13" t="n">
-        <v>0.006367042308607121</v>
+        <v>0.006367042308607108</v>
       </c>
     </row>
     <row r="14">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002347657338847642</v>
+        <v>0.00234765733884762</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001388178255553533</v>
+        <v>0.001388178255553523</v>
       </c>
     </row>
     <row r="15">
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002313667322257817</v>
+        <v>0.002313667322257829</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001302615063205645</v>
+        <v>0.00130261506320563</v>
       </c>
     </row>
     <row r="16">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002200612697474002</v>
+        <v>0.002200612697474014</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001640237144867066</v>
+        <v>0.001640237144867023</v>
       </c>
     </row>
     <row r="17">
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001854788330938895</v>
+        <v>0.001854788330938906</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0008958620777341456</v>
+        <v>0.0008958620777341561</v>
       </c>
     </row>
     <row r="18">
@@ -4504,7 +4504,7 @@
         <v>0.001854266814861505</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0008280998316244544</v>
+        <v>0.0008280998316244653</v>
       </c>
     </row>
     <row r="19">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001815440161301596</v>
+        <v>0.001815440161301607</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00220321137527468</v>
+        <v>0.002203211375274682</v>
       </c>
     </row>
     <row r="20">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001753806644895284</v>
+        <v>0.001753806644895251</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0007011217938123543</v>
+        <v>0.0007011217938123496</v>
       </c>
     </row>
     <row r="21">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.00171971692051659</v>
+        <v>0.001719716920516601</v>
       </c>
       <c r="D21" t="n">
-        <v>0.001167759873172892</v>
+        <v>0.001167759873172896</v>
       </c>
     </row>
     <row r="22">
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001557680894965208</v>
+        <v>0.001557680894965219</v>
       </c>
       <c r="D22" t="n">
-        <v>0.001107361403705591</v>
+        <v>0.001107361403705596</v>
       </c>
     </row>
     <row r="23">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001464157095111918</v>
+        <v>0.001464157095111895</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002388191188903144</v>
+        <v>0.0002388191188903398</v>
       </c>
     </row>
     <row r="24">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.00122806842735762</v>
+        <v>0.001228068427357631</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0008702151334907058</v>
+        <v>0.0008702151334907269</v>
       </c>
     </row>
     <row r="25">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.00116731946576254</v>
+        <v>0.001167319465762529</v>
       </c>
       <c r="D25" t="n">
-        <v>0.003100860501643399</v>
+        <v>0.003100860501643398</v>
       </c>
     </row>
     <row r="26">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001158717634249862</v>
+        <v>0.001158717634249884</v>
       </c>
       <c r="D26" t="n">
-        <v>0.00107372735173241</v>
+        <v>0.001073727351732406</v>
       </c>
     </row>
     <row r="27">
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0009890090611721302</v>
+        <v>0.0009890090611721525</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00113813189538075</v>
+        <v>0.001138131895380745</v>
       </c>
     </row>
     <row r="28">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0005601140805585825</v>
+        <v>0.0005601140805585713</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0004434803375421925</v>
+        <v>0.0004434803375421696</v>
       </c>
     </row>
     <row r="29">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0005228209926651961</v>
+        <v>0.0005228209926652183</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0005133725593386572</v>
+        <v>0.0005133725593386311</v>
       </c>
     </row>
     <row r="30">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0004731324973604401</v>
+        <v>0.0004731324973604622</v>
       </c>
       <c r="D30" t="n">
-        <v>0.001653268709317335</v>
+        <v>0.001653268709317363</v>
       </c>
     </row>
     <row r="31">
@@ -4712,7 +4712,7 @@
         <v>0.0004374426895113359</v>
       </c>
       <c r="D31" t="n">
-        <v>0.001379879424497482</v>
+        <v>0.001379879424497453</v>
       </c>
     </row>
     <row r="32">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0003738514379423741</v>
+        <v>0.0003738514379423852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0006258970832914081</v>
+        <v>0.0006258970832914124</v>
       </c>
     </row>
     <row r="33">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0002535083457601006</v>
+        <v>0.0002535083457600895</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0004960798918776066</v>
+        <v>0.0004960798918775569</v>
       </c>
     </row>
     <row r="34">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.000191604288994196</v>
+        <v>0.0001916042889941849</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0005096524084213707</v>
+        <v>0.000509652408421358</v>
       </c>
     </row>
     <row r="35">
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7.982958698583564e-05</v>
+        <v>7.982958698586895e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0005867689384628775</v>
+        <v>0.0005867689384629039</v>
       </c>
     </row>
     <row r="36">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.713116728115585e-05</v>
+        <v>4.713116728114475e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>5.447493510930545e-05</v>
+        <v>5.447493510932615e-05</v>
       </c>
     </row>
     <row r="37">
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.58058941945727e-05</v>
+        <v>4.58058941945616e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0001011902536356641</v>
+        <v>0.0001011902536356673</v>
       </c>
     </row>
     <row r="38">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3.929368774837627e-05</v>
+        <v>3.929368774836517e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>1.77424920512469e-05</v>
+        <v>1.774249205124809e-05</v>
       </c>
     </row>
     <row r="39">
@@ -4840,7 +4840,7 @@
         <v>-1.386100759229736e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>1.383000399694354e-05</v>
+        <v>1.383000399694778e-05</v>
       </c>
     </row>
     <row r="40">
@@ -4856,7 +4856,7 @@
         <v>-7.045442892575915e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0004115422248265498</v>
+        <v>0.0004115422248265511</v>
       </c>
     </row>
     <row r="41">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.0001852744188726718</v>
+        <v>-0.0001852744188726829</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0001474809906507178</v>
+        <v>0.0001474809906506867</v>
       </c>
     </row>
     <row r="42">
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.0002079511254434285</v>
+        <v>-0.0002079511254434618</v>
       </c>
       <c r="D42" t="n">
-        <v>0.000165171276314547</v>
+        <v>0.0001651712763145363</v>
       </c>
     </row>
     <row r="43">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.000356172619705486</v>
+        <v>-0.0003561726197054416</v>
       </c>
       <c r="D43" t="n">
-        <v>0.004190309319738993</v>
+        <v>0.004190309319738963</v>
       </c>
     </row>
     <row r="44">
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.0003614879095182877</v>
+        <v>-0.0003614879095183099</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0005902871062728733</v>
+        <v>0.0005902871062729058</v>
       </c>
     </row>
     <row r="45">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.0003790091634006343</v>
+        <v>-0.0003790091634006454</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002888491131521819</v>
+        <v>0.0002888491131521844</v>
       </c>
     </row>
     <row r="46">
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0007288706209371387</v>
+        <v>-0.0007288706209371498</v>
       </c>
       <c r="D46" t="n">
-        <v>0.001728379781492033</v>
+        <v>0.001728379781492024</v>
       </c>
     </row>
   </sheetData>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 11:49:32 UTC</t>
+          <t>2026-06-16 14:07:49 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_ash.xlsx
+++ b/NN/reports/feature_importance_white_ash.xlsx
@@ -513,7 +513,7 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2154246116620057</v>
+        <v>0.2154246116620059</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -550,7 +550,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1088415266228941</v>
+        <v>0.1088415266228942</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -587,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1234950401155566</v>
+        <v>0.1234950401155569</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -624,7 +624,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00954422484693343</v>
+        <v>0.009544224847013203</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -661,7 +661,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04068447534612057</v>
+        <v>0.04068447534612076</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -698,7 +698,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0193915821436946</v>
+        <v>0.01939158214369482</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -735,7 +735,7 @@
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04146228699703606</v>
+        <v>0.0414622869970363</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07313631731292096</v>
+        <v>0.07313631731292118</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -809,7 +809,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007081922240861072</v>
+        <v>0.007081922240861216</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
@@ -846,7 +846,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001167319465762529</v>
+        <v>0.001167319465762784</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -883,7 +883,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003669765706062533</v>
+        <v>0.003669765706062789</v>
       </c>
       <c r="H12" t="n">
         <v>12</v>
@@ -920,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00234765733884762</v>
+        <v>0.002347657338847842</v>
       </c>
       <c r="H13" t="n">
         <v>13</v>
@@ -957,7 +957,7 @@
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00967522210960442</v>
+        <v>0.009675222109604665</v>
       </c>
       <c r="H14" t="n">
         <v>8</v>
@@ -994,7 +994,7 @@
         <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002200612697474014</v>
+        <v>0.002200612697474224</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
@@ -1031,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.004257424079439265</v>
+        <v>0.004257424079439476</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
@@ -1068,7 +1068,7 @@
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004731324973604622</v>
+        <v>0.0004731324973606621</v>
       </c>
       <c r="H17" t="n">
         <v>29</v>
@@ -1105,7 +1105,7 @@
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001557680894965219</v>
+        <v>0.00155768089496543</v>
       </c>
       <c r="H18" t="n">
         <v>21</v>
@@ -1142,7 +1142,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0003561726197054416</v>
+        <v>-0.0003561726197052306</v>
       </c>
       <c r="H19" t="n">
         <v>42</v>
@@ -1179,7 +1179,7 @@
         <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0004374426895113359</v>
+        <v>0.0004374426895115802</v>
       </c>
       <c r="H20" t="n">
         <v>30</v>
@@ -1216,7 +1216,7 @@
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001158717634249884</v>
+        <v>0.001158717634250084</v>
       </c>
       <c r="H21" t="n">
         <v>25</v>
@@ -1253,7 +1253,7 @@
         <v>34</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001815440161301607</v>
+        <v>0.001815440161301785</v>
       </c>
       <c r="H22" t="n">
         <v>18</v>
@@ -1290,7 +1290,7 @@
         <v>26</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001854788330938906</v>
+        <v>0.001854788330939139</v>
       </c>
       <c r="H23" t="n">
         <v>16</v>
@@ -1327,7 +1327,7 @@
         <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0005228209926652183</v>
+        <v>0.0005228209926654182</v>
       </c>
       <c r="H24" t="n">
         <v>28</v>
@@ -1364,7 +1364,7 @@
         <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0007288706209371498</v>
+        <v>-0.0007288706209369056</v>
       </c>
       <c r="H25" t="n">
         <v>45</v>
@@ -1401,7 +1401,7 @@
         <v>23</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0005601140805585713</v>
+        <v>0.0005601140805587934</v>
       </c>
       <c r="H26" t="n">
         <v>27</v>
@@ -1438,7 +1438,7 @@
         <v>33</v>
       </c>
       <c r="G27" t="n">
-        <v>0.001228068427357631</v>
+        <v>0.001228068427357865</v>
       </c>
       <c r="H27" t="n">
         <v>23</v>
@@ -1475,7 +1475,7 @@
         <v>29</v>
       </c>
       <c r="G28" t="n">
-        <v>0.001719716920516601</v>
+        <v>0.001719716920516778</v>
       </c>
       <c r="H28" t="n">
         <v>20</v>
@@ -1512,7 +1512,7 @@
         <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>0.001854266814861505</v>
+        <v>0.001854266814861694</v>
       </c>
       <c r="H29" t="n">
         <v>17</v>
@@ -1549,7 +1549,7 @@
         <v>35</v>
       </c>
       <c r="G30" t="n">
-        <v>0.001753806644895251</v>
+        <v>0.001753806644895495</v>
       </c>
       <c r="H30" t="n">
         <v>19</v>
@@ -1586,7 +1586,7 @@
         <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003738514379423852</v>
+        <v>0.000373851437942585</v>
       </c>
       <c r="H31" t="n">
         <v>31</v>
@@ -1623,7 +1623,7 @@
         <v>36</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0009890090611721525</v>
+        <v>0.0009890090611723301</v>
       </c>
       <c r="H32" t="n">
         <v>26</v>
@@ -1660,7 +1660,7 @@
         <v>38</v>
       </c>
       <c r="G33" t="n">
-        <v>0.002313667322257829</v>
+        <v>0.002313667322258029</v>
       </c>
       <c r="H33" t="n">
         <v>14</v>
@@ -1697,7 +1697,7 @@
         <v>37</v>
       </c>
       <c r="G34" t="n">
-        <v>0.001464157095111895</v>
+        <v>0.00146415709511214</v>
       </c>
       <c r="H34" t="n">
         <v>22</v>
@@ -1734,7 +1734,7 @@
         <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0001852744188726829</v>
+        <v>-0.0001852744188724609</v>
       </c>
       <c r="H35" t="n">
         <v>40</v>
@@ -1771,7 +1771,7 @@
         <v>31</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0002535083457600895</v>
+        <v>0.0002535083457603338</v>
       </c>
       <c r="H36" t="n">
         <v>32</v>
@@ -1808,7 +1808,7 @@
         <v>28</v>
       </c>
       <c r="G37" t="n">
-        <v>4.58058941945616e-05</v>
+        <v>4.580589419481695e-05</v>
       </c>
       <c r="H37" t="n">
         <v>36</v>
@@ -1845,7 +1845,7 @@
         <v>30</v>
       </c>
       <c r="G38" t="n">
-        <v>7.982958698586895e-05</v>
+        <v>7.98295869860799e-05</v>
       </c>
       <c r="H38" t="n">
         <v>34</v>
@@ -1882,7 +1882,7 @@
         <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0001916042889941849</v>
+        <v>0.0001916042889944181</v>
       </c>
       <c r="H39" t="n">
         <v>33</v>
@@ -1919,7 +1919,7 @@
         <v>32</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0003614879095183099</v>
+        <v>-0.0003614879095180879</v>
       </c>
       <c r="H40" t="n">
         <v>43</v>
@@ -1956,7 +1956,7 @@
         <v>41</v>
       </c>
       <c r="G41" t="n">
-        <v>-7.045442892575915e-05</v>
+        <v>-7.0454428925526e-05</v>
       </c>
       <c r="H41" t="n">
         <v>39</v>
@@ -1993,7 +1993,7 @@
         <v>39</v>
       </c>
       <c r="G42" t="n">
-        <v>3.929368774836517e-05</v>
+        <v>3.929368774857611e-05</v>
       </c>
       <c r="H42" t="n">
         <v>37</v>
@@ -2030,7 +2030,7 @@
         <v>42</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.0003790091634006454</v>
+        <v>-0.0003790091634004123</v>
       </c>
       <c r="H43" t="n">
         <v>44</v>
@@ -2067,7 +2067,7 @@
         <v>43</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.0002079511254434618</v>
+        <v>-0.0002079511254432176</v>
       </c>
       <c r="H44" t="n">
         <v>41</v>
@@ -2104,7 +2104,7 @@
         <v>45</v>
       </c>
       <c r="G45" t="n">
-        <v>4.713116728114475e-05</v>
+        <v>4.7131167281389e-05</v>
       </c>
       <c r="H45" t="n">
         <v>35</v>
@@ -2141,7 +2141,7 @@
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.386100759229736e-05</v>
+        <v>-1.386100759208642e-05</v>
       </c>
       <c r="H46" t="n">
         <v>38</v>
@@ -2249,7 +2249,7 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2154246116620057</v>
+        <v>0.2154246116620059</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1088415266228941</v>
+        <v>0.1088415266228942</v>
       </c>
       <c r="H3" t="n">
         <v>3</v>
@@ -2323,7 +2323,7 @@
         <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1234950401155566</v>
+        <v>0.1234950401155569</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -2360,7 +2360,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00954422484693343</v>
+        <v>0.009544224847013203</v>
       </c>
       <c r="H5" t="n">
         <v>9</v>
@@ -2397,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04068447534612057</v>
+        <v>0.04068447534612076</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -2434,7 +2434,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0193915821436946</v>
+        <v>0.01939158214369482</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -2471,7 +2471,7 @@
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04146228699703606</v>
+        <v>0.0414622869970363</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -2508,7 +2508,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07313631731292096</v>
+        <v>0.07313631731292118</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -2545,7 +2545,7 @@
         <v>9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007081922240861072</v>
+        <v>0.007081922240861216</v>
       </c>
       <c r="H10" t="n">
         <v>10</v>
@@ -2582,7 +2582,7 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001167319465762529</v>
+        <v>0.001167319465762784</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -2619,7 +2619,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003669765706062533</v>
+        <v>0.003669765706062789</v>
       </c>
       <c r="H12" t="n">
         <v>12</v>
@@ -2656,7 +2656,7 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00234765733884762</v>
+        <v>0.002347657338847842</v>
       </c>
       <c r="H13" t="n">
         <v>13</v>
@@ -2693,7 +2693,7 @@
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.00967522210960442</v>
+        <v>0.009675222109604665</v>
       </c>
       <c r="H14" t="n">
         <v>8</v>
@@ -2730,7 +2730,7 @@
         <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.002200612697474014</v>
+        <v>0.002200612697474224</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
@@ -2767,7 +2767,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.004257424079439265</v>
+        <v>0.004257424079439476</v>
       </c>
       <c r="H16" t="n">
         <v>11</v>
@@ -2804,7 +2804,7 @@
         <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004731324973604622</v>
+        <v>0.0004731324973606621</v>
       </c>
       <c r="H17" t="n">
         <v>29</v>
@@ -2841,7 +2841,7 @@
         <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001557680894965219</v>
+        <v>0.00155768089496543</v>
       </c>
       <c r="H18" t="n">
         <v>21</v>
@@ -2878,7 +2878,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0003561726197054416</v>
+        <v>-0.0003561726197052306</v>
       </c>
       <c r="H19" t="n">
         <v>42</v>
@@ -2915,7 +2915,7 @@
         <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0004374426895113359</v>
+        <v>0.0004374426895115802</v>
       </c>
       <c r="H20" t="n">
         <v>30</v>
@@ -2952,7 +2952,7 @@
         <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001158717634249884</v>
+        <v>0.001158717634250084</v>
       </c>
       <c r="H21" t="n">
         <v>25</v>
@@ -4245,10 +4245,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2154246116620057</v>
+        <v>0.2154246116620059</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02808542429341231</v>
+        <v>0.02808542429341228</v>
       </c>
     </row>
     <row r="3">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1234950401155566</v>
+        <v>0.1234950401155569</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01378019701006953</v>
+        <v>0.01378019701006952</v>
       </c>
     </row>
     <row r="4">
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1088415266228941</v>
+        <v>0.1088415266228942</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01863672268410217</v>
+        <v>0.01863672268410218</v>
       </c>
     </row>
     <row r="5">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07313631731292096</v>
+        <v>0.07313631731292118</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02194149750989386</v>
+        <v>0.02194149750989388</v>
       </c>
     </row>
     <row r="6">
@@ -4309,10 +4309,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04146228699703606</v>
+        <v>0.0414622869970363</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005809587909893889</v>
+        <v>0.005809587909893852</v>
       </c>
     </row>
     <row r="7">
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.04068447534612057</v>
+        <v>0.04068447534612076</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006685098577247514</v>
+        <v>0.006685098577247553</v>
       </c>
     </row>
     <row r="8">
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0193915821436946</v>
+        <v>0.01939158214369482</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002489699165584055</v>
+        <v>0.002489699165584047</v>
       </c>
     </row>
     <row r="9">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.00967522210960442</v>
+        <v>0.009675222109604665</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00344559597061358</v>
+        <v>0.003445595970613597</v>
       </c>
     </row>
     <row r="10">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.00954422484693343</v>
+        <v>0.009544224847013203</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000854619388731545</v>
+        <v>0.0008546193887320029</v>
       </c>
     </row>
     <row r="11">
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.007081922240861072</v>
+        <v>0.007081922240861216</v>
       </c>
       <c r="D11" t="n">
-        <v>0.004405778210307942</v>
+        <v>0.004405778210307932</v>
       </c>
     </row>
     <row r="12">
@@ -4405,10 +4405,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.004257424079439265</v>
+        <v>0.004257424079439476</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0008371371528291806</v>
+        <v>0.0008371371528291786</v>
       </c>
     </row>
     <row r="13">
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.003669765706062533</v>
+        <v>0.003669765706062789</v>
       </c>
       <c r="D13" t="n">
-        <v>0.006367042308607108</v>
+        <v>0.006367042308607099</v>
       </c>
     </row>
     <row r="14">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00234765733884762</v>
+        <v>0.002347657338847842</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001388178255553523</v>
+        <v>0.001388178255553495</v>
       </c>
     </row>
     <row r="15">
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002313667322257829</v>
+        <v>0.002313667322258029</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00130261506320563</v>
+        <v>0.001302615063205668</v>
       </c>
     </row>
     <row r="16">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002200612697474014</v>
+        <v>0.002200612697474224</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001640237144867023</v>
+        <v>0.00164023714486703</v>
       </c>
     </row>
     <row r="17">
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001854788330938906</v>
+        <v>0.001854788330939139</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0008958620777341561</v>
+        <v>0.0008958620777341598</v>
       </c>
     </row>
     <row r="18">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001854266814861505</v>
+        <v>0.001854266814861694</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0008280998316244653</v>
+        <v>0.0008280998316244859</v>
       </c>
     </row>
     <row r="19">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001815440161301607</v>
+        <v>0.001815440161301785</v>
       </c>
       <c r="D19" t="n">
-        <v>0.002203211375274682</v>
+        <v>0.002203211375274665</v>
       </c>
     </row>
     <row r="20">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001753806644895251</v>
+        <v>0.001753806644895495</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0007011217938123496</v>
+        <v>0.0007011217938123471</v>
       </c>
     </row>
     <row r="21">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001719716920516601</v>
+        <v>0.001719716920516778</v>
       </c>
       <c r="D21" t="n">
-        <v>0.001167759873172896</v>
+        <v>0.001167759873172881</v>
       </c>
     </row>
     <row r="22">
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001557680894965219</v>
+        <v>0.00155768089496543</v>
       </c>
       <c r="D22" t="n">
-        <v>0.001107361403705596</v>
+        <v>0.001107361403705588</v>
       </c>
     </row>
     <row r="23">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001464157095111895</v>
+        <v>0.00146415709511214</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002388191188903398</v>
+        <v>0.000238819118890349</v>
       </c>
     </row>
     <row r="24">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001228068427357631</v>
+        <v>0.001228068427357865</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0008702151334907269</v>
+        <v>0.0008702151334907064</v>
       </c>
     </row>
     <row r="25">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001167319465762529</v>
+        <v>0.001167319465762784</v>
       </c>
       <c r="D25" t="n">
-        <v>0.003100860501643398</v>
+        <v>0.003100860501643377</v>
       </c>
     </row>
     <row r="26">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001158717634249884</v>
+        <v>0.001158717634250084</v>
       </c>
       <c r="D26" t="n">
-        <v>0.001073727351732406</v>
+        <v>0.001073727351732405</v>
       </c>
     </row>
     <row r="27">
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0009890090611721525</v>
+        <v>0.0009890090611723301</v>
       </c>
       <c r="D27" t="n">
-        <v>0.001138131895380745</v>
+        <v>0.001138131895380738</v>
       </c>
     </row>
     <row r="28">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0005601140805585713</v>
+        <v>0.0005601140805587934</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0004434803375421696</v>
+        <v>0.0004434803375421708</v>
       </c>
     </row>
     <row r="29">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0005228209926652183</v>
+        <v>0.0005228209926654182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0005133725593386311</v>
+        <v>0.0005133725593386553</v>
       </c>
     </row>
     <row r="30">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0004731324973604622</v>
+        <v>0.0004731324973606621</v>
       </c>
       <c r="D30" t="n">
-        <v>0.001653268709317363</v>
+        <v>0.001653268709317334</v>
       </c>
     </row>
     <row r="31">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0004374426895113359</v>
+        <v>0.0004374426895115802</v>
       </c>
       <c r="D31" t="n">
-        <v>0.001379879424497453</v>
+        <v>0.001379879424497454</v>
       </c>
     </row>
     <row r="32">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0003738514379423852</v>
+        <v>0.000373851437942585</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0006258970832914124</v>
+        <v>0.0006258970832914084</v>
       </c>
     </row>
     <row r="33">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0002535083457600895</v>
+        <v>0.0002535083457603338</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0004960798918775569</v>
+        <v>0.0004960798918775981</v>
       </c>
     </row>
     <row r="34">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001916042889941849</v>
+        <v>0.0001916042889944181</v>
       </c>
       <c r="D34" t="n">
-        <v>0.000509652408421358</v>
+        <v>0.0005096524084213675</v>
       </c>
     </row>
     <row r="35">
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7.982958698586895e-05</v>
+        <v>7.98295869860799e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0005867689384629039</v>
+        <v>0.0005867689384628971</v>
       </c>
     </row>
     <row r="36">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.713116728114475e-05</v>
+        <v>4.7131167281389e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>5.447493510932615e-05</v>
+        <v>5.447493510929977e-05</v>
       </c>
     </row>
     <row r="37">
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.58058941945616e-05</v>
+        <v>4.580589419481695e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0001011902536356673</v>
+        <v>0.0001011902536356924</v>
       </c>
     </row>
     <row r="38">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3.929368774836517e-05</v>
+        <v>3.929368774857611e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>1.774249205124809e-05</v>
+        <v>1.77424920512815e-05</v>
       </c>
     </row>
     <row r="39">
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-1.386100759229736e-05</v>
+        <v>-1.386100759208642e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>1.383000399694778e-05</v>
+        <v>1.383000399696545e-05</v>
       </c>
     </row>
     <row r="40">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-7.045442892575915e-05</v>
+        <v>-7.0454428925526e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0004115422248265511</v>
+        <v>0.0004115422248265537</v>
       </c>
     </row>
     <row r="41">
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.0001852744188726829</v>
+        <v>-0.0001852744188724609</v>
       </c>
       <c r="D41" t="n">
         <v>0.0001474809906506867</v>
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.0002079511254434618</v>
+        <v>-0.0002079511254432176</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0001651712763145363</v>
+        <v>0.0001651712763145285</v>
       </c>
     </row>
     <row r="43">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.0003561726197054416</v>
+        <v>-0.0003561726197052306</v>
       </c>
       <c r="D43" t="n">
-        <v>0.004190309319738963</v>
+        <v>0.004190309319738974</v>
       </c>
     </row>
     <row r="44">
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.0003614879095183099</v>
+        <v>-0.0003614879095180879</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0005902871062729058</v>
+        <v>0.0005902871062729006</v>
       </c>
     </row>
     <row r="45">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.0003790091634006454</v>
+        <v>-0.0003790091634004123</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002888491131521844</v>
+        <v>0.0002888491131521806</v>
       </c>
     </row>
     <row r="46">
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0007288706209371498</v>
+        <v>-0.0007288706209369056</v>
       </c>
       <c r="D46" t="n">
-        <v>0.001728379781492024</v>
+        <v>0.001728379781492075</v>
       </c>
     </row>
   </sheetData>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 14:07:49 UTC</t>
+          <t>2026-06-16 15:21:23 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_ash.xlsx
+++ b/NN/reports/feature_importance_white_ash.xlsx
@@ -624,7 +624,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0267286212150805</v>
+        <v>0.02672862121508051</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02321682924137427</v>
+        <v>0.02321682924137426</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007607948772168915</v>
+        <v>0.007607948772168938</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02412762964736483</v>
+        <v>0.02412762964736486</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003391445003130155</v>
+        <v>0.0003391445003132153</v>
       </c>
       <c r="H9" t="n">
         <v>13</v>
@@ -809,7 +809,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005898315449532676</v>
+        <v>0.0005898315449532898</v>
       </c>
       <c r="H10" t="n">
         <v>8</v>
@@ -846,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003414091818776388</v>
+        <v>0.0003414091818776499</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -883,7 +883,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002622409575994022</v>
+        <v>0.0002622409575994133</v>
       </c>
       <c r="H12" t="n">
         <v>20</v>
@@ -920,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003118967992993826</v>
+        <v>0.0003118967992993715</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -957,7 +957,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002677155603517445</v>
+        <v>0.0002677155603517667</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -994,7 +994,7 @@
         <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003836315463246143</v>
+        <v>0.0003836315463246476</v>
       </c>
       <c r="H15" t="n">
         <v>9</v>
@@ -1031,7 +1031,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001394017991636964</v>
+        <v>0.0001394017991637298</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -1068,7 +1068,7 @@
         <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0002794175086170636</v>
+        <v>0.0002794175086170525</v>
       </c>
       <c r="H17" t="n">
         <v>18</v>
@@ -1105,7 +1105,7 @@
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002076550830599877</v>
+        <v>0.0002076550830599988</v>
       </c>
       <c r="H18" t="n">
         <v>21</v>
@@ -1142,7 +1142,7 @@
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003451852789800203</v>
+        <v>0.0003451852789800536</v>
       </c>
       <c r="H19" t="n">
         <v>11</v>
@@ -1179,7 +1179,7 @@
         <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003046542802608299</v>
+        <v>0.000304654280260841</v>
       </c>
       <c r="H20" t="n">
         <v>16</v>
@@ -1253,7 +1253,7 @@
         <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001718180908426681</v>
+        <v>0.000171818090842657</v>
       </c>
       <c r="H22" t="n">
         <v>22</v>
@@ -1327,7 +1327,7 @@
         <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0007979795144487101</v>
+        <v>-0.0007979795144487211</v>
       </c>
       <c r="H24" t="n">
         <v>53</v>
@@ -1364,7 +1364,7 @@
         <v>34</v>
       </c>
       <c r="G25" t="n">
-        <v>7.508100486477431e-05</v>
+        <v>7.508100486478542e-05</v>
       </c>
       <c r="H25" t="n">
         <v>30</v>
@@ -1401,7 +1401,7 @@
         <v>21</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0001431098473282488</v>
+        <v>-0.000143109847328271</v>
       </c>
       <c r="H26" t="n">
         <v>50</v>
@@ -1438,7 +1438,7 @@
         <v>29</v>
       </c>
       <c r="G27" t="n">
-        <v>4.451721783136353e-05</v>
+        <v>4.451721783137464e-05</v>
       </c>
       <c r="H27" t="n">
         <v>33</v>
@@ -1475,7 +1475,7 @@
         <v>22</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.667800517023421e-05</v>
+        <v>-1.667800517020091e-05</v>
       </c>
       <c r="H28" t="n">
         <v>42</v>
@@ -1512,7 +1512,7 @@
         <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0003785540810612442</v>
+        <v>0.0003785540810612109</v>
       </c>
       <c r="H29" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
         <v>33</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0001149755631063343</v>
+        <v>0.0001149755631063676</v>
       </c>
       <c r="H30" t="n">
         <v>25</v>
@@ -1623,7 +1623,7 @@
         <v>31</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0001678774978638109</v>
+        <v>0.000167877497863822</v>
       </c>
       <c r="H32" t="n">
         <v>23</v>
@@ -1660,7 +1660,7 @@
         <v>25</v>
       </c>
       <c r="G33" t="n">
-        <v>-6.855343983093176e-05</v>
+        <v>-6.855343983092066e-05</v>
       </c>
       <c r="H33" t="n">
         <v>45</v>
@@ -1697,7 +1697,7 @@
         <v>24</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.0002577785125864707</v>
+        <v>-0.0002577785125864818</v>
       </c>
       <c r="H34" t="n">
         <v>51</v>
@@ -1734,7 +1734,7 @@
         <v>20</v>
       </c>
       <c r="G35" t="n">
-        <v>4.514813604096224e-05</v>
+        <v>4.514813604092893e-05</v>
       </c>
       <c r="H35" t="n">
         <v>32</v>
@@ -1771,7 +1771,7 @@
         <v>17</v>
       </c>
       <c r="G36" t="n">
-        <v>3.269396022548277e-05</v>
+        <v>3.269396022547167e-05</v>
       </c>
       <c r="H36" t="n">
         <v>35</v>
@@ -1808,7 +1808,7 @@
         <v>26</v>
       </c>
       <c r="G37" t="n">
-        <v>3.301514620210888e-05</v>
+        <v>3.301514620211999e-05</v>
       </c>
       <c r="H37" t="n">
         <v>34</v>
@@ -1845,7 +1845,7 @@
         <v>13</v>
       </c>
       <c r="G38" t="n">
-        <v>3.188194014031032e-05</v>
+        <v>3.188194014029922e-05</v>
       </c>
       <c r="H38" t="n">
         <v>36</v>
@@ -1919,7 +1919,7 @@
         <v>42</v>
       </c>
       <c r="G40" t="n">
-        <v>-7.676763974000523e-05</v>
+        <v>-7.676763973999413e-05</v>
       </c>
       <c r="H40" t="n">
         <v>47</v>
@@ -1956,7 +1956,7 @@
         <v>41</v>
       </c>
       <c r="G41" t="n">
-        <v>9.737969164342885e-05</v>
+        <v>9.737969164345107e-05</v>
       </c>
       <c r="H41" t="n">
         <v>27</v>
@@ -1993,7 +1993,7 @@
         <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>-7.059586605757673e-05</v>
+        <v>-7.059586605755453e-05</v>
       </c>
       <c r="H42" t="n">
         <v>46</v>
@@ -2104,7 +2104,7 @@
         <v>47</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0001032949656526116</v>
+        <v>0.0001032949656526228</v>
       </c>
       <c r="H45" t="n">
         <v>26</v>
@@ -2178,7 +2178,7 @@
         <v>48</v>
       </c>
       <c r="G47" t="n">
-        <v>7.591721942727947e-05</v>
+        <v>7.591721942731277e-05</v>
       </c>
       <c r="H47" t="n">
         <v>29</v>
@@ -2215,7 +2215,7 @@
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>-9.471982957667268e-05</v>
+        <v>-9.471982957668379e-05</v>
       </c>
       <c r="H48" t="n">
         <v>49</v>
@@ -2289,7 +2289,7 @@
         <v>45</v>
       </c>
       <c r="G50" t="n">
-        <v>-8.463044702849976e-05</v>
+        <v>-8.463044702852195e-05</v>
       </c>
       <c r="H50" t="n">
         <v>48</v>
@@ -2326,7 +2326,7 @@
         <v>49</v>
       </c>
       <c r="G51" t="n">
-        <v>-5.715355416913149e-06</v>
+        <v>-5.715355416935353e-06</v>
       </c>
       <c r="H51" t="n">
         <v>41</v>
@@ -2363,7 +2363,7 @@
         <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>1.367625866949274e-05</v>
+        <v>1.367625866950384e-05</v>
       </c>
       <c r="H52" t="n">
         <v>38</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0267286212150805</v>
+        <v>0.02672862121508051</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -2693,7 +2693,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02321682924137427</v>
+        <v>0.02321682924137426</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -2730,7 +2730,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007607948772168915</v>
+        <v>0.007607948772168938</v>
       </c>
       <c r="H7" t="n">
         <v>7</v>
@@ -2767,7 +2767,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02412762964736483</v>
+        <v>0.02412762964736486</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -2804,7 +2804,7 @@
         <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0003391445003130155</v>
+        <v>0.0003391445003132153</v>
       </c>
       <c r="H9" t="n">
         <v>13</v>
@@ -2841,7 +2841,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0005898315449532676</v>
+        <v>0.0005898315449532898</v>
       </c>
       <c r="H10" t="n">
         <v>8</v>
@@ -2878,7 +2878,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0003414091818776388</v>
+        <v>0.0003414091818776499</v>
       </c>
       <c r="H11" t="n">
         <v>12</v>
@@ -2915,7 +2915,7 @@
         <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002622409575994022</v>
+        <v>0.0002622409575994133</v>
       </c>
       <c r="H12" t="n">
         <v>20</v>
@@ -2952,7 +2952,7 @@
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0003118967992993826</v>
+        <v>0.0003118967992993715</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -2989,7 +2989,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002677155603517445</v>
+        <v>0.0002677155603517667</v>
       </c>
       <c r="H14" t="n">
         <v>19</v>
@@ -3026,7 +3026,7 @@
         <v>28</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003836315463246143</v>
+        <v>0.0003836315463246476</v>
       </c>
       <c r="H15" t="n">
         <v>9</v>
@@ -3063,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0001394017991636964</v>
+        <v>0.0001394017991637298</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -3100,7 +3100,7 @@
         <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0002794175086170636</v>
+        <v>0.0002794175086170525</v>
       </c>
       <c r="H17" t="n">
         <v>18</v>
@@ -3137,7 +3137,7 @@
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0002076550830599877</v>
+        <v>0.0002076550830599988</v>
       </c>
       <c r="H18" t="n">
         <v>21</v>
@@ -3174,7 +3174,7 @@
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003451852789800203</v>
+        <v>0.0003451852789800536</v>
       </c>
       <c r="H19" t="n">
         <v>11</v>
@@ -3211,7 +3211,7 @@
         <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003046542802608299</v>
+        <v>0.000304654280260841</v>
       </c>
       <c r="H20" t="n">
         <v>16</v>
@@ -4752,7 +4752,7 @@
         <v>1.707635805653452</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07801799479420515</v>
+        <v>0.07801799479420517</v>
       </c>
     </row>
     <row r="3">
@@ -4768,7 +4768,7 @@
         <v>0.09795943275339536</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008682725788401426</v>
+        <v>0.008682725788401466</v>
       </c>
     </row>
     <row r="4">
@@ -4784,7 +4784,7 @@
         <v>0.05354981604745403</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005935131558129029</v>
+        <v>0.005935131558128992</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0267286212150805</v>
+        <v>0.02672862121508051</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003212245253402749</v>
+        <v>0.003212245253402783</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.02412762964736483</v>
+        <v>0.02412762964736486</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002811931222986497</v>
+        <v>0.002811931222986525</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02321682924137427</v>
+        <v>0.02321682924137426</v>
       </c>
       <c r="D7" t="n">
-        <v>0.003626306122843932</v>
+        <v>0.003626306122843926</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007607948772168915</v>
+        <v>0.007607948772168938</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002231029644669918</v>
+        <v>0.002231029644669924</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0005898315449532676</v>
+        <v>0.0005898315449532898</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004752076410622965</v>
+        <v>0.0004752076410622951</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0003836315463246143</v>
+        <v>0.0003836315463246476</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0001569891301369052</v>
+        <v>0.0001569891301368725</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.0003785540810612442</v>
+        <v>0.0003785540810612109</v>
       </c>
       <c r="D11" t="n">
-        <v>9.320889179858812e-05</v>
+        <v>9.320889179855772e-05</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0003451852789800203</v>
+        <v>0.0003451852789800536</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0001229530453033242</v>
+        <v>0.0001229530453033177</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0003414091818776388</v>
+        <v>0.0003414091818776499</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001949165249264165</v>
+        <v>0.0001949165249264202</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0003391445003130155</v>
+        <v>0.0003391445003132153</v>
       </c>
       <c r="D14" t="n">
-        <v>3.707081220569008e-05</v>
+        <v>3.707081220456666e-05</v>
       </c>
     </row>
     <row r="15">
@@ -4960,7 +4960,7 @@
         <v>0.0003204965668262783</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0001922446410491603</v>
+        <v>0.0001922446410491616</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0003118967992993826</v>
+        <v>0.0003118967992993715</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0003173268004239832</v>
+        <v>0.0003173268004239815</v>
       </c>
     </row>
     <row r="17">
@@ -4989,10 +4989,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0003046542802608299</v>
+        <v>0.000304654280260841</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0001439406965768496</v>
+        <v>0.0001439406965768341</v>
       </c>
     </row>
     <row r="18">
@@ -5008,7 +5008,7 @@
         <v>0.0002799502317631264</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001280604313256435</v>
+        <v>0.0001280604313256624</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0002794175086170636</v>
+        <v>0.0002794175086170525</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0003944946494375706</v>
+        <v>0.0003944946494375663</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0002677155603517445</v>
+        <v>0.0002677155603517667</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001647124028711472</v>
+        <v>0.0001647124028711501</v>
       </c>
     </row>
     <row r="21">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0002622409575994022</v>
+        <v>0.0002622409575994133</v>
       </c>
       <c r="D21" t="n">
-        <v>7.740803687130581e-05</v>
+        <v>7.740803687132656e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0002076550830599877</v>
+        <v>0.0002076550830599988</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001455212522585836</v>
+        <v>0.0001455212522585714</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0001718180908426681</v>
+        <v>0.000171818090842657</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001570658298068233</v>
+        <v>0.00015706582980682</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0001678774978638109</v>
+        <v>0.000167877497863822</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0001349968981410332</v>
+        <v>0.0001349968981410507</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0001394017991636964</v>
+        <v>0.0001394017991637298</v>
       </c>
       <c r="D25" t="n">
-        <v>0.000220205941170529</v>
+        <v>0.0002202059411705452</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0001149755631063343</v>
+        <v>0.0001149755631063676</v>
       </c>
       <c r="D26" t="n">
-        <v>6.155517252700753e-05</v>
+        <v>6.155517252705322e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0001032949656526116</v>
+        <v>0.0001032949656526228</v>
       </c>
       <c r="D27" t="n">
-        <v>6.520066052022178e-05</v>
+        <v>6.520066052020097e-05</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9.737969164342885e-05</v>
+        <v>9.737969164345107e-05</v>
       </c>
       <c r="D28" t="n">
-        <v>4.872398371474235e-05</v>
+        <v>4.872398371475305e-05</v>
       </c>
     </row>
     <row r="29">
@@ -5184,7 +5184,7 @@
         <v>7.943631783050576e-05</v>
       </c>
       <c r="D29" t="n">
-        <v>5.051636987226809e-05</v>
+        <v>5.051636987227834e-05</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.591721942727947e-05</v>
+        <v>7.591721942731277e-05</v>
       </c>
       <c r="D30" t="n">
-        <v>6.203837256941819e-05</v>
+        <v>6.203837256942922e-05</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7.508100486477431e-05</v>
+        <v>7.508100486478542e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0001249166349489409</v>
+        <v>0.0001249166349489544</v>
       </c>
     </row>
     <row r="32">
@@ -5232,7 +5232,7 @@
         <v>5.396597271619674e-05</v>
       </c>
       <c r="D32" t="n">
-        <v>7.491467483872107e-05</v>
+        <v>7.491467483870237e-05</v>
       </c>
     </row>
     <row r="33">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4.514813604096224e-05</v>
+        <v>4.514813604092893e-05</v>
       </c>
       <c r="D33" t="n">
-        <v>2.601168765519987e-05</v>
+        <v>2.601168765518539e-05</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4.451721783136353e-05</v>
+        <v>4.451721783137464e-05</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0001464450104960018</v>
+        <v>0.0001464450104959824</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3.301514620210888e-05</v>
+        <v>3.301514620211999e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>6.669297915275336e-05</v>
+        <v>6.669297915274081e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.269396022548277e-05</v>
+        <v>3.269396022547167e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>2.519865399273078e-05</v>
+        <v>2.519865399272013e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3.188194014031032e-05</v>
+        <v>3.188194014029922e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>2.528221235999303e-05</v>
+        <v>2.528221235998709e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5328,7 +5328,7 @@
         <v>2.541221249653392e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>5.84706564231459e-05</v>
+        <v>5.847065642314351e-05</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.367625866949274e-05</v>
+        <v>1.367625866950384e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>7.824739093467306e-06</v>
+        <v>7.824739093473277e-06</v>
       </c>
     </row>
     <row r="40">
@@ -5360,7 +5360,7 @@
         <v>9.887444687772806e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0001154125676430098</v>
+        <v>0.0001154125676429942</v>
       </c>
     </row>
     <row r="41">
@@ -5376,7 +5376,7 @@
         <v>-3.37317632691514e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>3.103601093983625e-06</v>
+        <v>3.103601093993018e-06</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-5.715355416913149e-06</v>
+        <v>-5.715355416935353e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>1.861720893452239e-05</v>
+        <v>1.861720893454216e-05</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-1.667800517023421e-05</v>
+        <v>-1.667800517020091e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0003124043520494461</v>
+        <v>0.0003124043520494532</v>
       </c>
     </row>
     <row r="44">
@@ -5424,7 +5424,7 @@
         <v>-2.377115489509141e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001786426619872065</v>
+        <v>0.0001786426619872424</v>
       </c>
     </row>
     <row r="45">
@@ -5440,7 +5440,7 @@
         <v>-2.704625013825179e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>1.552544431576424e-05</v>
+        <v>1.552544431577921e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-6.855343983093176e-05</v>
+        <v>-6.855343983092066e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0001749117956052541</v>
+        <v>0.0001749117956052367</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-7.059586605757673e-05</v>
+        <v>-7.059586605755453e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0001541723545647746</v>
+        <v>0.0001541723545648253</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-7.676763974000523e-05</v>
+        <v>-7.676763973999413e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>9.031310258090133e-05</v>
+        <v>9.031310258090262e-05</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-8.463044702849976e-05</v>
+        <v>-8.463044702852195e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>3.332377236627358e-05</v>
+        <v>3.332377236627373e-05</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-9.471982957667268e-05</v>
+        <v>-9.471982957668379e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001419861488978549</v>
+        <v>0.0001419861488978697</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.0001431098473282488</v>
+        <v>-0.000143109847328271</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0001179461880385185</v>
+        <v>0.0001179461880384979</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0002577785125864707</v>
+        <v>-0.0002577785125864818</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0001257590458424681</v>
+        <v>0.0001257590458424582</v>
       </c>
     </row>
     <row r="53">
@@ -5568,7 +5568,7 @@
         <v>-0.0002784330466673035</v>
       </c>
       <c r="D53" t="n">
-        <v>8.788422570898574e-05</v>
+        <v>8.788422570898975e-05</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0007979795144487101</v>
+        <v>-0.0007979795144487211</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003239428442837587</v>
+        <v>0.0003239428442837166</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 21:59:55 UTC</t>
+          <t>2026-06-16 19:26:08 UTC</t>
         </is>
       </c>
     </row>
